--- a/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -1,59 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\EPS Models\EPS China 3.3.1\InputData\trans\BCDTRtSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BCDTRtSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D596A40-B1E8-45CB-9B27-84705F591AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2672D63-A094-4683-905F-A8926D8DCAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="742" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4293" yWindow="788" windowWidth="15378" windowHeight="13069" tabRatio="742" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="33" r:id="rId1"/>
     <sheet name="raw data" sheetId="26" r:id="rId2"/>
     <sheet name="passenger" sheetId="38" r:id="rId3"/>
-    <sheet name="freight" sheetId="39" r:id="rId4"/>
-    <sheet name="BCDTRtSY-psgr" sheetId="31" r:id="rId5"/>
-    <sheet name="BCDTRtSY-frgt" sheetId="32" r:id="rId6"/>
+    <sheet name="2022交科院" sheetId="40" r:id="rId4"/>
+    <sheet name="freight" sheetId="39" r:id="rId5"/>
+    <sheet name="BCDTRtSY-psgr" sheetId="31" r:id="rId6"/>
+    <sheet name="BCDTRtSY-frgt" sheetId="32" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="_Toc93782300" localSheetId="0">'About '!$B$16</definedName>
     <definedName name="_Toc93782301" localSheetId="0">'About '!$B$17</definedName>
     <definedName name="Eno_TM" localSheetId="0">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Eno_TM" localSheetId="6">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_TM" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM">'[2]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="0">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Eno_Tons" localSheetId="6">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_Tons" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons">'[2]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="0">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Sum_T2" localSheetId="6">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_T2" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2">'[2]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="0">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Sum_TTM" localSheetId="6">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_TTM" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM">'[2]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="0">#REF!</definedName>
+    <definedName name="ti_tbl_50" localSheetId="6">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="5">#REF!</definedName>
-    <definedName name="ti_tbl_50" localSheetId="4">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="1">#REF!</definedName>
     <definedName name="ti_tbl_50">#REF!</definedName>
+    <definedName name="ti_tbl_69" localSheetId="6">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="5">#REF!</definedName>
-    <definedName name="ti_tbl_69" localSheetId="4">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="1">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
   </definedNames>
@@ -95,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="122">
   <si>
     <t>Sources:</t>
   </si>
@@ -464,6 +465,220 @@
     <t>Freight</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
+  <si>
+    <t>周转量</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>BCD</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>客运航空</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>货运航空</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>人均GDP预测数据</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>客运铁路</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>货运铁路</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁路旅客周转量(亿人公里)</t>
+  </si>
+  <si>
+    <t>公路旅客周转量(亿人公里)</t>
+  </si>
+  <si>
+    <t>水运旅客周转量(亿人公里)</t>
+  </si>
+  <si>
+    <t>民用航空旅客周转量(亿人公里)</t>
+  </si>
+  <si>
+    <t>公交车(亿人次)</t>
+  </si>
+  <si>
+    <t>轨道交通(亿人次)</t>
+  </si>
+  <si>
+    <t>巡游出租车(亿人次)</t>
+  </si>
+  <si>
+    <t>网约车(亿人次)</t>
+  </si>
+  <si>
+    <t>私家车出行(亿人次)</t>
+  </si>
+  <si>
+    <t>铁路货物周转量(亿吨公里)</t>
+  </si>
+  <si>
+    <t>公路货物周转量(亿吨公里)</t>
+  </si>
+  <si>
+    <t>内河货运周转量 (亿吨公里)</t>
+  </si>
+  <si>
+    <t>沿海货运周转量(亿吨公里)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>民用航空货物周转量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿吨公里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8266</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4641</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>33.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5892</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>客运水运</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>货运水运</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>远洋</t>
+    </r>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>客运周转量</t>
+  </si>
+  <si>
+    <t>乘用车</t>
+  </si>
+  <si>
+    <t>出租车</t>
+  </si>
+  <si>
+    <t>公交车</t>
+  </si>
+  <si>
+    <t>道路客车</t>
+  </si>
+  <si>
+    <t>道路客运</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>微型货车</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻型货车</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型货车</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型货车</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -479,7 +694,7 @@
     <numFmt numFmtId="182" formatCode="0.000_ "/>
     <numFmt numFmtId="183" formatCode="0_ "/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="64">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,8 +1057,38 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1019,8 +1264,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1398,8 +1649,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="155">
+  <cellStyleXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyProtection="0">
@@ -1656,8 +1918,9 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1793,11 +2056,9 @@
     </xf>
     <xf numFmtId="183" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1810,6 +2071,9 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1841,9 +2105,31 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="155" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="155" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="155">
+  <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="20% - Accent2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent3 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -1998,6 +2284,7 @@
     <cellStyle name="Wrap Title" xfId="151" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
     <cellStyle name="Wrap_NTS99-~11" xfId="152" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="155" xr:uid="{69A2AD4D-109A-42E1-B86D-E51CC952D9FD}"/>
     <cellStyle name="超链接" xfId="153" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2017,16 +2304,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>112145</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>163905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>152009</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381864</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>134760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2049,8 +2336,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="5311140"/>
-          <a:ext cx="5768340" cy="3078089"/>
+          <a:off x="4485737" y="1069679"/>
+          <a:ext cx="5859636" cy="2774439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2146,6 +2433,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
       <sheetName val="Waterborne Flows 93-97"/>
@@ -2225,9 +2515,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2265,9 +2555,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2300,26 +2590,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2352,26 +2625,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2546,7 +2802,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="107.5" customWidth="1"/>
@@ -2636,7 +2892,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.6" customHeight="1"/>
+    <row r="22" spans="1:2" ht="15.65" customHeight="1"/>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>15</v>
@@ -2667,13 +2923,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15">
+    <row r="30" spans="1:2" ht="14.3">
       <c r="B30" s="19"/>
     </row>
-    <row r="31" spans="1:2" ht="15">
+    <row r="31" spans="1:2" ht="14.3">
       <c r="B31" s="19"/>
     </row>
-    <row r="32" spans="1:2" ht="15">
+    <row r="32" spans="1:2" ht="14.3">
       <c r="B32" s="19"/>
     </row>
   </sheetData>
@@ -2689,7 +2945,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W53"/>
-  <sheetFormatPr defaultRowHeight="13.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="13.6" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -2707,7 +2963,7 @@
     <col min="16" max="21" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.5" customHeight="1">
+    <row r="1" spans="1:21" ht="13.6" customHeight="1">
       <c r="A1" s="60" t="s">
         <v>61</v>
       </c>
@@ -2726,7 +2982,7 @@
       <c r="M1" s="60"/>
       <c r="N1" s="40"/>
     </row>
-    <row r="2" spans="1:21" s="39" customFormat="1" ht="13.5" customHeight="1">
+    <row r="2" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
       <c r="A2" s="59" t="s">
         <v>25</v>
       </c>
@@ -2766,7 +3022,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="39" customFormat="1" ht="13.5" customHeight="1">
+    <row r="3" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
       <c r="A3" s="59"/>
       <c r="B3" s="59"/>
       <c r="C3" s="59"/>
@@ -2784,7 +3040,7 @@
       </c>
       <c r="N3" s="59"/>
     </row>
-    <row r="4" spans="1:21" ht="13.5" customHeight="1">
+    <row r="4" spans="1:21" ht="13.6" customHeight="1">
       <c r="A4" s="42" t="s">
         <v>27</v>
       </c>
@@ -2825,7 +3081,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="13.5" customHeight="1">
+    <row r="5" spans="1:21" ht="13.6" customHeight="1">
       <c r="A5" s="42" t="s">
         <v>28</v>
       </c>
@@ -2866,7 +3122,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="13.5" customHeight="1">
+    <row r="6" spans="1:21" ht="13.6" customHeight="1">
       <c r="A6" s="42" t="s">
         <v>29</v>
       </c>
@@ -2906,16 +3162,16 @@
       <c r="N6" s="44">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="57" t="s">
+      <c r="P6" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
     </row>
-    <row r="7" spans="1:21" ht="13.5" customHeight="1">
+    <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="42" t="s">
         <v>30</v>
       </c>
@@ -2970,7 +3226,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="13.5" customHeight="1">
+    <row r="8" spans="1:21" ht="13.6" customHeight="1">
       <c r="A8" s="42" t="s">
         <v>31</v>
       </c>
@@ -3017,7 +3273,7 @@
       <c r="T8" s="58"/>
       <c r="U8" s="58"/>
     </row>
-    <row r="9" spans="1:21" ht="13.5" customHeight="1">
+    <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="42" t="s">
         <v>32</v>
       </c>
@@ -3057,7 +3313,7 @@
       <c r="N9" s="44">
         <v>13.42</v>
       </c>
-      <c r="P9" s="56" t="s">
+      <c r="P9" s="57" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="54">
@@ -3076,7 +3332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="13.5" customHeight="1">
+    <row r="10" spans="1:21" ht="13.6" customHeight="1">
       <c r="A10" s="42" t="s">
         <v>33</v>
       </c>
@@ -3116,7 +3372,7 @@
       <c r="N10" s="44">
         <v>16.61</v>
       </c>
-      <c r="P10" s="56"/>
+      <c r="P10" s="57"/>
       <c r="Q10" s="54">
         <v>2020</v>
       </c>
@@ -3137,7 +3393,7 @@
         <v>0.53919060922162132</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="13.5" customHeight="1">
+    <row r="11" spans="1:21" ht="13.6" customHeight="1">
       <c r="A11" s="42" t="s">
         <v>34</v>
       </c>
@@ -3177,7 +3433,7 @@
       <c r="N11" s="44">
         <v>18.579999999999998</v>
       </c>
-      <c r="P11" s="56"/>
+      <c r="P11" s="57"/>
       <c r="Q11" s="54">
         <v>2021</v>
       </c>
@@ -3198,7 +3454,7 @@
         <v>0.55784914268139529</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="13.5" customHeight="1">
+    <row r="12" spans="1:21" ht="13.6" customHeight="1">
       <c r="A12" s="42" t="s">
         <v>35</v>
       </c>
@@ -3238,7 +3494,7 @@
       <c r="N12" s="44">
         <v>22.3</v>
       </c>
-      <c r="P12" s="56"/>
+      <c r="P12" s="57"/>
       <c r="Q12" s="54">
         <v>2022</v>
       </c>
@@ -3259,7 +3515,7 @@
         <v>0.33435852747947475</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="13.5" customHeight="1">
+    <row r="13" spans="1:21" ht="13.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>36</v>
       </c>
@@ -3299,7 +3555,7 @@
       <c r="N13" s="44">
         <v>24.93</v>
       </c>
-      <c r="P13" s="56" t="s">
+      <c r="P13" s="57" t="s">
         <v>83</v>
       </c>
       <c r="Q13" s="54">
@@ -3318,7 +3574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="13.5" customHeight="1">
+    <row r="14" spans="1:21" ht="13.6" customHeight="1">
       <c r="A14" s="42" t="s">
         <v>37</v>
       </c>
@@ -3358,7 +3614,7 @@
       <c r="N14" s="44">
         <v>29.1</v>
       </c>
-      <c r="P14" s="56"/>
+      <c r="P14" s="57"/>
       <c r="Q14" s="54">
         <v>2020</v>
       </c>
@@ -3379,7 +3635,7 @@
         <v>0.91261398176291797</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="13.5" customHeight="1">
+    <row r="15" spans="1:21" ht="13.6" customHeight="1">
       <c r="A15" s="42" t="s">
         <v>38</v>
       </c>
@@ -3419,7 +3675,7 @@
       <c r="N15" s="44">
         <v>33.450000000000003</v>
       </c>
-      <c r="P15" s="56"/>
+      <c r="P15" s="57"/>
       <c r="Q15" s="54">
         <v>2021</v>
       </c>
@@ -3440,7 +3696,7 @@
         <v>1.0568389057750762</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="13.5" customHeight="1">
+    <row r="16" spans="1:21" ht="13.6" customHeight="1">
       <c r="A16" s="42" t="s">
         <v>39</v>
       </c>
@@ -3480,7 +3736,7 @@
       <c r="N16" s="44">
         <v>42.34</v>
       </c>
-      <c r="P16" s="56"/>
+      <c r="P16" s="57"/>
       <c r="Q16" s="54">
         <v>2022</v>
       </c>
@@ -3501,7 +3757,7 @@
         <v>0.96542553191489366</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="13.5" customHeight="1">
+    <row r="17" spans="1:23" ht="13.6" customHeight="1">
       <c r="A17" s="42" t="s">
         <v>40</v>
       </c>
@@ -3542,7 +3798,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="13.5" customHeight="1">
+    <row r="18" spans="1:23" ht="13.6" customHeight="1">
       <c r="A18" s="42" t="s">
         <v>41</v>
       </c>
@@ -3583,7 +3839,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="13.5" customHeight="1">
+    <row r="19" spans="1:23" ht="13.6" customHeight="1">
       <c r="A19" s="42" t="s">
         <v>42</v>
       </c>
@@ -3623,17 +3879,17 @@
       <c r="N19" s="44">
         <v>51.55</v>
       </c>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="56" t="s">
+      <c r="P19" s="56"/>
+      <c r="Q19" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="56"/>
-      <c r="S19" s="56"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
     </row>
-    <row r="20" spans="1:23" ht="13.5" customHeight="1">
+    <row r="20" spans="1:23" ht="13.6" customHeight="1">
       <c r="A20" s="42" t="s">
         <v>43</v>
       </c>
@@ -3673,7 +3929,7 @@
       <c r="N20" s="44">
         <v>57.9</v>
       </c>
-      <c r="P20" s="72"/>
+      <c r="P20" s="56"/>
       <c r="Q20" s="55"/>
       <c r="R20" s="55"/>
       <c r="S20" s="54">
@@ -3692,7 +3948,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="13.5" customHeight="1">
+    <row r="21" spans="1:23" ht="13.6" customHeight="1">
       <c r="A21" s="42" t="s">
         <v>44</v>
       </c>
@@ -3732,7 +3988,7 @@
       <c r="N21" s="44">
         <v>71.8</v>
       </c>
-      <c r="P21" s="72"/>
+      <c r="P21" s="56"/>
       <c r="Q21" s="58" t="s">
         <v>20</v>
       </c>
@@ -3755,7 +4011,7 @@
         <v>0.91708753212843208</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="13.5" customHeight="1">
+    <row r="22" spans="1:23" ht="13.6" customHeight="1">
       <c r="A22" s="42" t="s">
         <v>45</v>
       </c>
@@ -3795,7 +4051,7 @@
       <c r="N22" s="44">
         <v>78.900000000000006</v>
       </c>
-      <c r="P22" s="72"/>
+      <c r="P22" s="56"/>
       <c r="Q22" s="58" t="s">
         <v>21</v>
       </c>
@@ -3817,7 +4073,7 @@
         <v>0.89077308769235974</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="13.5" customHeight="1">
+    <row r="23" spans="1:23" ht="13.6" customHeight="1">
       <c r="A23" s="42" t="s">
         <v>46</v>
       </c>
@@ -3857,7 +4113,7 @@
       <c r="N23" s="44">
         <v>94.275260000000003</v>
       </c>
-      <c r="P23" s="72"/>
+      <c r="P23" s="56"/>
       <c r="Q23" s="58" t="s">
         <v>22</v>
       </c>
@@ -3879,7 +4135,7 @@
         <v>0.89227362842892766</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="13.5" customHeight="1">
+    <row r="24" spans="1:23" ht="13.6" customHeight="1">
       <c r="A24" s="42" t="s">
         <v>47</v>
       </c>
@@ -3919,7 +4175,7 @@
       <c r="N24" s="44">
         <v>116.386674</v>
       </c>
-      <c r="P24" s="72"/>
+      <c r="P24" s="56"/>
       <c r="Q24" s="58" t="s">
         <v>80</v>
       </c>
@@ -3941,7 +4197,7 @@
         <v>0.90015377912192118</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="13.5" customHeight="1">
+    <row r="25" spans="1:23" ht="13.6" customHeight="1">
       <c r="A25" s="42">
         <v>2008</v>
       </c>
@@ -3981,16 +4237,16 @@
       <c r="N25" s="44">
         <v>119.602272</v>
       </c>
-      <c r="Q25" s="56" t="s">
+      <c r="Q25" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="R25" s="56"/>
-      <c r="S25" s="56"/>
-      <c r="T25" s="56"/>
-      <c r="U25" s="56"/>
-      <c r="V25" s="56"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
     </row>
-    <row r="26" spans="1:23" ht="13.5" customHeight="1">
+    <row r="26" spans="1:23" ht="13.6" customHeight="1">
       <c r="A26" s="42">
         <v>2009</v>
       </c>
@@ -4043,7 +4299,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="13.5" customHeight="1">
+    <row r="27" spans="1:23" ht="13.6" customHeight="1">
       <c r="A27" s="42">
         <v>2010</v>
       </c>
@@ -4101,7 +4357,7 @@
         <v>1.1909664551163859</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="13.5" customHeight="1">
+    <row r="28" spans="1:23" ht="13.6" customHeight="1">
       <c r="A28" s="42">
         <v>2011</v>
       </c>
@@ -4158,7 +4414,7 @@
         <v>1.1579848729944922</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="13.5" customHeight="1">
+    <row r="29" spans="1:23" ht="13.6" customHeight="1">
       <c r="A29" s="42">
         <v>2012</v>
       </c>
@@ -4215,7 +4471,7 @@
         <v>1.1639053398207673</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="13.5" customHeight="1">
+    <row r="30" spans="1:23" ht="13.6" customHeight="1">
       <c r="A30" s="42">
         <v>2013</v>
       </c>
@@ -4272,7 +4528,7 @@
         <v>0.96542553191489366</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="13.5" customHeight="1">
+    <row r="31" spans="1:23" ht="13.6" customHeight="1">
       <c r="A31" s="42">
         <v>2014</v>
       </c>
@@ -4313,7 +4569,7 @@
         <v>187.771491</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="13.5" customHeight="1">
+    <row r="32" spans="1:23" ht="13.6" customHeight="1">
       <c r="A32" s="42">
         <v>2015</v>
       </c>
@@ -4354,7 +4610,7 @@
         <v>208.06829999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="13.5" customHeight="1">
+    <row r="33" spans="1:14" ht="13.6" customHeight="1">
       <c r="A33" s="42">
         <v>2016</v>
       </c>
@@ -4395,7 +4651,7 @@
         <v>222.44933700000001</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="13.5" customHeight="1">
+    <row r="34" spans="1:14" ht="13.6" customHeight="1">
       <c r="A34" s="42">
         <v>2017</v>
       </c>
@@ -4436,7 +4692,7 @@
         <v>243.55229499999999</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="13.5" customHeight="1">
+    <row r="35" spans="1:14" ht="13.6" customHeight="1">
       <c r="A35" s="42">
         <v>2018</v>
       </c>
@@ -4478,7 +4734,7 @@
         <v>262.49910699999998</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="13.5" customHeight="1">
+    <row r="36" spans="1:14" ht="13.6" customHeight="1">
       <c r="A36" s="45">
         <v>2019</v>
       </c>
@@ -4522,7 +4778,7 @@
         <v>263.2</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="13.5" customHeight="1">
+    <row r="37" spans="1:14" ht="13.6" customHeight="1">
       <c r="A37" s="45">
         <v>2020</v>
       </c>
@@ -4566,7 +4822,7 @@
         <v>240.2</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="13.5" customHeight="1">
+    <row r="38" spans="1:14" ht="13.6" customHeight="1">
       <c r="A38" s="45">
         <v>2021</v>
       </c>
@@ -4610,7 +4866,7 @@
         <v>278.16000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="13.5" customHeight="1">
+    <row r="39" spans="1:14" ht="13.6" customHeight="1">
       <c r="A39" s="45">
         <v>2022</v>
       </c>
@@ -4651,7 +4907,7 @@
         <v>254.1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="13.5" customHeight="1">
+    <row r="40" spans="1:14" ht="13.6" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -4666,7 +4922,7 @@
       <c r="M40" s="52"/>
       <c r="N40" s="49"/>
     </row>
-    <row r="41" spans="1:14" ht="13.5" customHeight="1">
+    <row r="41" spans="1:14" ht="13.6" customHeight="1">
       <c r="A41" s="4"/>
       <c r="C41" s="4"/>
       <c r="E41" s="4"/>
@@ -4675,7 +4931,7 @@
       <c r="J41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:14" ht="13.5" customHeight="1">
+    <row r="42" spans="1:14" ht="13.6" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" t="s">
         <v>64</v>
@@ -4687,7 +4943,7 @@
       <c r="J42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:14" ht="13.5" customHeight="1">
+    <row r="43" spans="1:14" ht="13.6" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
         <v>68</v>
@@ -4711,7 +4967,7 @@
       <c r="J43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:14" ht="13.5" customHeight="1">
+    <row r="44" spans="1:14" ht="13.6" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" t="s">
         <v>66</v>
@@ -4735,7 +4991,7 @@
       <c r="J44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:14" ht="13.5" customHeight="1">
+    <row r="45" spans="1:14" ht="13.6" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
         <v>52</v>
@@ -4759,7 +5015,7 @@
       <c r="J45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:14" ht="13.5" customHeight="1">
+    <row r="46" spans="1:14" ht="13.6" customHeight="1">
       <c r="A46" s="4"/>
       <c r="C46" s="4"/>
       <c r="E46" s="4"/>
@@ -4768,7 +5024,7 @@
       <c r="J46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:14" ht="13.5" customHeight="1">
+    <row r="47" spans="1:14" ht="13.6" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" t="s">
         <v>72</v>
@@ -4782,7 +5038,7 @@
       <c r="J47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:14" ht="13.5" customHeight="1">
+    <row r="48" spans="1:14" ht="13.6" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
         <v>66</v>
@@ -4800,7 +5056,7 @@
       </c>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="2:6" ht="13.5" customHeight="1">
+    <row r="49" spans="2:6" ht="13.6" customHeight="1">
       <c r="B49" t="s">
         <v>52</v>
       </c>
@@ -4816,7 +5072,7 @@
         <v>89979679.590000004</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="13.5" customHeight="1">
+    <row r="51" spans="2:6" ht="13.6" customHeight="1">
       <c r="B51" t="s">
         <v>74</v>
       </c>
@@ -4824,7 +5080,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="13.5" customHeight="1">
+    <row r="52" spans="2:6" ht="13.6" customHeight="1">
       <c r="B52" t="s">
         <v>66</v>
       </c>
@@ -4840,7 +5096,7 @@
         <v>0.21888727151535026</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="13.5" customHeight="1">
+    <row r="53" spans="2:6" ht="13.6" customHeight="1">
       <c r="B53" t="s">
         <v>52</v>
       </c>
@@ -4858,16 +5114,17 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
@@ -4879,17 +5136,16 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
   </mergeCells>
   <phoneticPr fontId="44" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4899,18 +5155,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D031EB3F-D67A-42BA-A5A6-940E289A7F13}">
-  <dimension ref="A1:BY25"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:BY44"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" ht="14.25">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:77" ht="14.3">
+      <c r="A1" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="65"/>
+      <c r="B1" s="66"/>
       <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
@@ -5137,11 +5395,11 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:77" ht="14.25">
-      <c r="A2" s="62" t="s">
+    <row r="2" spans="1:77" ht="14.3">
+      <c r="A2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="63"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="11"/>
       <c r="D2" s="12">
         <v>1743.1</v>
@@ -5252,11 +5510,11 @@
         <v>78471.41700403922</v>
       </c>
     </row>
-    <row r="3" spans="1:77" ht="14.25">
-      <c r="A3" s="62" t="s">
+    <row r="3" spans="1:77" ht="14.3">
+      <c r="A3" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="63"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9">
         <v>1093.22</v>
@@ -5517,11 +5775,11 @@
         <v>19742.90167709309</v>
       </c>
     </row>
-    <row r="4" spans="1:77" ht="14.25">
-      <c r="A4" s="62" t="s">
+    <row r="4" spans="1:77" ht="14.3">
+      <c r="A4" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="63"/>
+      <c r="B4" s="64"/>
       <c r="C4" s="7"/>
       <c r="D4" s="9">
         <v>521.29999999999995</v>
@@ -5782,11 +6040,11 @@
         <v>45026.835046247543</v>
       </c>
     </row>
-    <row r="5" spans="1:77" ht="14.25">
-      <c r="A5" s="62" t="s">
+    <row r="5" spans="1:77" ht="14.3">
+      <c r="A5" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="63"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="7"/>
       <c r="D5" s="9">
         <v>100.63</v>
@@ -6047,7 +6305,7 @@
         <v>40.119413400301283</v>
       </c>
     </row>
-    <row r="6" spans="1:77" ht="14.25">
+    <row r="6" spans="1:77" ht="14.3">
       <c r="A6" s="24" t="s">
         <v>23</v>
       </c>
@@ -9140,6 +9398,2450 @@
       <c r="BY25">
         <f t="shared" si="31"/>
         <v>0.51286713223443736</v>
+      </c>
+    </row>
+    <row r="28" spans="3:77">
+      <c r="E28">
+        <v>2019</v>
+      </c>
+      <c r="F28">
+        <v>2020</v>
+      </c>
+      <c r="G28">
+        <v>2021</v>
+      </c>
+      <c r="H28">
+        <v>2022</v>
+      </c>
+      <c r="I28">
+        <v>2023</v>
+      </c>
+      <c r="J28">
+        <v>2024</v>
+      </c>
+      <c r="K28">
+        <v>2025</v>
+      </c>
+      <c r="L28">
+        <v>2026</v>
+      </c>
+      <c r="M28">
+        <v>2027</v>
+      </c>
+      <c r="N28">
+        <v>2028</v>
+      </c>
+      <c r="O28">
+        <v>2029</v>
+      </c>
+      <c r="P28">
+        <v>2030</v>
+      </c>
+      <c r="Q28">
+        <v>2031</v>
+      </c>
+      <c r="R28">
+        <v>2032</v>
+      </c>
+      <c r="S28">
+        <v>2033</v>
+      </c>
+      <c r="T28">
+        <v>2034</v>
+      </c>
+      <c r="U28">
+        <v>2035</v>
+      </c>
+      <c r="V28">
+        <v>2036</v>
+      </c>
+      <c r="W28">
+        <v>2037</v>
+      </c>
+      <c r="X28">
+        <v>2038</v>
+      </c>
+      <c r="Y28">
+        <v>2039</v>
+      </c>
+      <c r="Z28">
+        <v>2040</v>
+      </c>
+      <c r="AA28">
+        <v>2041</v>
+      </c>
+      <c r="AB28">
+        <v>2042</v>
+      </c>
+      <c r="AC28">
+        <v>2043</v>
+      </c>
+      <c r="AD28">
+        <v>2044</v>
+      </c>
+      <c r="AE28">
+        <v>2045</v>
+      </c>
+      <c r="AF28">
+        <v>2046</v>
+      </c>
+      <c r="AG28">
+        <v>2047</v>
+      </c>
+      <c r="AH28">
+        <v>2048</v>
+      </c>
+      <c r="AI28">
+        <v>2049</v>
+      </c>
+      <c r="AJ28">
+        <v>2050</v>
+      </c>
+      <c r="AK28">
+        <v>2051</v>
+      </c>
+      <c r="AL28">
+        <v>2052</v>
+      </c>
+      <c r="AM28">
+        <v>2053</v>
+      </c>
+      <c r="AN28">
+        <v>2054</v>
+      </c>
+      <c r="AO28">
+        <v>2055</v>
+      </c>
+      <c r="AP28">
+        <v>2056</v>
+      </c>
+      <c r="AQ28">
+        <v>2057</v>
+      </c>
+      <c r="AR28">
+        <v>2058</v>
+      </c>
+      <c r="AS28">
+        <v>2059</v>
+      </c>
+      <c r="AT28">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="29" spans="3:77">
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29">
+        <v>11705.3</v>
+      </c>
+      <c r="F29">
+        <v>6311.3</v>
+      </c>
+      <c r="G29">
+        <v>6529.7</v>
+      </c>
+      <c r="H29">
+        <v>3913.9</v>
+      </c>
+      <c r="I29">
+        <v>10309</v>
+      </c>
+      <c r="J29">
+        <v>12914.7</v>
+      </c>
+      <c r="K29">
+        <v>14626</v>
+      </c>
+      <c r="L29">
+        <f>($P29/$K29)^(0.2)*K29</f>
+        <v>15498.981006842399</v>
+      </c>
+      <c r="M29">
+        <f t="shared" ref="M29:O29" si="32">($P$29/$K$29)^(0.2)*L29</f>
+        <v>16424.067568061088</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="32"/>
+        <v>17404.369704121087</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="32"/>
+        <v>18443.183063054559</v>
+      </c>
+      <c r="P29">
+        <v>19544</v>
+      </c>
+      <c r="Q29">
+        <f>($U$29/$P$29)^(0.2)*P29</f>
+        <v>20380.638027329063</v>
+      </c>
+      <c r="R29">
+        <f t="shared" ref="R29:T29" si="33">($U$29/$P$29)^(0.2)*Q29</f>
+        <v>21253.090790064034</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="33"/>
+        <v>22162.891442604181</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="33"/>
+        <v>23111.638770502694</v>
+      </c>
+      <c r="U29">
+        <v>24101</v>
+      </c>
+      <c r="V29">
+        <f>($Z$29/$U$29)^(0.2)*U29</f>
+        <v>24179.4871313365</v>
+      </c>
+      <c r="W29">
+        <f t="shared" ref="W29:Y29" si="34">($Z$29/$U$29)^(0.2)*V29</f>
+        <v>24258.229863261582</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="34"/>
+        <v>24337.229028162157</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="34"/>
+        <v>24416.485461135886</v>
+      </c>
+      <c r="Z29">
+        <v>24496</v>
+      </c>
+      <c r="AA29">
+        <f>($AE$29/$Z$29)^(0.2)*Z29</f>
+        <v>24624.250031759726</v>
+      </c>
+      <c r="AB29">
+        <f t="shared" ref="AB29:AD29" si="35">($AE$29/$Z$29)^(0.2)*AA29</f>
+        <v>24753.171522967787</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="35"/>
+        <v>24882.767989083666</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="35"/>
+        <v>25013.042963972217</v>
+      </c>
+      <c r="AE29">
+        <v>25144</v>
+      </c>
+      <c r="AF29">
+        <f>($AJ$29/$AE$29)^(0.2)*AE29</f>
+        <v>24979.665910972242</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" ref="AG29:AI29" si="36">($AJ$29/$AE$29)^(0.2)*AF29</f>
+        <v>24816.405863179636</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="36"/>
+        <v>24654.21283699173</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="36"/>
+        <v>24493.079858656401</v>
+      </c>
+      <c r="AJ29">
+        <v>24333</v>
+      </c>
+      <c r="AK29">
+        <f>($AO$29/$AJ$29)^(0.2)*AJ29</f>
+        <v>23785.073159983513</v>
+      </c>
+      <c r="AL29">
+        <f t="shared" ref="AL29:AN29" si="37">($AO$29/$AJ$29)^(0.2)*AK29</f>
+        <v>23249.484454270667</v>
+      </c>
+      <c r="AM29">
+        <f t="shared" si="37"/>
+        <v>22725.956054605977</v>
+      </c>
+      <c r="AN29">
+        <f t="shared" si="37"/>
+        <v>22214.216388828892</v>
+      </c>
+      <c r="AO29">
+        <v>21714</v>
+      </c>
+      <c r="AP29">
+        <f>($AT$29/$AO$29)^(0.2)*AO29</f>
+        <v>21025.273795259374</v>
+      </c>
+      <c r="AQ29">
+        <f t="shared" ref="AQ29:AS29" si="38">($AT$29/$AO$29)^(0.2)*AP29</f>
+        <v>20358.39265753065</v>
+      </c>
+      <c r="AR29">
+        <f t="shared" si="38"/>
+        <v>19712.66370341623</v>
+      </c>
+      <c r="AS29">
+        <f t="shared" si="38"/>
+        <v>19087.416026443672</v>
+      </c>
+      <c r="AT29">
+        <v>18482</v>
+      </c>
+    </row>
+    <row r="30" spans="3:77">
+      <c r="D30" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="73">
+        <f>E29/$E$29</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="73">
+        <f t="shared" ref="F30:K30" si="39">F29/$E$29</f>
+        <v>0.53918310508914769</v>
+      </c>
+      <c r="G30" s="73">
+        <f t="shared" si="39"/>
+        <v>0.5578413197440476</v>
+      </c>
+      <c r="H30" s="73">
+        <f t="shared" si="39"/>
+        <v>0.33436990081416113</v>
+      </c>
+      <c r="I30" s="73">
+        <f t="shared" si="39"/>
+        <v>0.88071215603188302</v>
+      </c>
+      <c r="J30" s="73">
+        <f t="shared" si="39"/>
+        <v>1.1033207179653663</v>
+      </c>
+      <c r="K30" s="73">
+        <f t="shared" si="39"/>
+        <v>1.2495194484549734</v>
+      </c>
+      <c r="L30" s="73">
+        <f t="shared" ref="L30" si="40">L29/$E$29</f>
+        <v>1.3240994256313294</v>
+      </c>
+      <c r="M30" s="73">
+        <f t="shared" ref="M30" si="41">M29/$E$29</f>
+        <v>1.4031308525250177</v>
+      </c>
+      <c r="N30" s="73">
+        <f t="shared" ref="N30" si="42">N29/$E$29</f>
+        <v>1.4868794224941768</v>
+      </c>
+      <c r="O30" s="73">
+        <f t="shared" ref="O30" si="43">O29/$E$29</f>
+        <v>1.575626687317246</v>
+      </c>
+      <c r="P30" s="73">
+        <f t="shared" ref="P30" si="44">P29/$E$29</f>
+        <v>1.6696710037333518</v>
+      </c>
+      <c r="Q30" s="73">
+        <f t="shared" ref="Q30" si="45">Q29/$E$29</f>
+        <v>1.741146149806418</v>
+      </c>
+      <c r="R30" s="73">
+        <f t="shared" ref="R30" si="46">R29/$E$29</f>
+        <v>1.8156809983566449</v>
+      </c>
+      <c r="S30" s="73">
+        <f t="shared" ref="S30" si="47">S29/$E$29</f>
+        <v>1.8934065288889803</v>
+      </c>
+      <c r="T30" s="73">
+        <f t="shared" ref="T30" si="48">T29/$E$29</f>
+        <v>1.9744593278688025</v>
+      </c>
+      <c r="U30" s="73">
+        <f t="shared" ref="U30" si="49">U29/$E$29</f>
+        <v>2.0589818287442441</v>
+      </c>
+      <c r="V30" s="73">
+        <f t="shared" ref="V30" si="50">V29/$E$29</f>
+        <v>2.065687093140415</v>
+      </c>
+      <c r="W30" s="73">
+        <f t="shared" ref="W30" si="51">W29/$E$29</f>
+        <v>2.0724141938490757</v>
+      </c>
+      <c r="X30" s="73">
+        <f t="shared" ref="X30" si="52">X29/$E$29</f>
+        <v>2.0791632019821926</v>
+      </c>
+      <c r="Y30" s="73">
+        <f t="shared" ref="Y30" si="53">Y29/$E$29</f>
+        <v>2.0859341888833169</v>
+      </c>
+      <c r="Z30" s="73">
+        <f t="shared" ref="Z30" si="54">Z29/$E$29</f>
+        <v>2.0927272261283352</v>
+      </c>
+      <c r="AA30" s="73">
+        <f t="shared" ref="AA30" si="55">AA29/$E$29</f>
+        <v>2.1036838040682193</v>
+      </c>
+      <c r="AB30" s="73">
+        <f t="shared" ref="AB30" si="56">AB29/$E$29</f>
+        <v>2.1146977457192713</v>
+      </c>
+      <c r="AC30" s="73">
+        <f t="shared" ref="AC30" si="57">AC29/$E$29</f>
+        <v>2.125769351412067</v>
+      </c>
+      <c r="AD30" s="73">
+        <f t="shared" ref="AD30" si="58">AD29/$E$29</f>
+        <v>2.1368989230495776</v>
+      </c>
+      <c r="AE30" s="73">
+        <f t="shared" ref="AE30" si="59">AE29/$E$29</f>
+        <v>2.1480867641154009</v>
+      </c>
+      <c r="AF30" s="73">
+        <f t="shared" ref="AF30" si="60">AF29/$E$29</f>
+        <v>2.1340474751584533</v>
+      </c>
+      <c r="AG30" s="73">
+        <f t="shared" ref="AG30" si="61">AG29/$E$29</f>
+        <v>2.1200999430326122</v>
+      </c>
+      <c r="AH30" s="73">
+        <f t="shared" ref="AH30" si="62">AH29/$E$29</f>
+        <v>2.1062435680411209</v>
+      </c>
+      <c r="AI30" s="73">
+        <f t="shared" ref="AI30" si="63">AI29/$E$29</f>
+        <v>2.0924777544066706</v>
+      </c>
+      <c r="AJ30" s="73">
+        <f t="shared" ref="AJ30" si="64">AJ29/$E$29</f>
+        <v>2.0788019102457862</v>
+      </c>
+      <c r="AK30" s="73">
+        <f t="shared" ref="AK30" si="65">AK29/$E$29</f>
+        <v>2.0319917609957465</v>
+      </c>
+      <c r="AL30" s="73">
+        <f t="shared" ref="AL30" si="66">AL29/$E$29</f>
+        <v>1.9862356756572381</v>
+      </c>
+      <c r="AM30" s="73">
+        <f t="shared" ref="AM30" si="67">AM29/$E$29</f>
+        <v>1.9415099189773843</v>
+      </c>
+      <c r="AN30" s="73">
+        <f t="shared" ref="AN30" si="68">AN29/$E$29</f>
+        <v>1.8977912901701703</v>
+      </c>
+      <c r="AO30" s="73">
+        <f t="shared" ref="AO30" si="69">AO29/$E$29</f>
+        <v>1.8550571108813958</v>
+      </c>
+      <c r="AP30" s="73">
+        <f t="shared" ref="AP30" si="70">AP29/$E$29</f>
+        <v>1.7962182767856762</v>
+      </c>
+      <c r="AQ30" s="73">
+        <f t="shared" ref="AQ30" si="71">AQ29/$E$29</f>
+        <v>1.7392456970372951</v>
+      </c>
+      <c r="AR30" s="73">
+        <f t="shared" ref="AR30" si="72">AR29/$E$29</f>
+        <v>1.6840801776474104</v>
+      </c>
+      <c r="AS30" s="73">
+        <f t="shared" ref="AS30" si="73">AS29/$E$29</f>
+        <v>1.6306644021463503</v>
+      </c>
+      <c r="AT30" s="73">
+        <f t="shared" ref="AT30" si="74">AT29/$E$29</f>
+        <v>1.5789428720323273</v>
+      </c>
+    </row>
+    <row r="31" spans="3:77">
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31">
+        <v>14706.6</v>
+      </c>
+      <c r="F31">
+        <v>8266.2000000000007</v>
+      </c>
+      <c r="G31">
+        <v>9567.7999999999993</v>
+      </c>
+      <c r="H31">
+        <v>6577.5</v>
+      </c>
+      <c r="I31">
+        <v>14729.4</v>
+      </c>
+      <c r="J31">
+        <v>15799.1</v>
+      </c>
+      <c r="K31">
+        <v>15603.503430179268</v>
+      </c>
+      <c r="L31">
+        <v>16059.819247424719</v>
+      </c>
+      <c r="M31">
+        <v>16529.479768056823</v>
+      </c>
+      <c r="N31">
+        <v>17012.875250536385</v>
+      </c>
+      <c r="O31">
+        <v>17510.407366216779</v>
+      </c>
+      <c r="P31">
+        <v>18022.489533107691</v>
+      </c>
+      <c r="Q31">
+        <v>18549.547259399558</v>
+      </c>
+      <c r="R31">
+        <v>19092.01849703422</v>
+      </c>
+      <c r="S31">
+        <v>19650.354005615536</v>
+      </c>
+      <c r="T31">
+        <v>20225.017726962367</v>
+      </c>
+      <c r="U31">
+        <v>20816.487170615161</v>
+      </c>
+      <c r="V31">
+        <v>21232.816914027466</v>
+      </c>
+      <c r="W31">
+        <v>21657.473252308017</v>
+      </c>
+      <c r="X31">
+        <v>22090.622717354177</v>
+      </c>
+      <c r="Y31">
+        <v>22532.435171701261</v>
+      </c>
+      <c r="Z31">
+        <v>22983.083875135286</v>
+      </c>
+      <c r="AA31">
+        <v>23442.745552637993</v>
+      </c>
+      <c r="AB31">
+        <v>23911.600463690753</v>
+      </c>
+      <c r="AC31">
+        <v>24389.832472964568</v>
+      </c>
+      <c r="AD31">
+        <v>24877.629122423859</v>
+      </c>
+      <c r="AE31">
+        <v>25375.181704872339</v>
+      </c>
+      <c r="AF31">
+        <v>25628.933521921062</v>
+      </c>
+      <c r="AG31">
+        <v>25885.222857140274</v>
+      </c>
+      <c r="AH31">
+        <v>26144.075085711676</v>
+      </c>
+      <c r="AI31">
+        <v>26405.515836568793</v>
+      </c>
+      <c r="AJ31">
+        <v>26669.570994934482</v>
+      </c>
+      <c r="AK31">
+        <v>26936.266704883827</v>
+      </c>
+      <c r="AL31">
+        <v>27205.629371932664</v>
+      </c>
+      <c r="AM31">
+        <v>27477.685665651992</v>
+      </c>
+      <c r="AN31">
+        <v>27752.462522308513</v>
+      </c>
+      <c r="AO31">
+        <v>27752.462522308513</v>
+      </c>
+      <c r="AP31">
+        <v>27891.224834920053</v>
+      </c>
+      <c r="AQ31">
+        <v>28030.68095909465</v>
+      </c>
+      <c r="AR31">
+        <v>28170.834363890121</v>
+      </c>
+      <c r="AS31">
+        <v>28311.688535709567</v>
+      </c>
+      <c r="AT31">
+        <v>28453.246978388113</v>
+      </c>
+    </row>
+    <row r="32" spans="3:77">
+      <c r="D32" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="73">
+        <f>E31/$E31</f>
+        <v>1</v>
+      </c>
+      <c r="F32" s="73">
+        <f t="shared" ref="F32:J32" si="75">F31/$E$31</f>
+        <v>0.56207417078046595</v>
+      </c>
+      <c r="G32" s="73">
+        <f t="shared" si="75"/>
+        <v>0.65057865176179397</v>
+      </c>
+      <c r="H32" s="73">
+        <f t="shared" si="75"/>
+        <v>0.44724817428909469</v>
+      </c>
+      <c r="I32" s="73">
+        <f t="shared" si="75"/>
+        <v>1.0015503243441719</v>
+      </c>
+      <c r="J32" s="73">
+        <f t="shared" si="75"/>
+        <v>1.0742863748249085</v>
+      </c>
+      <c r="K32" s="73">
+        <f>K31/$E$31</f>
+        <v>1.0609864571130831</v>
+      </c>
+      <c r="L32" s="73">
+        <f t="shared" ref="L32" si="76">L31/$E$31</f>
+        <v>1.092014418521257</v>
+      </c>
+      <c r="M32" s="73">
+        <f t="shared" ref="M32" si="77">M31/$E$31</f>
+        <v>1.1239497754788206</v>
+      </c>
+      <c r="N32" s="73">
+        <f t="shared" ref="N32" si="78">N31/$E$31</f>
+        <v>1.156819064266138</v>
+      </c>
+      <c r="O32" s="73">
+        <f t="shared" ref="O32" si="79">O31/$E$31</f>
+        <v>1.1906495972023974</v>
+      </c>
+      <c r="P32" s="73">
+        <f t="shared" ref="P32" si="80">P31/$E$31</f>
+        <v>1.2254694853404384</v>
+      </c>
+      <c r="Q32" s="73">
+        <f t="shared" ref="Q32" si="81">Q31/$E$31</f>
+        <v>1.2613076618252728</v>
+      </c>
+      <c r="R32" s="73">
+        <f t="shared" ref="R32" si="82">R31/$E$31</f>
+        <v>1.2981939059357173</v>
+      </c>
+      <c r="S32" s="73">
+        <f t="shared" ref="S32" si="83">S31/$E$31</f>
+        <v>1.3361588678291063</v>
+      </c>
+      <c r="T32" s="73">
+        <f t="shared" ref="T32" si="84">T31/$E$31</f>
+        <v>1.3752340940096532</v>
+      </c>
+      <c r="U32" s="73">
+        <f t="shared" ref="U32" si="85">U31/$E$31</f>
+        <v>1.415452053541618</v>
+      </c>
+      <c r="V32" s="73">
+        <f t="shared" ref="V32" si="86">V31/$E$31</f>
+        <v>1.4437610946124506</v>
+      </c>
+      <c r="W32" s="73">
+        <f t="shared" ref="W32" si="87">W31/$E$31</f>
+        <v>1.4726363165046996</v>
+      </c>
+      <c r="X32" s="73">
+        <f t="shared" ref="X32" si="88">X31/$E$31</f>
+        <v>1.5020890428347937</v>
+      </c>
+      <c r="Y32" s="73">
+        <f t="shared" ref="Y32" si="89">Y31/$E$31</f>
+        <v>1.5321308236914897</v>
+      </c>
+      <c r="Z32" s="73">
+        <f t="shared" ref="Z32" si="90">Z31/$E$31</f>
+        <v>1.5627734401653193</v>
+      </c>
+      <c r="AA32" s="73">
+        <f t="shared" ref="AA32" si="91">AA31/$E$31</f>
+        <v>1.5940289089686257</v>
+      </c>
+      <c r="AB32" s="73">
+        <f t="shared" ref="AB32" si="92">AB31/$E$31</f>
+        <v>1.6259094871479984</v>
+      </c>
+      <c r="AC32" s="73">
+        <f t="shared" ref="AC32" si="93">AC31/$E$31</f>
+        <v>1.6584276768909583</v>
+      </c>
+      <c r="AD32" s="73">
+        <f t="shared" ref="AD32" si="94">AD31/$E$31</f>
+        <v>1.6915962304287775</v>
+      </c>
+      <c r="AE32" s="73">
+        <f t="shared" ref="AE32" si="95">AE31/$E$31</f>
+        <v>1.7254281550373531</v>
+      </c>
+      <c r="AF32" s="73">
+        <f t="shared" ref="AF32" si="96">AF31/$E$31</f>
+        <v>1.7426824365877267</v>
+      </c>
+      <c r="AG32" s="73">
+        <f t="shared" ref="AG32" si="97">AG31/$E$31</f>
+        <v>1.760109260953604</v>
+      </c>
+      <c r="AH32" s="73">
+        <f t="shared" ref="AH32" si="98">AH31/$E$31</f>
+        <v>1.77771035356314</v>
+      </c>
+      <c r="AI32" s="73">
+        <f t="shared" ref="AI32" si="99">AI31/$E$31</f>
+        <v>1.7954874570987716</v>
+      </c>
+      <c r="AJ32" s="73">
+        <f t="shared" ref="AJ32" si="100">AJ31/$E$31</f>
+        <v>1.8134423316697592</v>
+      </c>
+      <c r="AK32" s="73">
+        <f t="shared" ref="AK32" si="101">AK31/$E$31</f>
+        <v>1.8315767549864568</v>
+      </c>
+      <c r="AL32" s="73">
+        <f t="shared" ref="AL32" si="102">AL31/$E$31</f>
+        <v>1.8498925225363214</v>
+      </c>
+      <c r="AM32" s="73">
+        <f t="shared" ref="AM32" si="103">AM31/$E$31</f>
+        <v>1.8683914477616848</v>
+      </c>
+      <c r="AN32" s="73">
+        <f t="shared" ref="AN32" si="104">AN31/$E$31</f>
+        <v>1.8870753622393015</v>
+      </c>
+      <c r="AO32" s="73">
+        <f t="shared" ref="AO32" si="105">AO31/$E$31</f>
+        <v>1.8870753622393015</v>
+      </c>
+      <c r="AP32" s="73">
+        <f t="shared" ref="AP32" si="106">AP31/$E$31</f>
+        <v>1.8965107390504978</v>
+      </c>
+      <c r="AQ32" s="73">
+        <f t="shared" ref="AQ32" si="107">AQ31/$E$31</f>
+        <v>1.9059932927457501</v>
+      </c>
+      <c r="AR32" s="73">
+        <f t="shared" ref="AR32" si="108">AR31/$E$31</f>
+        <v>1.9155232592094786</v>
+      </c>
+      <c r="AS32" s="73">
+        <f t="shared" ref="AS32" si="109">AS31/$E$31</f>
+        <v>1.9251008755055259</v>
+      </c>
+      <c r="AT32" s="73">
+        <f t="shared" ref="AT32" si="110">AT31/$E$31</f>
+        <v>1.9347263798830534</v>
+      </c>
+    </row>
+    <row r="33" spans="3:46">
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33">
+        <v>80.2</v>
+      </c>
+      <c r="F33">
+        <v>33</v>
+      </c>
+      <c r="G33">
+        <v>33.1</v>
+      </c>
+      <c r="H33">
+        <v>22.6</v>
+      </c>
+      <c r="I33">
+        <v>53.8</v>
+      </c>
+      <c r="J33">
+        <v>54.7</v>
+      </c>
+      <c r="K33">
+        <v>55.973520000000001</v>
+      </c>
+      <c r="L33">
+        <v>57.092990400000005</v>
+      </c>
+      <c r="M33">
+        <v>58.234850208000005</v>
+      </c>
+      <c r="N33">
+        <v>59.399547212160009</v>
+      </c>
+      <c r="O33">
+        <v>60.587538156403212</v>
+      </c>
+      <c r="P33">
+        <v>61.799288919531278</v>
+      </c>
+      <c r="Q33">
+        <v>63.035274697921906</v>
+      </c>
+      <c r="R33">
+        <v>64.295980191880346</v>
+      </c>
+      <c r="S33">
+        <v>65.581899795717959</v>
+      </c>
+      <c r="T33">
+        <v>66.893537791632326</v>
+      </c>
+      <c r="U33">
+        <v>68.23140854746498</v>
+      </c>
+      <c r="V33">
+        <v>68.572565590202302</v>
+      </c>
+      <c r="W33">
+        <v>68.915428418153311</v>
+      </c>
+      <c r="X33">
+        <v>69.260005560244068</v>
+      </c>
+      <c r="Y33">
+        <v>69.606305588045274</v>
+      </c>
+      <c r="Z33">
+        <v>69.954337115985496</v>
+      </c>
+      <c r="AA33">
+        <v>70.30410880156542</v>
+      </c>
+      <c r="AB33">
+        <v>70.655629345573246</v>
+      </c>
+      <c r="AC33">
+        <v>71.008907492301105</v>
+      </c>
+      <c r="AD33">
+        <v>71.363952029762601</v>
+      </c>
+      <c r="AE33">
+        <v>71.72077178991141</v>
+      </c>
+      <c r="AF33">
+        <v>71.864213333491236</v>
+      </c>
+      <c r="AG33">
+        <v>72.007941760158218</v>
+      </c>
+      <c r="AH33">
+        <v>72.151957643678529</v>
+      </c>
+      <c r="AI33">
+        <v>72.296261558965881</v>
+      </c>
+      <c r="AJ33">
+        <v>72.440854082083817</v>
+      </c>
+      <c r="AK33">
+        <v>72.585735790247981</v>
+      </c>
+      <c r="AL33">
+        <v>72.730907261828477</v>
+      </c>
+      <c r="AM33">
+        <v>72.876369076352134</v>
+      </c>
+      <c r="AN33">
+        <v>73.022121814504843</v>
+      </c>
+      <c r="AO33">
+        <v>73.022121814504843</v>
+      </c>
+      <c r="AP33">
+        <v>73.168166058133849</v>
+      </c>
+      <c r="AQ33">
+        <v>73.314502390250112</v>
+      </c>
+      <c r="AR33">
+        <v>73.46113139503062</v>
+      </c>
+      <c r="AS33">
+        <v>73.608053657820676</v>
+      </c>
+      <c r="AT33">
+        <v>73.755269765136319</v>
+      </c>
+    </row>
+    <row r="34" spans="3:46">
+      <c r="D34" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="73">
+        <f>E33/$E33</f>
+        <v>1</v>
+      </c>
+      <c r="F34" s="73">
+        <f t="shared" ref="F34:J34" si="111">F33/$E33</f>
+        <v>0.41147132169576056</v>
+      </c>
+      <c r="G34" s="73">
+        <f t="shared" si="111"/>
+        <v>0.41271820448877805</v>
+      </c>
+      <c r="H34" s="73">
+        <f t="shared" si="111"/>
+        <v>0.28179551122194513</v>
+      </c>
+      <c r="I34" s="73">
+        <f t="shared" si="111"/>
+        <v>0.67082294264339148</v>
+      </c>
+      <c r="J34" s="73">
+        <f t="shared" si="111"/>
+        <v>0.68204488778054861</v>
+      </c>
+      <c r="K34" s="73">
+        <f t="shared" ref="K34" si="112">K33/$E33</f>
+        <v>0.69792418952618451</v>
+      </c>
+      <c r="L34" s="73">
+        <f t="shared" ref="L34" si="113">L33/$E33</f>
+        <v>0.71188267331670829</v>
+      </c>
+      <c r="M34" s="73">
+        <f t="shared" ref="M34" si="114">M33/$E33</f>
+        <v>0.72612032678304239</v>
+      </c>
+      <c r="N34" s="73">
+        <f t="shared" ref="N34" si="115">N33/$E33</f>
+        <v>0.74064273331870334</v>
+      </c>
+      <c r="O34" s="73">
+        <f t="shared" ref="O34" si="116">O33/$E33</f>
+        <v>0.75545558798507739</v>
+      </c>
+      <c r="P34" s="73">
+        <f t="shared" ref="P34" si="117">P33/$E33</f>
+        <v>0.77056469974477904</v>
+      </c>
+      <c r="Q34" s="73">
+        <f t="shared" ref="Q34" si="118">Q33/$E33</f>
+        <v>0.78597599373967464</v>
+      </c>
+      <c r="R34" s="73">
+        <f t="shared" ref="R34" si="119">R33/$E33</f>
+        <v>0.80169551361446811</v>
+      </c>
+      <c r="S34" s="73">
+        <f t="shared" ref="S34" si="120">S33/$E33</f>
+        <v>0.81772942388675751</v>
+      </c>
+      <c r="T34" s="73">
+        <f t="shared" ref="T34" si="121">T33/$E33</f>
+        <v>0.83408401236449281</v>
+      </c>
+      <c r="U34" s="73">
+        <f t="shared" ref="U34" si="122">U33/$E33</f>
+        <v>0.85076569261178281</v>
+      </c>
+      <c r="V34" s="73">
+        <f t="shared" ref="V34" si="123">V33/$E33</f>
+        <v>0.85501952107484169</v>
+      </c>
+      <c r="W34" s="73">
+        <f t="shared" ref="W34" si="124">W33/$E33</f>
+        <v>0.85929461868021584</v>
+      </c>
+      <c r="X34" s="73">
+        <f t="shared" ref="X34" si="125">X33/$E33</f>
+        <v>0.86359109177361681</v>
+      </c>
+      <c r="Y34" s="73">
+        <f t="shared" ref="Y34" si="126">Y33/$E33</f>
+        <v>0.86790904723248463</v>
+      </c>
+      <c r="Z34" s="73">
+        <f t="shared" ref="Z34" si="127">Z33/$E33</f>
+        <v>0.87224859246864705</v>
+      </c>
+      <c r="AA34" s="73">
+        <f t="shared" ref="AA34" si="128">AA33/$E33</f>
+        <v>0.87660983543099025</v>
+      </c>
+      <c r="AB34" s="73">
+        <f t="shared" ref="AB34" si="129">AB33/$E33</f>
+        <v>0.88099288460814518</v>
+      </c>
+      <c r="AC34" s="73">
+        <f t="shared" ref="AC34" si="130">AC33/$E33</f>
+        <v>0.88539784903118579</v>
+      </c>
+      <c r="AD34" s="73">
+        <f t="shared" ref="AD34" si="131">AD33/$E33</f>
+        <v>0.88982483827634162</v>
+      </c>
+      <c r="AE34" s="73">
+        <f t="shared" ref="AE34" si="132">AE33/$E33</f>
+        <v>0.89427396246772328</v>
+      </c>
+      <c r="AF34" s="73">
+        <f t="shared" ref="AF34" si="133">AF33/$E33</f>
+        <v>0.89606251039265872</v>
+      </c>
+      <c r="AG34" s="73">
+        <f t="shared" ref="AG34" si="134">AG33/$E33</f>
+        <v>0.89785463541344412</v>
+      </c>
+      <c r="AH34" s="73">
+        <f t="shared" ref="AH34" si="135">AH33/$E33</f>
+        <v>0.89965034468427085</v>
+      </c>
+      <c r="AI34" s="73">
+        <f t="shared" ref="AI34" si="136">AI33/$E33</f>
+        <v>0.90144964537363936</v>
+      </c>
+      <c r="AJ34" s="73">
+        <f t="shared" ref="AJ34" si="137">AJ33/$E33</f>
+        <v>0.90325254466438676</v>
+      </c>
+      <c r="AK34" s="73">
+        <f t="shared" ref="AK34" si="138">AK33/$E33</f>
+        <v>0.90505904975371543</v>
+      </c>
+      <c r="AL34" s="73">
+        <f t="shared" ref="AL34" si="139">AL33/$E33</f>
+        <v>0.90686916785322291</v>
+      </c>
+      <c r="AM34" s="73">
+        <f t="shared" ref="AM34" si="140">AM33/$E33</f>
+        <v>0.90868290618892933</v>
+      </c>
+      <c r="AN34" s="73">
+        <f t="shared" ref="AN34" si="141">AN33/$E33</f>
+        <v>0.91050027200130723</v>
+      </c>
+      <c r="AO34" s="73">
+        <f t="shared" ref="AO34" si="142">AO33/$E33</f>
+        <v>0.91050027200130723</v>
+      </c>
+      <c r="AP34" s="73">
+        <f t="shared" ref="AP34" si="143">AP33/$E33</f>
+        <v>0.91232127254530981</v>
+      </c>
+      <c r="AQ34" s="73">
+        <f t="shared" ref="AQ34" si="144">AQ33/$E33</f>
+        <v>0.91414591509040033</v>
+      </c>
+      <c r="AR34" s="73">
+        <f t="shared" ref="AR34" si="145">AR33/$E33</f>
+        <v>0.91597420692058129</v>
+      </c>
+      <c r="AS34" s="73">
+        <f t="shared" ref="AS34" si="146">AS33/$E33</f>
+        <v>0.91780615533442234</v>
+      </c>
+      <c r="AT34" s="73">
+        <f t="shared" ref="AT34" si="147">AT33/$E33</f>
+        <v>0.9196417676450912</v>
+      </c>
+    </row>
+    <row r="35" spans="3:46" s="81" customFormat="1">
+      <c r="C35" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="81">
+        <f>E41+E42</f>
+        <v>40404.152501724369</v>
+      </c>
+      <c r="F35" s="81">
+        <f t="shared" ref="F35:O35" si="148">F41+F42</f>
+        <v>37647.358320109633</v>
+      </c>
+      <c r="G35" s="81">
+        <f t="shared" si="148"/>
+        <v>39816.103110580858</v>
+      </c>
+      <c r="H35" s="81">
+        <f t="shared" si="148"/>
+        <v>38580.837164949124</v>
+      </c>
+      <c r="I35" s="81">
+        <f t="shared" si="148"/>
+        <v>37514.213096250001</v>
+      </c>
+      <c r="J35" s="81">
+        <f t="shared" si="148"/>
+        <v>37015.327399328584</v>
+      </c>
+      <c r="K35" s="81">
+        <f t="shared" si="148"/>
+        <v>38945.826080989827</v>
+      </c>
+      <c r="L35" s="81">
+        <f t="shared" si="148"/>
+        <v>40714.742013766692</v>
+      </c>
+      <c r="M35" s="81">
+        <f t="shared" si="148"/>
+        <v>42064.826527197823</v>
+      </c>
+      <c r="N35" s="81">
+        <f t="shared" si="148"/>
+        <v>43127.57517350679</v>
+      </c>
+      <c r="O35" s="81">
+        <f t="shared" si="148"/>
+        <v>43982.299598038211</v>
+      </c>
+      <c r="P35" s="81">
+        <f t="shared" ref="P35:AP35" si="149">P41+P42</f>
+        <v>44726.149946288126</v>
+      </c>
+      <c r="Q35" s="81">
+        <f t="shared" si="149"/>
+        <v>45343.781535297574</v>
+      </c>
+      <c r="R35" s="81">
+        <f t="shared" si="149"/>
+        <v>45902.018979910885</v>
+      </c>
+      <c r="S35" s="81">
+        <f t="shared" si="149"/>
+        <v>46372.122266823113</v>
+      </c>
+      <c r="T35" s="81">
+        <f t="shared" si="149"/>
+        <v>46754.478376104664</v>
+      </c>
+      <c r="U35" s="81">
+        <f t="shared" si="149"/>
+        <v>47034.894997192525</v>
+      </c>
+      <c r="V35" s="81">
+        <f t="shared" si="149"/>
+        <v>47255.584808148706</v>
+      </c>
+      <c r="W35" s="81">
+        <f t="shared" si="149"/>
+        <v>47390.819739572122</v>
+      </c>
+      <c r="X35" s="81">
+        <f t="shared" si="149"/>
+        <v>47452.39710058221</v>
+      </c>
+      <c r="Y35" s="81">
+        <f t="shared" si="149"/>
+        <v>47446.810391801555</v>
+      </c>
+      <c r="Z35" s="81">
+        <f t="shared" si="149"/>
+        <v>47379.722838498863</v>
+      </c>
+      <c r="AA35" s="81">
+        <f t="shared" si="149"/>
+        <v>47260.872531611429</v>
+      </c>
+      <c r="AB35" s="81">
+        <f t="shared" si="149"/>
+        <v>47089.335408015497</v>
+      </c>
+      <c r="AC35" s="81">
+        <f t="shared" si="149"/>
+        <v>46869.683008907472</v>
+      </c>
+      <c r="AD35" s="81">
+        <f t="shared" si="149"/>
+        <v>46606.582742589482</v>
+      </c>
+      <c r="AE35" s="81">
+        <f t="shared" si="149"/>
+        <v>46303.661195475586</v>
+      </c>
+      <c r="AF35" s="81">
+        <f t="shared" si="149"/>
+        <v>45966.789291628986</v>
+      </c>
+      <c r="AG35" s="81">
+        <f t="shared" si="149"/>
+        <v>45596.470469612585</v>
+      </c>
+      <c r="AH35" s="81">
+        <f t="shared" si="149"/>
+        <v>45196.028947519459</v>
+      </c>
+      <c r="AI35" s="81">
+        <f t="shared" si="149"/>
+        <v>44769.525627499424</v>
+      </c>
+      <c r="AJ35" s="81">
+        <f t="shared" si="149"/>
+        <v>44320.156820994103</v>
+      </c>
+      <c r="AK35" s="81">
+        <f t="shared" si="149"/>
+        <v>43858.102802805799</v>
+      </c>
+      <c r="AL35" s="81">
+        <f t="shared" si="149"/>
+        <v>43370.869247706942</v>
+      </c>
+      <c r="AM35" s="81">
+        <f t="shared" si="149"/>
+        <v>42858.864539594484</v>
+      </c>
+      <c r="AN35" s="81">
+        <f t="shared" si="149"/>
+        <v>42322.193625002896</v>
+      </c>
+      <c r="AO35" s="81">
+        <f t="shared" si="149"/>
+        <v>41760.707547394813</v>
+      </c>
+      <c r="AP35" s="81">
+        <f t="shared" si="149"/>
+        <v>41173.903256058285</v>
+      </c>
+      <c r="AQ35" s="81">
+        <f>AQ41+AQ42</f>
+        <v>40561.26036433519</v>
+      </c>
+      <c r="AR35" s="81">
+        <f t="shared" ref="AR35:AT35" si="150">AR41+AR42</f>
+        <v>39922.126435311853</v>
+      </c>
+      <c r="AS35" s="81">
+        <f t="shared" si="150"/>
+        <v>39255.711187499692</v>
+      </c>
+      <c r="AT35" s="81">
+        <f t="shared" si="150"/>
+        <v>38561.535692607569</v>
+      </c>
+    </row>
+    <row r="36" spans="3:46">
+      <c r="D36" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="73">
+        <f>E35/$E35</f>
+        <v>1</v>
+      </c>
+      <c r="F36" s="73">
+        <f t="shared" ref="F36:O36" si="151">F35/$E35</f>
+        <v>0.93176953330484824</v>
+      </c>
+      <c r="G36" s="73">
+        <f t="shared" si="151"/>
+        <v>0.98544581794857811</v>
+      </c>
+      <c r="H36" s="73">
+        <f t="shared" si="151"/>
+        <v>0.95487307061576332</v>
+      </c>
+      <c r="I36" s="73">
+        <f t="shared" si="151"/>
+        <v>0.92847419815695842</v>
+      </c>
+      <c r="J36" s="73">
+        <f t="shared" si="151"/>
+        <v>0.91612681141496144</v>
+      </c>
+      <c r="K36" s="73">
+        <f t="shared" si="151"/>
+        <v>0.9639065212252057</v>
+      </c>
+      <c r="L36" s="73">
+        <f t="shared" si="151"/>
+        <v>1.007687069095907</v>
+      </c>
+      <c r="M36" s="73">
+        <f t="shared" si="151"/>
+        <v>1.0411015680975508</v>
+      </c>
+      <c r="N36" s="73">
+        <f t="shared" si="151"/>
+        <v>1.0674045241183117</v>
+      </c>
+      <c r="O36" s="73">
+        <f t="shared" si="151"/>
+        <v>1.0885588949344038</v>
+      </c>
+      <c r="P36" s="73">
+        <f t="shared" ref="P36" si="152">P35/$E35</f>
+        <v>1.1069691399758801</v>
+      </c>
+      <c r="Q36" s="73">
+        <f t="shared" ref="Q36" si="153">Q35/$E35</f>
+        <v>1.1222554793931736</v>
+      </c>
+      <c r="R36" s="73">
+        <f t="shared" ref="R36" si="154">R35/$E35</f>
+        <v>1.1360718178150595</v>
+      </c>
+      <c r="S36" s="73">
+        <f t="shared" ref="S36" si="155">S35/$E35</f>
+        <v>1.1477068418857206</v>
+      </c>
+      <c r="T36" s="73">
+        <f t="shared" ref="T36" si="156">T35/$E35</f>
+        <v>1.1571701293353269</v>
+      </c>
+      <c r="U36" s="73">
+        <f t="shared" ref="U36" si="157">U35/$E35</f>
+        <v>1.1641104214519824</v>
+      </c>
+      <c r="V36" s="73">
+        <f t="shared" ref="V36" si="158">V35/$E35</f>
+        <v>1.1695724791191184</v>
+      </c>
+      <c r="W36" s="73">
+        <f t="shared" ref="W36" si="159">W35/$E35</f>
+        <v>1.1729195343857188</v>
+      </c>
+      <c r="X36" s="73">
+        <f t="shared" ref="X36:Y36" si="160">X35/$E35</f>
+        <v>1.1744435698424076</v>
+      </c>
+      <c r="Y36" s="73">
+        <f t="shared" si="160"/>
+        <v>1.1743052991837069</v>
+      </c>
+      <c r="Z36" s="73">
+        <f t="shared" ref="Z36" si="161">Z35/$E35</f>
+        <v>1.1726448868461425</v>
+      </c>
+      <c r="AA36" s="73">
+        <f t="shared" ref="AA36" si="162">AA35/$E35</f>
+        <v>1.1697033499117306</v>
+      </c>
+      <c r="AB36" s="73">
+        <f t="shared" ref="AB36" si="163">AB35/$E35</f>
+        <v>1.1654578178816104</v>
+      </c>
+      <c r="AC36" s="73">
+        <f t="shared" ref="AC36" si="164">AC35/$E35</f>
+        <v>1.1600214360864807</v>
+      </c>
+      <c r="AD36" s="73">
+        <f t="shared" ref="AD36" si="165">AD35/$E35</f>
+        <v>1.1535097225613236</v>
+      </c>
+      <c r="AE36" s="73">
+        <f t="shared" ref="AE36" si="166">AE35/$E35</f>
+        <v>1.1460124350708616</v>
+      </c>
+      <c r="AF36" s="73">
+        <f t="shared" ref="AF36" si="167">AF35/$E35</f>
+        <v>1.1376748785825224</v>
+      </c>
+      <c r="AG36" s="73">
+        <f t="shared" ref="AG36" si="168">AG35/$E35</f>
+        <v>1.1285095131661682</v>
+      </c>
+      <c r="AH36" s="73">
+        <f t="shared" ref="AH36:AI36" si="169">AH35/$E35</f>
+        <v>1.1185986129913399</v>
+      </c>
+      <c r="AI36" s="73">
+        <f t="shared" si="169"/>
+        <v>1.108042685107397</v>
+      </c>
+      <c r="AJ36" s="73">
+        <f t="shared" ref="AJ36" si="170">AJ35/$E35</f>
+        <v>1.0969208380030395</v>
+      </c>
+      <c r="AK36" s="73">
+        <f t="shared" ref="AK36" si="171">AK35/$E35</f>
+        <v>1.0854850327805792</v>
+      </c>
+      <c r="AL36" s="73">
+        <f t="shared" ref="AL36" si="172">AL35/$E35</f>
+        <v>1.073426035748577</v>
+      </c>
+      <c r="AM36" s="73">
+        <f t="shared" ref="AM36" si="173">AM35/$E35</f>
+        <v>1.0607539543804403</v>
+      </c>
+      <c r="AN36" s="73">
+        <f t="shared" ref="AN36" si="174">AN35/$E35</f>
+        <v>1.0474713860956908</v>
+      </c>
+      <c r="AO36" s="73">
+        <f t="shared" ref="AO36" si="175">AO35/$E35</f>
+        <v>1.0335746442302569</v>
+      </c>
+      <c r="AP36" s="73">
+        <f t="shared" ref="AP36" si="176">AP35/$E35</f>
+        <v>1.019051278313561</v>
+      </c>
+      <c r="AQ36" s="73">
+        <f>AQ35/$E35</f>
+        <v>1.0038884088115476</v>
+      </c>
+      <c r="AR36" s="73">
+        <f t="shared" ref="AR36" si="177">AR35/$E35</f>
+        <v>0.98806988795540396</v>
+      </c>
+      <c r="AS36" s="73">
+        <f t="shared" ref="AS36" si="178">AS35/$E35</f>
+        <v>0.97157615633255356</v>
+      </c>
+      <c r="AT36" s="73">
+        <f t="shared" ref="AT36" si="179">AT35/$E35</f>
+        <v>0.95439536050067719</v>
+      </c>
+    </row>
+    <row r="37" spans="3:46" s="81" customFormat="1">
+      <c r="C37" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="81">
+        <f>E43+E44</f>
+        <v>20683.626500000006</v>
+      </c>
+      <c r="F37" s="81">
+        <f t="shared" ref="F37:O37" si="180">F43+F44</f>
+        <v>15024.313599999992</v>
+      </c>
+      <c r="G37" s="81">
+        <f t="shared" si="180"/>
+        <v>14677.074724999997</v>
+      </c>
+      <c r="H37" s="81">
+        <f t="shared" si="180"/>
+        <v>13325.719208313925</v>
+      </c>
+      <c r="I37" s="81">
+        <f t="shared" si="180"/>
+        <v>15802.422465132951</v>
+      </c>
+      <c r="J37" s="81">
+        <f t="shared" si="180"/>
+        <v>15742.833551444439</v>
+      </c>
+      <c r="K37" s="81">
+        <f t="shared" si="180"/>
+        <v>15674.562723964056</v>
+      </c>
+      <c r="L37" s="81">
+        <f t="shared" si="180"/>
+        <v>15608.444391811085</v>
+      </c>
+      <c r="M37" s="81">
+        <f t="shared" si="180"/>
+        <v>15554.390665093806</v>
+      </c>
+      <c r="N37" s="81">
+        <f t="shared" si="180"/>
+        <v>15508.219462685473</v>
+      </c>
+      <c r="O37" s="81">
+        <f t="shared" si="180"/>
+        <v>15467.436256218141</v>
+      </c>
+      <c r="P37" s="81">
+        <f t="shared" ref="P37:AP37" si="181">P43+P44</f>
+        <v>15428.064352163685</v>
+      </c>
+      <c r="Q37" s="81">
+        <f t="shared" si="181"/>
+        <v>15391.125952468414</v>
+      </c>
+      <c r="R37" s="81">
+        <f t="shared" si="181"/>
+        <v>15353.11281919395</v>
+      </c>
+      <c r="S37" s="81">
+        <f t="shared" si="181"/>
+        <v>15315.559839093825</v>
+      </c>
+      <c r="T37" s="81">
+        <f t="shared" si="181"/>
+        <v>15278.611440056833</v>
+      </c>
+      <c r="U37" s="81">
+        <f t="shared" si="181"/>
+        <v>15250.708910089512</v>
+      </c>
+      <c r="V37" s="81">
+        <f t="shared" si="181"/>
+        <v>15221.896240112357</v>
+      </c>
+      <c r="W37" s="81">
+        <f t="shared" si="181"/>
+        <v>15194.279919421642</v>
+      </c>
+      <c r="X37" s="81">
+        <f t="shared" si="181"/>
+        <v>15167.532473271567</v>
+      </c>
+      <c r="Y37" s="81">
+        <f t="shared" si="181"/>
+        <v>15141.70607993106</v>
+      </c>
+      <c r="Z37" s="81">
+        <f t="shared" si="181"/>
+        <v>15116.869261943189</v>
+      </c>
+      <c r="AA37" s="81">
+        <f t="shared" si="181"/>
+        <v>15092.351872963813</v>
+      </c>
+      <c r="AB37" s="81">
+        <f t="shared" si="181"/>
+        <v>15068.971571339904</v>
+      </c>
+      <c r="AC37" s="81">
+        <f t="shared" si="181"/>
+        <v>15046.809166834548</v>
+      </c>
+      <c r="AD37" s="81">
+        <f t="shared" si="181"/>
+        <v>15025.93571491392</v>
+      </c>
+      <c r="AE37" s="81">
+        <f t="shared" si="181"/>
+        <v>15006.433316051523</v>
+      </c>
+      <c r="AF37" s="81">
+        <f t="shared" si="181"/>
+        <v>14987.169238631526</v>
+      </c>
+      <c r="AG37" s="81">
+        <f t="shared" si="181"/>
+        <v>14969.407679608492</v>
+      </c>
+      <c r="AH37" s="81">
+        <f t="shared" si="181"/>
+        <v>14953.21600605495</v>
+      </c>
+      <c r="AI37" s="81">
+        <f t="shared" si="181"/>
+        <v>14938.638750124421</v>
+      </c>
+      <c r="AJ37" s="81">
+        <f t="shared" si="181"/>
+        <v>14925.728680348129</v>
+      </c>
+      <c r="AK37" s="81">
+        <f t="shared" si="181"/>
+        <v>14913.012428254826</v>
+      </c>
+      <c r="AL37" s="81">
+        <f t="shared" si="181"/>
+        <v>14902.197453446139</v>
+      </c>
+      <c r="AM37" s="81">
+        <f t="shared" si="181"/>
+        <v>14893.377776086205</v>
+      </c>
+      <c r="AN37" s="81">
+        <f t="shared" si="181"/>
+        <v>14886.649517233964</v>
+      </c>
+      <c r="AO37" s="81">
+        <f t="shared" si="181"/>
+        <v>14882.111220567127</v>
+      </c>
+      <c r="AP37" s="81">
+        <f t="shared" si="181"/>
+        <v>14878.770476658083</v>
+      </c>
+      <c r="AQ37" s="81">
+        <f>AQ43+AQ44</f>
+        <v>14877.809725644393</v>
+      </c>
+      <c r="AR37" s="81">
+        <f t="shared" ref="AR37:AT37" si="182">AR43+AR44</f>
+        <v>14879.333857683061</v>
+      </c>
+      <c r="AS37" s="81">
+        <f t="shared" si="182"/>
+        <v>14883.450474555724</v>
+      </c>
+      <c r="AT37" s="81">
+        <f t="shared" si="182"/>
+        <v>14891.740640924232</v>
+      </c>
+    </row>
+    <row r="38" spans="3:46">
+      <c r="D38" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" s="73">
+        <f>E37/$E37</f>
+        <v>1</v>
+      </c>
+      <c r="F38" s="73">
+        <f t="shared" ref="F38:O38" si="183">F37/$E37</f>
+        <v>0.72638681616108225</v>
+      </c>
+      <c r="G38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.70959871205371039</v>
+      </c>
+      <c r="H38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.64426415785036162</v>
+      </c>
+      <c r="I38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.76400637311512787</v>
+      </c>
+      <c r="J38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.76112540281291752</v>
+      </c>
+      <c r="K38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.75782468436877115</v>
+      </c>
+      <c r="L38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.75462803352260688</v>
+      </c>
+      <c r="M38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.75201467523568954</v>
+      </c>
+      <c r="N38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.74978241667076462</v>
+      </c>
+      <c r="O38" s="73">
+        <f t="shared" si="183"/>
+        <v>0.74781065381441392</v>
+      </c>
+      <c r="P38" s="73">
+        <f t="shared" ref="P38" si="184">P37/$E37</f>
+        <v>0.74590712379009938</v>
+      </c>
+      <c r="Q38" s="73">
+        <f t="shared" ref="Q38" si="185">Q37/$E37</f>
+        <v>0.74412124742575536</v>
+      </c>
+      <c r="R38" s="73">
+        <f t="shared" ref="R38" si="186">R37/$E37</f>
+        <v>0.74228341046450175</v>
+      </c>
+      <c r="S38" s="73">
+        <f t="shared" ref="S38" si="187">S37/$E37</f>
+        <v>0.74046782072253237</v>
+      </c>
+      <c r="T38" s="73">
+        <f t="shared" ref="T38" si="188">T37/$E37</f>
+        <v>0.73868146091580356</v>
+      </c>
+      <c r="U38" s="73">
+        <f t="shared" ref="U38" si="189">U37/$E37</f>
+        <v>0.73733244555008315</v>
+      </c>
+      <c r="V38" s="73">
+        <f t="shared" ref="V38" si="190">V37/$E37</f>
+        <v>0.7359394272620593</v>
+      </c>
+      <c r="W38" s="73">
+        <f t="shared" ref="W38" si="191">W37/$E37</f>
+        <v>0.73460424937675406</v>
+      </c>
+      <c r="X38" s="73">
+        <f t="shared" ref="X38:Y38" si="192">X37/$E37</f>
+        <v>0.73331107933473672</v>
+      </c>
+      <c r="Y38" s="73">
+        <f t="shared" si="192"/>
+        <v>0.73206243982074692</v>
+      </c>
+      <c r="Z38" s="73">
+        <f t="shared" ref="Z38" si="193">Z37/$E37</f>
+        <v>0.7308616437230282</v>
+      </c>
+      <c r="AA38" s="73">
+        <f t="shared" ref="AA38" si="194">AA37/$E37</f>
+        <v>0.72967629119409061</v>
+      </c>
+      <c r="AB38" s="73">
+        <f t="shared" ref="AB38" si="195">AB37/$E37</f>
+        <v>0.72854591390634038</v>
+      </c>
+      <c r="AC38" s="73">
+        <f t="shared" ref="AC38" si="196">AC37/$E37</f>
+        <v>0.72747441880342134</v>
+      </c>
+      <c r="AD38" s="73">
+        <f t="shared" ref="AD38" si="197">AD37/$E37</f>
+        <v>0.72646524123387723</v>
+      </c>
+      <c r="AE38" s="73">
+        <f t="shared" ref="AE38" si="198">AE37/$E37</f>
+        <v>0.72552235054387193</v>
+      </c>
+      <c r="AF38" s="73">
+        <f t="shared" ref="AF38" si="199">AF37/$E37</f>
+        <v>0.72459098208099637</v>
+      </c>
+      <c r="AG38" s="73">
+        <f t="shared" ref="AG38" si="200">AG37/$E37</f>
+        <v>0.72373225650774964</v>
+      </c>
+      <c r="AH38" s="73">
+        <f t="shared" ref="AH38:AI38" si="201">AH37/$E37</f>
+        <v>0.72294943084835472</v>
+      </c>
+      <c r="AI38" s="73">
+        <f t="shared" si="201"/>
+        <v>0.72224465811758964</v>
+      </c>
+      <c r="AJ38" s="73">
+        <f t="shared" ref="AJ38" si="202">AJ37/$E37</f>
+        <v>0.72162048953785374</v>
+      </c>
+      <c r="AK38" s="73">
+        <f t="shared" ref="AK38" si="203">AK37/$E37</f>
+        <v>0.72100569154325145</v>
+      </c>
+      <c r="AL38" s="73">
+        <f t="shared" ref="AL38" si="204">AL37/$E37</f>
+        <v>0.72048281540213144</v>
+      </c>
+      <c r="AM38" s="73">
+        <f t="shared" ref="AM38" si="205">AM37/$E37</f>
+        <v>0.72005640674696003</v>
+      </c>
+      <c r="AN38" s="73">
+        <f t="shared" ref="AN38" si="206">AN37/$E37</f>
+        <v>0.71973111278304891</v>
+      </c>
+      <c r="AO38" s="73">
+        <f t="shared" ref="AO38" si="207">AO37/$E37</f>
+        <v>0.71951169784308</v>
+      </c>
+      <c r="AP38" s="73">
+        <f t="shared" ref="AP38" si="208">AP37/$E37</f>
+        <v>0.71935018149056595</v>
+      </c>
+      <c r="AQ38" s="73">
+        <f>AQ37/$E37</f>
+        <v>0.71930373165674732</v>
+      </c>
+      <c r="AR38" s="73">
+        <f t="shared" ref="AR38" si="209">AR37/$E37</f>
+        <v>0.71937741951021295</v>
+      </c>
+      <c r="AS38" s="73">
+        <f t="shared" ref="AS38" si="210">AS37/$E37</f>
+        <v>0.71957644731960901</v>
+      </c>
+      <c r="AT38" s="73">
+        <f t="shared" ref="AT38" si="211">AT37/$E37</f>
+        <v>0.7199772554839079</v>
+      </c>
+    </row>
+    <row r="39" spans="3:46">
+      <c r="C39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="3:46">
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40">
+        <v>2019</v>
+      </c>
+      <c r="F40">
+        <v>2020</v>
+      </c>
+      <c r="G40">
+        <v>2021</v>
+      </c>
+      <c r="H40">
+        <v>2022</v>
+      </c>
+      <c r="I40">
+        <v>2023</v>
+      </c>
+      <c r="J40">
+        <v>2024</v>
+      </c>
+      <c r="K40">
+        <v>2025</v>
+      </c>
+      <c r="L40">
+        <v>2026</v>
+      </c>
+      <c r="M40">
+        <v>2027</v>
+      </c>
+      <c r="N40">
+        <v>2028</v>
+      </c>
+      <c r="O40">
+        <v>2029</v>
+      </c>
+      <c r="P40">
+        <v>2030</v>
+      </c>
+      <c r="Q40">
+        <v>2031</v>
+      </c>
+      <c r="R40">
+        <v>2032</v>
+      </c>
+      <c r="S40">
+        <v>2033</v>
+      </c>
+      <c r="T40">
+        <v>2034</v>
+      </c>
+      <c r="U40">
+        <v>2035</v>
+      </c>
+      <c r="V40">
+        <v>2036</v>
+      </c>
+      <c r="W40">
+        <v>2037</v>
+      </c>
+      <c r="X40">
+        <v>2038</v>
+      </c>
+      <c r="Y40">
+        <v>2039</v>
+      </c>
+      <c r="Z40">
+        <v>2040</v>
+      </c>
+      <c r="AA40">
+        <v>2041</v>
+      </c>
+      <c r="AB40">
+        <v>2042</v>
+      </c>
+      <c r="AC40">
+        <v>2043</v>
+      </c>
+      <c r="AD40">
+        <v>2044</v>
+      </c>
+      <c r="AE40">
+        <v>2045</v>
+      </c>
+      <c r="AF40">
+        <v>2046</v>
+      </c>
+      <c r="AG40">
+        <v>2047</v>
+      </c>
+      <c r="AH40">
+        <v>2048</v>
+      </c>
+      <c r="AI40">
+        <v>2049</v>
+      </c>
+      <c r="AJ40">
+        <v>2050</v>
+      </c>
+      <c r="AK40">
+        <v>2051</v>
+      </c>
+      <c r="AL40">
+        <v>2052</v>
+      </c>
+      <c r="AM40">
+        <v>2053</v>
+      </c>
+      <c r="AN40">
+        <v>2054</v>
+      </c>
+      <c r="AO40">
+        <v>2055</v>
+      </c>
+      <c r="AP40">
+        <v>2056</v>
+      </c>
+      <c r="AQ40">
+        <v>2057</v>
+      </c>
+      <c r="AR40">
+        <v>2058</v>
+      </c>
+      <c r="AS40">
+        <v>2059</v>
+      </c>
+      <c r="AT40">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="41" spans="3:46">
+      <c r="C41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41">
+        <f>22241.62*1.25*1.11111235721358/0.873698773342676</f>
+        <v>35356.777960068117</v>
+      </c>
+      <c r="F41">
+        <f>23940.89*1.25*0.965899928884944/0.873698773342676</f>
+        <v>33084.205698221434</v>
+      </c>
+      <c r="G41">
+        <f>25797.39*1.25*0.93/0.873698773342676</f>
+        <v>34324.720132390234</v>
+      </c>
+      <c r="H41">
+        <v>33421.896764949124</v>
+      </c>
+      <c r="I41">
+        <v>32306.333096250004</v>
+      </c>
+      <c r="J41">
+        <v>31815.000839346354</v>
+      </c>
+      <c r="K41">
+        <v>33754.177712075383</v>
+      </c>
+      <c r="L41">
+        <v>35531.525305294148</v>
+      </c>
+      <c r="M41">
+        <v>36888.524550128219</v>
+      </c>
+      <c r="N41">
+        <v>37957.194742992702</v>
+      </c>
+      <c r="O41">
+        <v>38817.161201446776</v>
+      </c>
+      <c r="P41">
+        <v>39566.082041562615</v>
+      </c>
+      <c r="Q41">
+        <v>40188.479692148983</v>
+      </c>
+      <c r="R41">
+        <v>40751.630561520811</v>
+      </c>
+      <c r="S41">
+        <v>41226.596669548861</v>
+      </c>
+      <c r="T41">
+        <v>41613.745972010729</v>
+      </c>
+      <c r="U41">
+        <v>41909.000957969482</v>
+      </c>
+      <c r="V41">
+        <v>42145.008001976254</v>
+      </c>
+      <c r="W41">
+        <v>42294.919049328026</v>
+      </c>
+      <c r="X41">
+        <v>42370.70599432318</v>
+      </c>
+      <c r="Y41">
+        <v>42378.835053498842</v>
+      </c>
+      <c r="Z41">
+        <v>42324.933516896555</v>
+      </c>
+      <c r="AA41">
+        <v>42219.095616444436</v>
+      </c>
+      <c r="AB41">
+        <v>42059.963588797778</v>
+      </c>
+      <c r="AC41">
+        <v>41852.066630146815</v>
+      </c>
+      <c r="AD41">
+        <v>41600.035003880235</v>
+      </c>
+      <c r="AE41">
+        <v>41307.452311610839</v>
+      </c>
+      <c r="AF41">
+        <v>40980.790368191672</v>
+      </c>
+      <c r="AG41">
+        <v>40619.882836204597</v>
+      </c>
+      <c r="AH41">
+        <v>40228.018799175035</v>
+      </c>
+      <c r="AI41">
+        <v>39809.23610648152</v>
+      </c>
+      <c r="AJ41">
+        <v>39366.703625992799</v>
+      </c>
+      <c r="AK41">
+        <v>38911.382162007598</v>
+      </c>
+      <c r="AL41">
+        <v>38429.873582758519</v>
+      </c>
+      <c r="AM41">
+        <v>37922.536961461454</v>
+      </c>
+      <c r="AN41">
+        <v>37389.426770696671</v>
+      </c>
+      <c r="AO41">
+        <v>36830.342232842981</v>
+      </c>
+      <c r="AP41">
+        <v>36245.305663395011</v>
+      </c>
+      <c r="AQ41">
+        <v>35633.171121101412</v>
+      </c>
+      <c r="AR41">
+        <v>34993.230758620215</v>
+      </c>
+      <c r="AS41">
+        <v>34324.637323667681</v>
+      </c>
+      <c r="AT41">
+        <v>33626.075090494181</v>
+      </c>
+    </row>
+    <row r="42" spans="3:46">
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42">
+        <f>9.6*1.25*330.741*1.11111235721358/0.873698773342676</f>
+        <v>5047.3745416562524</v>
+      </c>
+      <c r="F42">
+        <f>9.6*1.25*343.964277*0.965899928884944/0.873698773342676</f>
+        <v>4563.1526218881972</v>
+      </c>
+      <c r="G42">
+        <f>9.6*1.25*429.9117*0.93/0.873698773342676</f>
+        <v>5491.3829781906252</v>
+      </c>
+      <c r="H42">
+        <v>5158.9403999999995</v>
+      </c>
+      <c r="I42">
+        <v>5207.88</v>
+      </c>
+      <c r="J42">
+        <v>5200.3265599822298</v>
+      </c>
+      <c r="K42">
+        <v>5191.6483689144434</v>
+      </c>
+      <c r="L42">
+        <v>5183.2167084725406</v>
+      </c>
+      <c r="M42">
+        <v>5176.3019770696055</v>
+      </c>
+      <c r="N42">
+        <v>5170.3804305140839</v>
+      </c>
+      <c r="O42">
+        <v>5165.1383965914365</v>
+      </c>
+      <c r="P42">
+        <v>5160.0679047255126</v>
+      </c>
+      <c r="Q42">
+        <v>5155.3018431485925</v>
+      </c>
+      <c r="R42">
+        <v>5150.3884183900755</v>
+      </c>
+      <c r="S42">
+        <v>5145.5255972742507</v>
+      </c>
+      <c r="T42">
+        <v>5140.7324040939366</v>
+      </c>
+      <c r="U42">
+        <v>5125.8940392230443</v>
+      </c>
+      <c r="V42">
+        <v>5110.5768061724502</v>
+      </c>
+      <c r="W42">
+        <v>5095.9006902440969</v>
+      </c>
+      <c r="X42">
+        <v>5081.6911062590298</v>
+      </c>
+      <c r="Y42">
+        <v>5067.9753383027091</v>
+      </c>
+      <c r="Z42">
+        <v>5054.7893216023103</v>
+      </c>
+      <c r="AA42">
+        <v>5041.7769151669918</v>
+      </c>
+      <c r="AB42">
+        <v>5029.3718192177148</v>
+      </c>
+      <c r="AC42">
+        <v>5017.6163787606583</v>
+      </c>
+      <c r="AD42">
+        <v>5006.5477387092496</v>
+      </c>
+      <c r="AE42">
+        <v>4996.2088838647496</v>
+      </c>
+      <c r="AF42">
+        <v>4985.9989234373134</v>
+      </c>
+      <c r="AG42">
+        <v>4976.5876334079849</v>
+      </c>
+      <c r="AH42">
+        <v>4968.0101483444232</v>
+      </c>
+      <c r="AI42">
+        <v>4960.2895210179058</v>
+      </c>
+      <c r="AJ42">
+        <v>4953.4531950013034</v>
+      </c>
+      <c r="AK42">
+        <v>4946.7206407982003</v>
+      </c>
+      <c r="AL42">
+        <v>4940.9956649484229</v>
+      </c>
+      <c r="AM42">
+        <v>4936.3275781330321</v>
+      </c>
+      <c r="AN42">
+        <v>4932.7668543062218</v>
+      </c>
+      <c r="AO42">
+        <v>4930.365314551831</v>
+      </c>
+      <c r="AP42">
+        <v>4928.5975926632736</v>
+      </c>
+      <c r="AQ42">
+        <v>4928.0892432337805</v>
+      </c>
+      <c r="AR42">
+        <v>4928.8956766916353</v>
+      </c>
+      <c r="AS42">
+        <v>4931.0738638320072</v>
+      </c>
+      <c r="AT42">
+        <v>4935.4606021133877</v>
+      </c>
+    </row>
+    <row r="43" spans="3:46">
+      <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="E43">
+        <f>(47701.5602677324+536324.439732268)*45000*45/10^8</f>
+        <v>11826.526500000007</v>
+      </c>
+      <c r="F43">
+        <f>(48186.3139605286+541774.686039471)*4.4*40/10^4</f>
+        <v>10383.313599999992</v>
+      </c>
+      <c r="G43">
+        <f>(57945.2593223947+651497.740677605)*4.45*35/10^4</f>
+        <v>11049.574724999997</v>
+      </c>
+      <c r="H43">
+        <v>10918.219208313925</v>
+      </c>
+      <c r="I43">
+        <v>11062.422465132951</v>
+      </c>
+      <c r="J43">
+        <v>11030.332883751809</v>
+      </c>
+      <c r="K43">
+        <v>10993.518527883047</v>
+      </c>
+      <c r="L43">
+        <v>10957.80978618787</v>
+      </c>
+      <c r="M43">
+        <v>10928.572995330915</v>
+      </c>
+      <c r="N43">
+        <v>10903.569023745047</v>
+      </c>
+      <c r="O43">
+        <v>10881.459672424167</v>
+      </c>
+      <c r="P43">
+        <v>10860.095539066264</v>
+      </c>
+      <c r="Q43">
+        <v>10840.033832504996</v>
+      </c>
+      <c r="R43">
+        <v>10819.370952915671</v>
+      </c>
+      <c r="S43">
+        <v>10798.940390691694</v>
+      </c>
+      <c r="T43">
+        <v>10778.821393533197</v>
+      </c>
+      <c r="U43">
+        <v>10767.154275493647</v>
+      </c>
+      <c r="V43">
+        <v>10755.088842853938</v>
+      </c>
+      <c r="W43">
+        <v>10743.506764891123</v>
+      </c>
+      <c r="X43">
+        <v>10732.272679082544</v>
+      </c>
+      <c r="Y43">
+        <v>10721.410052943511</v>
+      </c>
+      <c r="Z43">
+        <v>10710.949315476408</v>
+      </c>
+      <c r="AA43">
+        <v>10700.609476098329</v>
+      </c>
+      <c r="AB43">
+        <v>10690.736313607684</v>
+      </c>
+      <c r="AC43">
+        <v>10681.365785933394</v>
+      </c>
+      <c r="AD43">
+        <v>10672.529803051983</v>
+      </c>
+      <c r="AE43">
+        <v>10664.264995977121</v>
+      </c>
+      <c r="AF43">
+        <v>10656.092670260197</v>
+      </c>
+      <c r="AG43">
+        <v>10648.549980702961</v>
+      </c>
+      <c r="AH43">
+        <v>10641.6674199151</v>
+      </c>
+      <c r="AI43">
+        <v>10635.465715472938</v>
+      </c>
+      <c r="AJ43">
+        <v>10629.968996683037</v>
+      </c>
+      <c r="AK43">
+        <v>10624.551045839193</v>
+      </c>
+      <c r="AL43">
+        <v>10619.940013912519</v>
+      </c>
+      <c r="AM43">
+        <v>10616.177502873181</v>
+      </c>
+      <c r="AN43">
+        <v>10613.305837987762</v>
+      </c>
+      <c r="AO43">
+        <v>10611.368162086363</v>
+      </c>
+      <c r="AP43">
+        <v>10609.941446221699</v>
+      </c>
+      <c r="AQ43">
+        <v>10609.531069011466</v>
+      </c>
+      <c r="AR43">
+        <v>10610.182123639634</v>
+      </c>
+      <c r="AS43">
+        <v>10611.940450740776</v>
+      </c>
+      <c r="AT43">
+        <v>10615.480638438765</v>
+      </c>
+    </row>
+    <row r="44" spans="3:46">
+      <c r="C44" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44">
+        <v>8857.1</v>
+      </c>
+      <c r="F44">
+        <v>4641</v>
+      </c>
+      <c r="G44">
+        <v>3627.5</v>
+      </c>
+      <c r="H44">
+        <v>2407.5</v>
+      </c>
+      <c r="I44">
+        <v>4740</v>
+      </c>
+      <c r="J44">
+        <v>4712.5006676926296</v>
+      </c>
+      <c r="K44">
+        <v>4681.0441960810103</v>
+      </c>
+      <c r="L44">
+        <v>4650.6346056232142</v>
+      </c>
+      <c r="M44">
+        <v>4625.8176697628915</v>
+      </c>
+      <c r="N44">
+        <v>4604.6504389404245</v>
+      </c>
+      <c r="O44">
+        <v>4585.976583793974</v>
+      </c>
+      <c r="P44">
+        <v>4567.9688130974209</v>
+      </c>
+      <c r="Q44">
+        <v>4551.0921199634186</v>
+      </c>
+      <c r="R44">
+        <v>4533.7418662782793</v>
+      </c>
+      <c r="S44">
+        <v>4516.6194484021307</v>
+      </c>
+      <c r="T44">
+        <v>4499.7900465236362</v>
+      </c>
+      <c r="U44">
+        <v>4483.5546345958646</v>
+      </c>
+      <c r="V44">
+        <v>4466.807397258418</v>
+      </c>
+      <c r="W44">
+        <v>4450.7731545305196</v>
+      </c>
+      <c r="X44">
+        <v>4435.2597941890244</v>
+      </c>
+      <c r="Y44">
+        <v>4420.2960269875493</v>
+      </c>
+      <c r="Z44">
+        <v>4405.9199464667818</v>
+      </c>
+      <c r="AA44">
+        <v>4391.742396865483</v>
+      </c>
+      <c r="AB44">
+        <v>4378.2352577322199</v>
+      </c>
+      <c r="AC44">
+        <v>4365.4433809011534</v>
+      </c>
+      <c r="AD44">
+        <v>4353.4059118619371</v>
+      </c>
+      <c r="AE44">
+        <v>4342.1683200744037</v>
+      </c>
+      <c r="AF44">
+        <v>4331.076568371328</v>
+      </c>
+      <c r="AG44">
+        <v>4320.85769890553</v>
+      </c>
+      <c r="AH44">
+        <v>4311.5485861398502</v>
+      </c>
+      <c r="AI44">
+        <v>4303.1730346514823</v>
+      </c>
+      <c r="AJ44">
+        <v>4295.7596836650928</v>
+      </c>
+      <c r="AK44">
+        <v>4288.4613824156331</v>
+      </c>
+      <c r="AL44">
+        <v>4282.2574395336196</v>
+      </c>
+      <c r="AM44">
+        <v>4277.200273213024</v>
+      </c>
+      <c r="AN44">
+        <v>4273.3436792462007</v>
+      </c>
+      <c r="AO44">
+        <v>4270.7430584807653</v>
+      </c>
+      <c r="AP44">
+        <v>4268.8290304363845</v>
+      </c>
+      <c r="AQ44">
+        <v>4268.2786566329269</v>
+      </c>
+      <c r="AR44">
+        <v>4269.1517340434266</v>
+      </c>
+      <c r="AS44">
+        <v>4271.510023814948</v>
+      </c>
+      <c r="AT44">
+        <v>4276.2600024854682</v>
       </c>
     </row>
   </sheetData>
@@ -9157,11 +11859,518 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8525320-127B-42E6-B371-C564E43981B5}">
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="59.8">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="75" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="75" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="75" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="75" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" s="75" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="80" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.3">
+      <c r="A2" s="76">
+        <v>2020</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="76">
+        <v>442</v>
+      </c>
+      <c r="G2" s="76">
+        <v>176</v>
+      </c>
+      <c r="H2" s="76">
+        <v>320</v>
+      </c>
+      <c r="I2" s="76">
+        <v>379</v>
+      </c>
+      <c r="J2" s="76">
+        <v>249</v>
+      </c>
+      <c r="K2" s="78">
+        <v>30515</v>
+      </c>
+      <c r="L2" s="78">
+        <v>83282</v>
+      </c>
+      <c r="M2" s="79">
+        <v>16764</v>
+      </c>
+      <c r="N2" s="79">
+        <v>34036</v>
+      </c>
+      <c r="O2" s="79">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.3">
+      <c r="A3" s="76">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="76">
+        <v>19740</v>
+      </c>
+      <c r="C3" s="76">
+        <v>8515</v>
+      </c>
+      <c r="D3" s="76">
+        <v>90</v>
+      </c>
+      <c r="E3" s="76">
+        <v>14626</v>
+      </c>
+      <c r="F3" s="76">
+        <v>676</v>
+      </c>
+      <c r="G3" s="76">
+        <v>357</v>
+      </c>
+      <c r="H3" s="76">
+        <v>304</v>
+      </c>
+      <c r="I3" s="76">
+        <v>409</v>
+      </c>
+      <c r="J3" s="76">
+        <v>1664</v>
+      </c>
+      <c r="K3" s="79">
+        <v>38622</v>
+      </c>
+      <c r="L3" s="79">
+        <v>93599</v>
+      </c>
+      <c r="M3" s="79">
+        <v>19278</v>
+      </c>
+      <c r="N3" s="79">
+        <v>37672</v>
+      </c>
+      <c r="O3" s="79">
+        <v>95</v>
+      </c>
+      <c r="P3">
+        <v>88108.832370196193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.3">
+      <c r="A4" s="76">
+        <v>2030</v>
+      </c>
+      <c r="B4" s="76">
+        <v>26143</v>
+      </c>
+      <c r="C4" s="76">
+        <v>8467</v>
+      </c>
+      <c r="D4" s="76">
+        <v>98</v>
+      </c>
+      <c r="E4" s="76">
+        <v>19544</v>
+      </c>
+      <c r="F4" s="76">
+        <v>670</v>
+      </c>
+      <c r="G4" s="76">
+        <v>591</v>
+      </c>
+      <c r="H4" s="76">
+        <v>289</v>
+      </c>
+      <c r="I4" s="76">
+        <v>429</v>
+      </c>
+      <c r="J4" s="76">
+        <v>2393</v>
+      </c>
+      <c r="K4" s="79">
+        <v>41810</v>
+      </c>
+      <c r="L4" s="79">
+        <v>109910</v>
+      </c>
+      <c r="M4" s="79">
+        <v>21364</v>
+      </c>
+      <c r="N4" s="79">
+        <v>41580</v>
+      </c>
+      <c r="O4" s="79">
+        <v>112</v>
+      </c>
+      <c r="P4">
+        <v>95744.316855708224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.3">
+      <c r="A5" s="76">
+        <v>2035</v>
+      </c>
+      <c r="B5" s="76">
+        <v>32149</v>
+      </c>
+      <c r="C5" s="76">
+        <v>7079</v>
+      </c>
+      <c r="D5" s="76">
+        <v>97</v>
+      </c>
+      <c r="E5" s="76">
+        <v>24101</v>
+      </c>
+      <c r="F5" s="76">
+        <v>644</v>
+      </c>
+      <c r="G5" s="76">
+        <v>920</v>
+      </c>
+      <c r="H5" s="76">
+        <v>266</v>
+      </c>
+      <c r="I5" s="76">
+        <v>447</v>
+      </c>
+      <c r="J5" s="76">
+        <v>2724</v>
+      </c>
+      <c r="K5" s="79">
+        <v>44461</v>
+      </c>
+      <c r="L5" s="79">
+        <v>127932</v>
+      </c>
+      <c r="M5" s="79">
+        <v>23726</v>
+      </c>
+      <c r="N5" s="79">
+        <v>45505</v>
+      </c>
+      <c r="O5" s="79">
+        <v>127</v>
+      </c>
+      <c r="P5">
+        <v>100761.26274628937</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14.3">
+      <c r="A6" s="76">
+        <v>2040</v>
+      </c>
+      <c r="B6" s="76">
+        <v>39395</v>
+      </c>
+      <c r="C6" s="76">
+        <v>8496</v>
+      </c>
+      <c r="D6" s="76">
+        <v>89</v>
+      </c>
+      <c r="E6" s="76">
+        <v>24496</v>
+      </c>
+      <c r="F6" s="76">
+        <v>606</v>
+      </c>
+      <c r="G6" s="76">
+        <v>1117</v>
+      </c>
+      <c r="H6" s="76">
+        <v>239</v>
+      </c>
+      <c r="I6" s="76">
+        <v>461</v>
+      </c>
+      <c r="J6" s="76">
+        <v>3337</v>
+      </c>
+      <c r="K6" s="79">
+        <v>48066</v>
+      </c>
+      <c r="L6" s="79">
+        <v>143831</v>
+      </c>
+      <c r="M6" s="79">
+        <v>26279</v>
+      </c>
+      <c r="N6" s="79">
+        <v>49367</v>
+      </c>
+      <c r="O6" s="79">
+        <v>139</v>
+      </c>
+      <c r="P6">
+        <v>105362.26286788104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.3">
+      <c r="A7" s="76">
+        <v>2045</v>
+      </c>
+      <c r="B7" s="76">
+        <v>47081</v>
+      </c>
+      <c r="C7" s="76">
+        <v>8035</v>
+      </c>
+      <c r="D7" s="76">
+        <v>76</v>
+      </c>
+      <c r="E7" s="76">
+        <v>25144</v>
+      </c>
+      <c r="F7" s="76">
+        <v>551</v>
+      </c>
+      <c r="G7" s="76">
+        <v>1133</v>
+      </c>
+      <c r="H7" s="76">
+        <v>227</v>
+      </c>
+      <c r="I7" s="76">
+        <v>472</v>
+      </c>
+      <c r="J7" s="76">
+        <v>4062</v>
+      </c>
+      <c r="K7" s="79">
+        <v>49671</v>
+      </c>
+      <c r="L7" s="79">
+        <v>162610</v>
+      </c>
+      <c r="M7" s="79">
+        <v>26388</v>
+      </c>
+      <c r="N7" s="79">
+        <v>50374</v>
+      </c>
+      <c r="O7" s="79">
+        <v>143</v>
+      </c>
+      <c r="P7">
+        <v>109254.23543248748</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.3">
+      <c r="A8" s="76">
+        <v>2050</v>
+      </c>
+      <c r="B8" s="76">
+        <v>53109</v>
+      </c>
+      <c r="C8" s="76">
+        <v>6996</v>
+      </c>
+      <c r="D8" s="76">
+        <v>56</v>
+      </c>
+      <c r="E8" s="76">
+        <v>24333</v>
+      </c>
+      <c r="F8" s="76">
+        <v>498</v>
+      </c>
+      <c r="G8" s="76">
+        <v>1091</v>
+      </c>
+      <c r="H8" s="76">
+        <v>215</v>
+      </c>
+      <c r="I8" s="76">
+        <v>484</v>
+      </c>
+      <c r="J8" s="76">
+        <v>4585</v>
+      </c>
+      <c r="K8" s="79">
+        <v>51277</v>
+      </c>
+      <c r="L8" s="79">
+        <v>181928</v>
+      </c>
+      <c r="M8" s="79">
+        <v>26498</v>
+      </c>
+      <c r="N8" s="79">
+        <v>51381</v>
+      </c>
+      <c r="O8" s="79">
+        <v>146</v>
+      </c>
+      <c r="P8">
+        <v>112762.25805648824</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.3">
+      <c r="A9" s="76">
+        <v>2055</v>
+      </c>
+      <c r="B9" s="76">
+        <v>60948</v>
+      </c>
+      <c r="C9" s="76">
+        <v>4853</v>
+      </c>
+      <c r="D9" s="76">
+        <v>48</v>
+      </c>
+      <c r="E9" s="76">
+        <v>21714</v>
+      </c>
+      <c r="F9" s="76">
+        <v>412</v>
+      </c>
+      <c r="G9" s="76">
+        <v>989</v>
+      </c>
+      <c r="H9" s="76">
+        <v>194</v>
+      </c>
+      <c r="I9" s="76">
+        <v>489</v>
+      </c>
+      <c r="J9" s="76">
+        <v>4790</v>
+      </c>
+      <c r="K9" s="79">
+        <v>53097</v>
+      </c>
+      <c r="L9" s="79">
+        <v>197391</v>
+      </c>
+      <c r="M9" s="79">
+        <v>26625</v>
+      </c>
+      <c r="N9" s="79">
+        <v>51704</v>
+      </c>
+      <c r="O9" s="79">
+        <v>148</v>
+      </c>
+      <c r="P9">
+        <v>113973.62011909923</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.3">
+      <c r="A10" s="76">
+        <v>2060</v>
+      </c>
+      <c r="B10" s="76">
+        <v>67849</v>
+      </c>
+      <c r="C10" s="76">
+        <v>2481</v>
+      </c>
+      <c r="D10" s="76">
+        <v>48</v>
+      </c>
+      <c r="E10" s="76">
+        <v>18482</v>
+      </c>
+      <c r="F10" s="76">
+        <v>332</v>
+      </c>
+      <c r="G10" s="76">
+        <v>901</v>
+      </c>
+      <c r="H10" s="76">
+        <v>172</v>
+      </c>
+      <c r="I10" s="76">
+        <v>494</v>
+      </c>
+      <c r="J10" s="76">
+        <v>4720</v>
+      </c>
+      <c r="K10" s="79">
+        <v>54917</v>
+      </c>
+      <c r="L10" s="79">
+        <v>204943</v>
+      </c>
+      <c r="M10" s="79">
+        <v>26752</v>
+      </c>
+      <c r="N10" s="79">
+        <v>52026</v>
+      </c>
+      <c r="O10" s="79">
+        <v>150</v>
+      </c>
+      <c r="P10">
+        <v>115184.98218171023</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11421F-6DD2-4FF2-A470-FE271B7BD140}">
-  <dimension ref="A1:BY25"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:BY47"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="12.875" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="9.5" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="8.875" style="38"/>
@@ -9170,12 +12379,12 @@
     <col min="77" max="77" width="8.875" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" ht="15" thickBot="1">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:77" ht="14.95" thickBot="1">
+      <c r="A1" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
       <c r="D1" s="22" t="s">
         <v>27</v>
       </c>
@@ -9399,12 +12608,12 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:77" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A2" s="68" t="s">
+    <row r="2" spans="1:77" ht="15.65" customHeight="1" thickBot="1">
+      <c r="A2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="64"/>
       <c r="D2" s="13">
         <v>9928</v>
       </c>
@@ -9514,12 +12723,12 @@
         <v>302296.95500000002</v>
       </c>
     </row>
-    <row r="3" spans="1:77" ht="16.5" thickBot="1">
-      <c r="A3" s="68" t="s">
+    <row r="3" spans="1:77" ht="16.3" thickBot="1">
+      <c r="A3" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
       <c r="D3" s="9">
         <v>5345.19</v>
       </c>
@@ -9779,12 +12988,12 @@
         <v>141000</v>
       </c>
     </row>
-    <row r="4" spans="1:77" ht="16.5" thickBot="1">
-      <c r="A4" s="68" t="s">
+    <row r="4" spans="1:77" ht="16.3" thickBot="1">
+      <c r="A4" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
       <c r="D4" s="9">
         <v>350.3</v>
       </c>
@@ -10044,12 +13253,12 @@
         <v>98000</v>
       </c>
     </row>
-    <row r="5" spans="1:77" ht="16.5" thickBot="1">
-      <c r="A5" s="69" t="s">
+    <row r="5" spans="1:77" ht="16.3" thickBot="1">
+      <c r="A5" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="9">
         <v>3801.8</v>
       </c>
@@ -10309,12 +13518,12 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="6" spans="1:77" ht="16.5" thickBot="1">
+    <row r="6" spans="1:77" ht="16.3" thickBot="1">
       <c r="A6" s="27"/>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="63"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="14">
         <v>2487</v>
       </c>
@@ -10421,7 +13630,7 @@
         <v>97842</v>
       </c>
     </row>
-    <row r="7" spans="1:77" ht="15.75">
+    <row r="7" spans="1:77" ht="15.65">
       <c r="A7" s="26" t="s">
         <v>23</v>
       </c>
@@ -11556,7 +14765,10 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="17" spans="3:77">
+    <row r="17" spans="1:77">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
@@ -11783,7 +14995,7 @@
         <v>141000</v>
       </c>
     </row>
-    <row r="18" spans="3:77">
+    <row r="18" spans="1:77">
       <c r="C18" t="s">
         <v>12</v>
       </c>
@@ -12010,12 +15222,12 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="20" spans="3:77">
+    <row r="20" spans="1:77">
       <c r="C20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="3:77">
+    <row r="21" spans="1:77">
       <c r="C21" t="s">
         <v>66</v>
       </c>
@@ -12316,7 +15528,7 @@
         <v>1.6286685551466342</v>
       </c>
     </row>
-    <row r="22" spans="3:77">
+    <row r="22" spans="1:77">
       <c r="C22" t="s">
         <v>52</v>
       </c>
@@ -12617,7 +15829,7 @@
         <v>1.6286685551466342</v>
       </c>
     </row>
-    <row r="23" spans="3:77">
+    <row r="23" spans="1:77">
       <c r="C23" t="s">
         <v>77</v>
       </c>
@@ -12918,7 +16130,7 @@
         <v>6.5778517901748543</v>
       </c>
     </row>
-    <row r="24" spans="3:77">
+    <row r="24" spans="1:77">
       <c r="C24" t="s">
         <v>11</v>
       </c>
@@ -13219,7 +16431,7 @@
         <v>4.6207601248719463</v>
       </c>
     </row>
-    <row r="25" spans="3:77">
+    <row r="25" spans="1:77">
       <c r="C25" t="s">
         <v>12</v>
       </c>
@@ -13518,6 +16730,2488 @@
       <c r="BY25" s="38">
         <f t="shared" si="28"/>
         <v>1.9180901793404868</v>
+      </c>
+    </row>
+    <row r="30" spans="1:77">
+      <c r="E30">
+        <v>2019</v>
+      </c>
+      <c r="F30">
+        <v>2020</v>
+      </c>
+      <c r="G30">
+        <v>2021</v>
+      </c>
+      <c r="H30">
+        <v>2022</v>
+      </c>
+      <c r="I30">
+        <v>2023</v>
+      </c>
+      <c r="J30">
+        <v>2024</v>
+      </c>
+      <c r="K30">
+        <v>2025</v>
+      </c>
+      <c r="L30">
+        <v>2026</v>
+      </c>
+      <c r="M30">
+        <v>2027</v>
+      </c>
+      <c r="N30">
+        <v>2028</v>
+      </c>
+      <c r="O30">
+        <v>2029</v>
+      </c>
+      <c r="P30">
+        <v>2030</v>
+      </c>
+      <c r="Q30">
+        <v>2031</v>
+      </c>
+      <c r="R30">
+        <v>2032</v>
+      </c>
+      <c r="S30">
+        <v>2033</v>
+      </c>
+      <c r="T30">
+        <v>2034</v>
+      </c>
+      <c r="U30">
+        <v>2035</v>
+      </c>
+      <c r="V30">
+        <v>2036</v>
+      </c>
+      <c r="W30">
+        <v>2037</v>
+      </c>
+      <c r="X30">
+        <v>2038</v>
+      </c>
+      <c r="Y30">
+        <v>2039</v>
+      </c>
+      <c r="Z30">
+        <v>2040</v>
+      </c>
+      <c r="AA30">
+        <v>2041</v>
+      </c>
+      <c r="AB30">
+        <v>2042</v>
+      </c>
+      <c r="AC30">
+        <v>2043</v>
+      </c>
+      <c r="AD30">
+        <v>2044</v>
+      </c>
+      <c r="AE30">
+        <v>2045</v>
+      </c>
+      <c r="AF30">
+        <v>2046</v>
+      </c>
+      <c r="AG30">
+        <v>2047</v>
+      </c>
+      <c r="AH30">
+        <v>2048</v>
+      </c>
+      <c r="AI30">
+        <v>2049</v>
+      </c>
+      <c r="AJ30">
+        <v>2050</v>
+      </c>
+      <c r="AK30">
+        <v>2051</v>
+      </c>
+      <c r="AL30">
+        <v>2052</v>
+      </c>
+      <c r="AM30">
+        <v>2053</v>
+      </c>
+      <c r="AN30">
+        <v>2054</v>
+      </c>
+      <c r="AO30">
+        <v>2055</v>
+      </c>
+      <c r="AP30">
+        <v>2056</v>
+      </c>
+      <c r="AQ30">
+        <v>2057</v>
+      </c>
+      <c r="AR30">
+        <v>2058</v>
+      </c>
+      <c r="AS30">
+        <v>2059</v>
+      </c>
+      <c r="AT30">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="31" spans="1:77">
+      <c r="C31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31">
+        <v>263.2</v>
+      </c>
+      <c r="F31">
+        <v>240.2</v>
+      </c>
+      <c r="G31">
+        <v>278.16000000000003</v>
+      </c>
+      <c r="H31">
+        <v>254.1</v>
+      </c>
+      <c r="I31">
+        <v>283.62</v>
+      </c>
+      <c r="J31">
+        <v>353.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:77">
+      <c r="D32" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="73">
+        <f>E31/$E$31</f>
+        <v>1</v>
+      </c>
+      <c r="F32" s="73">
+        <f>F31/$E$31</f>
+        <v>0.91261398176291797</v>
+      </c>
+      <c r="G32" s="73">
+        <f>G31/$E$31</f>
+        <v>1.0568389057750762</v>
+      </c>
+      <c r="H32" s="73">
+        <f>H31/$E$31</f>
+        <v>0.96542553191489366</v>
+      </c>
+      <c r="I32" s="73">
+        <f>I31/$E$31</f>
+        <v>1.0775835866261398</v>
+      </c>
+      <c r="J32" s="73">
+        <f>J31/$E$31</f>
+        <v>1.3445668693009118</v>
+      </c>
+      <c r="K32" s="73">
+        <f>(1+K33)*J32/$E$32</f>
+        <v>1.3984176791404332</v>
+      </c>
+      <c r="L32" s="73">
+        <f t="shared" ref="L32:AT32" si="29">(1+L33)*K32/$E$32</f>
+        <v>1.4529251443088298</v>
+      </c>
+      <c r="M32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.4994441506473171</v>
+      </c>
+      <c r="N32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.5406118957354304</v>
+      </c>
+      <c r="O32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.5780989933025782</v>
+      </c>
+      <c r="P32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.6152793551582547</v>
+      </c>
+      <c r="Q32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.6510859577662245</v>
+      </c>
+      <c r="R32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.6888528402657748</v>
+      </c>
+      <c r="S32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.7271222145467906</v>
+      </c>
+      <c r="T32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.7657348550500753</v>
+      </c>
+      <c r="U32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.8039598821254301</v>
+      </c>
+      <c r="V32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.8443894253187751</v>
+      </c>
+      <c r="W32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.8841136199395006</v>
+      </c>
+      <c r="X32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.9235165719601217</v>
+      </c>
+      <c r="Y32" s="73">
+        <f t="shared" si="29"/>
+        <v>1.9624541614497415</v>
+      </c>
+      <c r="Z32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.0007489709435924</v>
+      </c>
+      <c r="AA32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.0393775226920829</v>
+      </c>
+      <c r="AB32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.0770110905861077</v>
+      </c>
+      <c r="AC32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.1134214730578313</v>
+      </c>
+      <c r="AD32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.1483873310415347</v>
+      </c>
+      <c r="AE32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.1816615540060962</v>
+      </c>
+      <c r="AF32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.2150989241955128</v>
+      </c>
+      <c r="AG32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.2464571415849068</v>
+      </c>
+      <c r="AH32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.2754965466913193</v>
+      </c>
+      <c r="AI32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3020186253936443</v>
+      </c>
+      <c r="AJ32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.325813632347574</v>
+      </c>
+      <c r="AK32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3495223448300533</v>
+      </c>
+      <c r="AL32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3699160960534305</v>
+      </c>
+      <c r="AM32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3867087247538286</v>
+      </c>
+      <c r="AN32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3996207689142492</v>
+      </c>
+      <c r="AO32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.4083827652373375</v>
+      </c>
+      <c r="AP32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.4148589855453437</v>
+      </c>
+      <c r="AQ32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.4167270506965299</v>
+      </c>
+      <c r="AR32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.413760998151631</v>
+      </c>
+      <c r="AS32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.4057607935759342</v>
+      </c>
+      <c r="AT32" s="73">
+        <f t="shared" si="29"/>
+        <v>2.3897093564136922</v>
+      </c>
+    </row>
+    <row r="33" spans="3:46">
+      <c r="D33" t="s">
+        <v>88</v>
+      </c>
+      <c r="K33">
+        <v>4.0050674361417557E-2</v>
+      </c>
+      <c r="L33">
+        <v>3.8977957717111301E-2</v>
+      </c>
+      <c r="M33">
+        <v>3.2017483158512446E-2</v>
+      </c>
+      <c r="N33">
+        <v>2.7455337413094805E-2</v>
+      </c>
+      <c r="O33">
+        <v>2.4332602955303484E-2</v>
+      </c>
+      <c r="P33">
+        <v>2.3560221515550771E-2</v>
+      </c>
+      <c r="Q33">
+        <v>2.2167436545031328E-2</v>
+      </c>
+      <c r="R33">
+        <v>2.2873965054276055E-2</v>
+      </c>
+      <c r="S33">
+        <v>2.2659981597326916E-2</v>
+      </c>
+      <c r="T33">
+        <v>2.2356634740765591E-2</v>
+      </c>
+      <c r="U33">
+        <v>2.1648225930427634E-2</v>
+      </c>
+      <c r="V33">
+        <v>2.2411553379840621E-2</v>
+      </c>
+      <c r="W33">
+        <v>2.153785641763788E-2</v>
+      </c>
+      <c r="X33">
+        <v>2.0913256824652924E-2</v>
+      </c>
+      <c r="Y33">
+        <v>2.0242918650782028E-2</v>
+      </c>
+      <c r="Z33">
+        <v>1.9513734509631054E-2</v>
+      </c>
+      <c r="AA33">
+        <v>1.9307045666139853E-2</v>
+      </c>
+      <c r="AB33">
+        <v>1.8453458212261919E-2</v>
+      </c>
+      <c r="AC33">
+        <v>1.7530182018166005E-2</v>
+      </c>
+      <c r="AD33">
+        <v>1.6544668647239913E-2</v>
+      </c>
+      <c r="AE33">
+        <v>1.5487999991337674E-2</v>
+      </c>
+      <c r="AF33">
+        <v>1.5326561596145271E-2</v>
+      </c>
+      <c r="AG33">
+        <v>1.4156576506298845E-2</v>
+      </c>
+      <c r="AH33">
+        <v>1.2926756789103466E-2</v>
+      </c>
+      <c r="AI33">
+        <v>1.1655512613670727E-2</v>
+      </c>
+      <c r="AJ33">
+        <v>1.033658315855761E-2</v>
+      </c>
+      <c r="AK33">
+        <v>1.0193728402283319E-2</v>
+      </c>
+      <c r="AL33">
+        <v>8.6799562763266273E-3</v>
+      </c>
+      <c r="AM33">
+        <v>7.0857481952050433E-3</v>
+      </c>
+      <c r="AN33">
+        <v>5.4099790336805233E-3</v>
+      </c>
+      <c r="AO33">
+        <v>3.6514087711671194E-3</v>
+      </c>
+      <c r="AP33">
+        <v>2.6890328238037054E-3</v>
+      </c>
+      <c r="AQ33">
+        <v>7.7357111217168928E-4</v>
+      </c>
+      <c r="AR33">
+        <v>-1.2273014215834043E-3</v>
+      </c>
+      <c r="AS33">
+        <v>-3.3144145513259947E-3</v>
+      </c>
+      <c r="AT33">
+        <v>-6.6720836107662549E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="3:46" ht="14.3">
+      <c r="C34" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34">
+        <v>30182</v>
+      </c>
+      <c r="F34">
+        <v>30514.5</v>
+      </c>
+      <c r="G34">
+        <v>33238</v>
+      </c>
+      <c r="H34">
+        <v>35945.699999999997</v>
+      </c>
+      <c r="I34">
+        <v>36460.400000000001</v>
+      </c>
+      <c r="J34">
+        <v>35861.9</v>
+      </c>
+      <c r="K34">
+        <v>38622</v>
+      </c>
+      <c r="L34">
+        <f>($P34/$K34)^(0.2)*K34</f>
+        <v>39239.533996977785</v>
+      </c>
+      <c r="M34">
+        <f t="shared" ref="M34:O36" si="30">($P34/$K34)^(0.2)*L34</f>
+        <v>39866.94185438288</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="30"/>
+        <v>40504.381447118059</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="30"/>
+        <v>41152.013174375883</v>
+      </c>
+      <c r="P34">
+        <v>41810</v>
+      </c>
+      <c r="Q34">
+        <f>($U34/$P34)^(0.2)*P34</f>
+        <v>42327.242791662262</v>
+      </c>
+      <c r="R34">
+        <f t="shared" ref="R34:T36" si="31">($U34/$P34)^(0.2)*Q34</f>
+        <v>42850.88453346867</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="31"/>
+        <v>43381.004388558089</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="31"/>
+        <v>43917.682499417948</v>
+      </c>
+      <c r="U34" s="79">
+        <v>44461</v>
+      </c>
+      <c r="V34">
+        <f>($Z34/$U34)^(0.2)*U34</f>
+        <v>45159.692657414722</v>
+      </c>
+      <c r="W34">
+        <f t="shared" ref="W34:Y36" si="32">($Z34/$U34)^(0.2)*V34</f>
+        <v>45869.365082030476</v>
+      </c>
+      <c r="X34">
+        <f t="shared" si="32"/>
+        <v>46590.189817935869</v>
+      </c>
+      <c r="Y34">
+        <f t="shared" si="32"/>
+        <v>47322.342120703455</v>
+      </c>
+      <c r="Z34" s="79">
+        <v>48066</v>
+      </c>
+      <c r="AA34">
+        <f>($AE34/$Z34)^(0.2)*Z34</f>
+        <v>48382.796461540631</v>
+      </c>
+      <c r="AB34">
+        <f t="shared" ref="AB34:AD36" si="33">($AE34/$Z34)^(0.2)*AA34</f>
+        <v>48701.680885425638</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="33"/>
+        <v>49022.667033130543</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="33"/>
+        <v>49345.768756830883</v>
+      </c>
+      <c r="AE34" s="79">
+        <v>49671</v>
+      </c>
+      <c r="AF34">
+        <f>($AJ34/$AE34)^(0.2)*AE34</f>
+        <v>49988.124696397652</v>
+      </c>
+      <c r="AG34">
+        <f t="shared" ref="AG34:AI36" si="34">($AJ34/$AE34)^(0.2)*AF34</f>
+        <v>50307.274076676549</v>
+      </c>
+      <c r="AH34">
+        <f t="shared" si="34"/>
+        <v>50628.461067438955</v>
+      </c>
+      <c r="AI34">
+        <f t="shared" si="34"/>
+        <v>50951.698677817083</v>
+      </c>
+      <c r="AJ34" s="79">
+        <v>51277</v>
+      </c>
+      <c r="AK34">
+        <f>($AO34/$AJ34)^(0.2)*AJ34</f>
+        <v>51635.939539426283</v>
+      </c>
+      <c r="AL34">
+        <f t="shared" ref="AL34:AN36" si="35">($AO34/$AJ34)^(0.2)*AK34</f>
+        <v>51997.391659404537</v>
+      </c>
+      <c r="AM34">
+        <f t="shared" si="35"/>
+        <v>52361.373948025059</v>
+      </c>
+      <c r="AN34">
+        <f t="shared" si="35"/>
+        <v>52727.904116494967</v>
+      </c>
+      <c r="AO34" s="79">
+        <v>53097</v>
+      </c>
+      <c r="AP34">
+        <f>($AT34/$AO34)^(0.2)*AO34</f>
+        <v>53456.10952433286</v>
+      </c>
+      <c r="AQ34">
+        <f t="shared" ref="AQ34:AS36" si="36">($AT34/$AO34)^(0.2)*AP34</f>
+        <v>53817.64780453642</v>
+      </c>
+      <c r="AR34">
+        <f t="shared" si="36"/>
+        <v>54181.631266950499</v>
+      </c>
+      <c r="AS34">
+        <f t="shared" si="36"/>
+        <v>54548.076449010747</v>
+      </c>
+      <c r="AT34" s="79">
+        <v>54917</v>
+      </c>
+    </row>
+    <row r="35" spans="3:46">
+      <c r="D35" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="73">
+        <f>E34/$E$34</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="73">
+        <f t="shared" ref="F35:S35" si="37">F34/$E$34</f>
+        <v>1.011016499900603</v>
+      </c>
+      <c r="G35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.1012524020939634</v>
+      </c>
+      <c r="H35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.1909648134649791</v>
+      </c>
+      <c r="I35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.2080180239878073</v>
+      </c>
+      <c r="J35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.1881883241667219</v>
+      </c>
+      <c r="K35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.2796368696574116</v>
+      </c>
+      <c r="L35" s="73">
+        <f>L34/$E$34</f>
+        <v>1.3000972101576365</v>
+      </c>
+      <c r="M35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.3208846946651276</v>
+      </c>
+      <c r="N35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.3420045539433456</v>
+      </c>
+      <c r="O35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.3634621023913551</v>
+      </c>
+      <c r="P35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.3852627393810881</v>
+      </c>
+      <c r="Q35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.4024001985177346</v>
+      </c>
+      <c r="R35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.4197496697855898</v>
+      </c>
+      <c r="S35" s="73">
+        <f t="shared" si="37"/>
+        <v>1.4373137760439365</v>
+      </c>
+      <c r="T35" s="73">
+        <f t="shared" ref="T35" si="38">T34/$E$34</f>
+        <v>1.4550951726001573</v>
+      </c>
+      <c r="U35" s="73">
+        <f t="shared" ref="U35" si="39">U34/$E$34</f>
+        <v>1.473096547611159</v>
+      </c>
+      <c r="V35" s="73">
+        <f t="shared" ref="V35" si="40">V34/$E$34</f>
+        <v>1.4962458636742006</v>
+      </c>
+      <c r="W35" s="73">
+        <f t="shared" ref="W35" si="41">W34/$E$34</f>
+        <v>1.5197589650132688</v>
+      </c>
+      <c r="X35" s="73">
+        <f t="shared" ref="X35" si="42">X34/$E$34</f>
+        <v>1.5436415684161378</v>
+      </c>
+      <c r="Y35" s="73">
+        <f t="shared" ref="Y35" si="43">Y34/$E$34</f>
+        <v>1.5678994805083644</v>
+      </c>
+      <c r="Z35" s="73">
+        <f t="shared" ref="Z35" si="44">Z34/$E$34</f>
+        <v>1.5925385991650653</v>
+      </c>
+      <c r="AA35" s="73">
+        <f t="shared" ref="AA35" si="45">AA34/$E$34</f>
+        <v>1.6030348042389713</v>
+      </c>
+      <c r="AB35" s="73">
+        <f t="shared" ref="AB35" si="46">AB34/$E$34</f>
+        <v>1.6136001883714015</v>
+      </c>
+      <c r="AC35" s="73">
+        <f t="shared" ref="AC35" si="47">AC34/$E$34</f>
+        <v>1.6242352075121114</v>
+      </c>
+      <c r="AD35" s="73">
+        <f t="shared" ref="AD35" si="48">AD34/$E$34</f>
+        <v>1.6349403206159592</v>
+      </c>
+      <c r="AE35" s="73">
+        <f t="shared" ref="AE35" si="49">AE34/$E$34</f>
+        <v>1.6457159896627129</v>
+      </c>
+      <c r="AF35" s="73">
+        <f t="shared" ref="AF35" si="50">AF34/$E$34</f>
+        <v>1.6562230699223925</v>
+      </c>
+      <c r="AG35" s="73">
+        <f t="shared" ref="AG35" si="51">AG34/$E$34</f>
+        <v>1.6667972326776406</v>
+      </c>
+      <c r="AH35" s="73">
+        <f t="shared" ref="AH35" si="52">AH34/$E$34</f>
+        <v>1.6774389062169159</v>
+      </c>
+      <c r="AI35" s="73">
+        <f t="shared" ref="AI35" si="53">AI34/$E$34</f>
+        <v>1.6881485215630867</v>
+      </c>
+      <c r="AJ35" s="73">
+        <f t="shared" ref="AJ35" si="54">AJ34/$E$34</f>
+        <v>1.6989265124908886</v>
+      </c>
+      <c r="AK35" s="73">
+        <f t="shared" ref="AK35" si="55">AK34/$E$34</f>
+        <v>1.7108190159507748</v>
+      </c>
+      <c r="AL35" s="73">
+        <f t="shared" ref="AL35" si="56">AL34/$E$34</f>
+        <v>1.7227947670599872</v>
+      </c>
+      <c r="AM35" s="73">
+        <f t="shared" ref="AM35" si="57">AM34/$E$34</f>
+        <v>1.7348543485529475</v>
+      </c>
+      <c r="AN35" s="73">
+        <f t="shared" ref="AN35" si="58">AN34/$E$34</f>
+        <v>1.7469983472432233</v>
+      </c>
+      <c r="AO35" s="73">
+        <f t="shared" ref="AO35" si="59">AO34/$E$34</f>
+        <v>1.759227354052084</v>
+      </c>
+      <c r="AP35" s="73">
+        <f t="shared" ref="AP35" si="60">AP34/$E$34</f>
+        <v>1.7711254895080797</v>
+      </c>
+      <c r="AQ35" s="73">
+        <f t="shared" ref="AQ35" si="61">AQ34/$E$34</f>
+        <v>1.7831040953063555</v>
+      </c>
+      <c r="AR35" s="73">
+        <f t="shared" ref="AR35" si="62">AR34/$E$34</f>
+        <v>1.7951637156898317</v>
+      </c>
+      <c r="AS35" s="73">
+        <f t="shared" ref="AS35" si="63">AS34/$E$34</f>
+        <v>1.8073048985822924</v>
+      </c>
+      <c r="AT35" s="73">
+        <f t="shared" ref="AT35" si="64">AT34/$E$34</f>
+        <v>1.8195281956132794</v>
+      </c>
+    </row>
+    <row r="36" spans="3:46">
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36">
+        <v>103963</v>
+      </c>
+      <c r="F36">
+        <v>105834.4</v>
+      </c>
+      <c r="G36">
+        <v>115577.5</v>
+      </c>
+      <c r="H36">
+        <v>121003.1</v>
+      </c>
+      <c r="I36">
+        <v>129951.5</v>
+      </c>
+      <c r="J36">
+        <v>141422.9</v>
+      </c>
+      <c r="K36">
+        <f>'2022交科院'!M3+'2022交科院'!N3+'2022交科院'!P3</f>
+        <v>145058.83237019618</v>
+      </c>
+      <c r="L36">
+        <f>($P36/$K36)^(0.2)*K36</f>
+        <v>147687.70188149178</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="30"/>
+        <v>150364.21382030798</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="30"/>
+        <v>153089.23159994482</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="30"/>
+        <v>155863.63428115277</v>
+      </c>
+      <c r="P36">
+        <f>'2022交科院'!M4+'2022交科院'!N4+'2022交科院'!P4</f>
+        <v>158688.31685570822</v>
+      </c>
+      <c r="Q36">
+        <f>($U36/$P36)^(0.2)*P36</f>
+        <v>160887.3113107353</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="31"/>
+        <v>163116.77793100459</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="31"/>
+        <v>165377.13897899725</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="31"/>
+        <v>167668.82256861983</v>
+      </c>
+      <c r="U36">
+        <f>'2022交科院'!M5+'2022交科院'!N5+'2022交科院'!P5</f>
+        <v>169992.26274628937</v>
+      </c>
+      <c r="V36">
+        <f>($Z36/$U36)^(0.2)*U36</f>
+        <v>172140.47773565742</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="32"/>
+        <v>174315.840005531</v>
+      </c>
+      <c r="X36">
+        <f t="shared" si="32"/>
+        <v>176518.69261972938</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="32"/>
+        <v>178749.38297741525</v>
+      </c>
+      <c r="Z36">
+        <f>'2022交科院'!M6+'2022交科院'!N6+'2022交科院'!P6</f>
+        <v>181008.26286788104</v>
+      </c>
+      <c r="AA36">
+        <f>($AE36/$Z36)^(0.2)*Z36</f>
+        <v>181998.95341207349</v>
+      </c>
+      <c r="AB36">
+        <f t="shared" si="33"/>
+        <v>182995.06618251573</v>
+      </c>
+      <c r="AC36">
+        <f t="shared" si="33"/>
+        <v>183996.63085602026</v>
+      </c>
+      <c r="AD36">
+        <f t="shared" si="33"/>
+        <v>185003.67727182605</v>
+      </c>
+      <c r="AE36">
+        <f>'2022交科院'!M7+'2022交科院'!N7+'2022交科院'!P7</f>
+        <v>186016.23543248748</v>
+      </c>
+      <c r="AF36">
+        <f>($AJ36/$AE36)^(0.2)*AE36</f>
+        <v>186932.17529725743</v>
+      </c>
+      <c r="AG36">
+        <f t="shared" si="34"/>
+        <v>187852.62522983906</v>
+      </c>
+      <c r="AH36">
+        <f t="shared" si="34"/>
+        <v>188777.6074377074</v>
+      </c>
+      <c r="AI36">
+        <f t="shared" si="34"/>
+        <v>189707.14423768659</v>
+      </c>
+      <c r="AJ36">
+        <f>'2022交科院'!M8+'2022交科院'!N8+'2022交科院'!P8</f>
+        <v>190641.25805648824</v>
+      </c>
+      <c r="AK36">
+        <f>($AO36/$AJ36)^(0.2)*AJ36</f>
+        <v>190972.37824021498</v>
+      </c>
+      <c r="AL36">
+        <f t="shared" si="35"/>
+        <v>191304.07353856898</v>
+      </c>
+      <c r="AM36">
+        <f t="shared" si="35"/>
+        <v>191636.34495045294</v>
+      </c>
+      <c r="AN36">
+        <f t="shared" si="35"/>
+        <v>191969.19347650447</v>
+      </c>
+      <c r="AO36">
+        <f>'2022交科院'!M9+'2022交科院'!N9+'2022交科院'!P9</f>
+        <v>192302.62011909921</v>
+      </c>
+      <c r="AP36">
+        <f>($AT36/$AO36)^(0.2)*AO36</f>
+        <v>192633.55157726113</v>
+      </c>
+      <c r="AQ36">
+        <f t="shared" si="36"/>
+        <v>192965.05253171973</v>
+      </c>
+      <c r="AR36">
+        <f t="shared" si="36"/>
+        <v>193297.12396251492</v>
+      </c>
+      <c r="AS36">
+        <f t="shared" si="36"/>
+        <v>193629.7668513731</v>
+      </c>
+      <c r="AT36">
+        <f>'2022交科院'!M10+'2022交科院'!N10+'2022交科院'!P10</f>
+        <v>193962.98218171025</v>
+      </c>
+    </row>
+    <row r="37" spans="3:46">
+      <c r="D37" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="73">
+        <f>E36/$E36</f>
+        <v>1</v>
+      </c>
+      <c r="F37" s="73">
+        <f t="shared" ref="F37:J37" si="65">F36/$E36</f>
+        <v>1.0180006348412416</v>
+      </c>
+      <c r="G37" s="73">
+        <f t="shared" si="65"/>
+        <v>1.1117176303107836</v>
+      </c>
+      <c r="H37" s="73">
+        <f t="shared" si="65"/>
+        <v>1.1639054278926158</v>
+      </c>
+      <c r="I37" s="73">
+        <f t="shared" si="65"/>
+        <v>1.2499783576849457</v>
+      </c>
+      <c r="J37" s="73">
+        <f t="shared" si="65"/>
+        <v>1.3603195367582697</v>
+      </c>
+      <c r="K37" s="73">
+        <f t="shared" ref="K37" si="66">K36/$E36</f>
+        <v>1.3952928673681615</v>
+      </c>
+      <c r="L37" s="73">
+        <f t="shared" ref="L37" si="67">L36/$E36</f>
+        <v>1.4205794550127622</v>
+      </c>
+      <c r="M37" s="73">
+        <f t="shared" ref="M37" si="68">M36/$E36</f>
+        <v>1.4463243059579656</v>
+      </c>
+      <c r="N37" s="73">
+        <f t="shared" ref="N37" si="69">N36/$E36</f>
+        <v>1.4725357252093996</v>
+      </c>
+      <c r="O37" s="73">
+        <f t="shared" ref="O37" si="70">O36/$E36</f>
+        <v>1.4992221682824924</v>
+      </c>
+      <c r="P37" s="73">
+        <f t="shared" ref="P37" si="71">P36/$E36</f>
+        <v>1.5263922439301312</v>
+      </c>
+      <c r="Q37" s="73">
+        <f t="shared" ref="Q37" si="72">Q36/$E36</f>
+        <v>1.5475439465072698</v>
+      </c>
+      <c r="R37" s="73">
+        <f t="shared" ref="R37" si="73">R36/$E36</f>
+        <v>1.5689887549513248</v>
+      </c>
+      <c r="S37" s="73">
+        <f t="shared" ref="S37" si="74">S36/$E36</f>
+        <v>1.5907307309234751</v>
+      </c>
+      <c r="T37" s="73">
+        <f t="shared" ref="T37" si="75">T36/$E36</f>
+        <v>1.6127739923686295</v>
+      </c>
+      <c r="U37" s="73">
+        <f t="shared" ref="U37" si="76">U36/$E36</f>
+        <v>1.6351227142953684</v>
+      </c>
+      <c r="V37" s="73">
+        <f t="shared" ref="V37" si="77">V36/$E36</f>
+        <v>1.6557859790084686</v>
+      </c>
+      <c r="W37" s="73">
+        <f t="shared" ref="W37" si="78">W36/$E36</f>
+        <v>1.6767103681649338</v>
+      </c>
+      <c r="X37" s="73">
+        <f t="shared" ref="X37" si="79">X36/$E36</f>
+        <v>1.6978991816293236</v>
+      </c>
+      <c r="Y37" s="73">
+        <f t="shared" ref="Y37" si="80">Y36/$E36</f>
+        <v>1.7193557609670291</v>
+      </c>
+      <c r="Z37" s="73">
+        <f t="shared" ref="Z37" si="81">Z36/$E36</f>
+        <v>1.7410834899712497</v>
+      </c>
+      <c r="AA37" s="73">
+        <f t="shared" ref="AA37" si="82">AA36/$E36</f>
+        <v>1.7506127508062819</v>
+      </c>
+      <c r="AB37" s="73">
+        <f t="shared" ref="AB37" si="83">AB36/$E36</f>
+        <v>1.7601941669874448</v>
+      </c>
+      <c r="AC37" s="73">
+        <f t="shared" ref="AC37" si="84">AC36/$E36</f>
+        <v>1.7698280239702611</v>
+      </c>
+      <c r="AD37" s="73">
+        <f t="shared" ref="AD37" si="85">AD36/$E36</f>
+        <v>1.7795146087726021</v>
+      </c>
+      <c r="AE37" s="73">
+        <f t="shared" ref="AE37" si="86">AE36/$E36</f>
+        <v>1.7892542099832389</v>
+      </c>
+      <c r="AF37" s="73">
+        <f t="shared" ref="AF37" si="87">AF36/$E36</f>
+        <v>1.7980644584828971</v>
+      </c>
+      <c r="AG37" s="73">
+        <f t="shared" ref="AG37" si="88">AG36/$E36</f>
+        <v>1.8069180884529983</v>
+      </c>
+      <c r="AH37" s="73">
+        <f t="shared" ref="AH37" si="89">AH36/$E36</f>
+        <v>1.815815313502952</v>
+      </c>
+      <c r="AI37" s="73">
+        <f t="shared" ref="AI37" si="90">AI36/$E36</f>
+        <v>1.8247563482939757</v>
+      </c>
+      <c r="AJ37" s="73">
+        <f t="shared" ref="AJ37" si="91">AJ36/$E36</f>
+        <v>1.8337414085442729</v>
+      </c>
+      <c r="AK37" s="73">
+        <f t="shared" ref="AK37" si="92">AK36/$E36</f>
+        <v>1.8369263895829764</v>
+      </c>
+      <c r="AL37" s="73">
+        <f t="shared" ref="AL37" si="93">AL36/$E36</f>
+        <v>1.8401169025381048</v>
+      </c>
+      <c r="AM37" s="73">
+        <f t="shared" ref="AM37" si="94">AM36/$E36</f>
+        <v>1.8433129570179096</v>
+      </c>
+      <c r="AN37" s="73">
+        <f t="shared" ref="AN37" si="95">AN36/$E36</f>
+        <v>1.8465145626473309</v>
+      </c>
+      <c r="AO37" s="73">
+        <f t="shared" ref="AO37" si="96">AO36/$E36</f>
+        <v>1.8497217290680263</v>
+      </c>
+      <c r="AP37" s="73">
+        <f t="shared" ref="AP37" si="97">AP36/$E36</f>
+        <v>1.8529048947920042</v>
+      </c>
+      <c r="AQ37" s="73">
+        <f t="shared" ref="AQ37" si="98">AQ36/$E36</f>
+        <v>1.8560935383907711</v>
+      </c>
+      <c r="AR37" s="73">
+        <f t="shared" ref="AR37" si="99">AR36/$E36</f>
+        <v>1.8592876692911413</v>
+      </c>
+      <c r="AS37" s="73">
+        <f t="shared" ref="AS37" si="100">AS36/$E36</f>
+        <v>1.8624872969361514</v>
+      </c>
+      <c r="AT37" s="73">
+        <f t="shared" ref="AT37" si="101">AT36/$E36</f>
+        <v>1.8656924307850895</v>
+      </c>
+    </row>
+    <row r="38" spans="3:46">
+      <c r="C38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38">
+        <f>E44+E45</f>
+        <v>6003.4063882649998</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ref="F38:AT38" si="102">F44+F45</f>
+        <v>6075.4650161250001</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="102"/>
+        <v>6987.7955309999998</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="102"/>
+        <v>7760.2091208017628</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="102"/>
+        <v>8211</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="102"/>
+        <v>8544.4555111879326</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="102"/>
+        <v>8943.7019173411754</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="102"/>
+        <v>9350.4103583711767</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="102"/>
+        <v>9699.6830655745616</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="102"/>
+        <v>10010.375815500898</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="102"/>
+        <v>10294.550732344846</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="102"/>
+        <v>10577.516277278155</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="102"/>
+        <v>10851.072101638852</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="102"/>
+        <v>11140.646986368889</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="102"/>
+        <v>11435.168318011227</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="102"/>
+        <v>11733.428846177005</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="102"/>
+        <v>12029.77141787775</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="102"/>
+        <v>12344.311592869972</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="102"/>
+        <v>12654.493271975423</v>
+      </c>
+      <c r="X38">
+        <f t="shared" si="102"/>
+        <v>12963.247717721864</v>
+      </c>
+      <c r="Y38">
+        <f t="shared" si="102"/>
+        <v>13269.397348221606</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="102"/>
+        <v>13571.488761336941</v>
+      </c>
+      <c r="AA38">
+        <f t="shared" si="102"/>
+        <v>13877.185006821681</v>
+      </c>
+      <c r="AB38">
+        <f t="shared" si="102"/>
+        <v>14175.947402720092</v>
+      </c>
+      <c r="AC38">
+        <f t="shared" si="102"/>
+        <v>14465.872164011329</v>
+      </c>
+      <c r="AD38">
+        <f t="shared" si="102"/>
+        <v>14745.094069266042</v>
+      </c>
+      <c r="AE38">
+        <f t="shared" si="102"/>
+        <v>15011.528088885952</v>
+      </c>
+      <c r="AF38">
+        <f t="shared" si="102"/>
+        <v>15279.949050443629</v>
+      </c>
+      <c r="AG38">
+        <f t="shared" si="102"/>
+        <v>15532.312779479405</v>
+      </c>
+      <c r="AH38">
+        <f t="shared" si="102"/>
+        <v>15766.558947430789</v>
+      </c>
+      <c r="AI38">
+        <f t="shared" si="102"/>
+        <v>15980.954161897744</v>
+      </c>
+      <c r="AJ38">
+        <f t="shared" si="102"/>
+        <v>16173.674033819889</v>
+      </c>
+      <c r="AK38">
+        <f t="shared" si="102"/>
+        <v>16366.022414249017</v>
+      </c>
+      <c r="AL38">
+        <f t="shared" si="102"/>
+        <v>16531.754833050923</v>
+      </c>
+      <c r="AM38">
+        <f t="shared" si="102"/>
+        <v>16668.417993684769</v>
+      </c>
+      <c r="AN38">
+        <f t="shared" si="102"/>
+        <v>16773.623084200302</v>
+      </c>
+      <c r="AO38">
+        <f t="shared" si="102"/>
+        <v>16845.078331063185</v>
+      </c>
+      <c r="AP38">
+        <f t="shared" si="102"/>
+        <v>16897.924794373586</v>
+      </c>
+      <c r="AQ38">
+        <f t="shared" si="102"/>
+        <v>16913.175165262932</v>
+      </c>
+      <c r="AR38">
+        <f t="shared" si="102"/>
+        <v>16888.958007351808</v>
+      </c>
+      <c r="AS38">
+        <f t="shared" si="102"/>
+        <v>16823.651497812793</v>
+      </c>
+      <c r="AT38">
+        <f t="shared" si="102"/>
+        <v>16692.694553475696</v>
+      </c>
+    </row>
+    <row r="39" spans="3:46">
+      <c r="D39" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="73">
+        <f>E38/$E$38</f>
+        <v>1</v>
+      </c>
+      <c r="F39" s="73">
+        <f t="shared" ref="F39:AT39" si="103">F38/$E$38</f>
+        <v>1.0120029568547708</v>
+      </c>
+      <c r="G39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.1639717652063684</v>
+      </c>
+      <c r="H39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.2926343177384805</v>
+      </c>
+      <c r="I39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.3677235004530488</v>
+      </c>
+      <c r="J39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.423267884694593</v>
+      </c>
+      <c r="K39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.4897711963700544</v>
+      </c>
+      <c r="L39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.5575174748537171</v>
+      </c>
+      <c r="M39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.6156965626273045</v>
+      </c>
+      <c r="N39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.6674493059587663</v>
+      </c>
+      <c r="O39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.7147849181870891</v>
+      </c>
+      <c r="P39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.7619190827984386</v>
+      </c>
+      <c r="Q39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.8074858505080882</v>
+      </c>
+      <c r="R39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.855720946718812</v>
+      </c>
+      <c r="S39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.9047799829716376</v>
+      </c>
+      <c r="T39" s="73">
+        <f t="shared" si="103"/>
+        <v>1.9544618650359262</v>
+      </c>
+      <c r="U39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.0038242690670796</v>
+      </c>
+      <c r="V39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.0562178860654328</v>
+      </c>
+      <c r="W39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.1078854992577982</v>
+      </c>
+      <c r="X39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.1593153751945615</v>
+      </c>
+      <c r="Y39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.2103113615895817</v>
+      </c>
+      <c r="Z39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.2606313621988758</v>
+      </c>
+      <c r="AA39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.3115518273005375</v>
+      </c>
+      <c r="AB39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.3613173065262001</v>
+      </c>
+      <c r="AC39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.4096106824099248</v>
+      </c>
+      <c r="AD39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.4561212611041334</v>
+      </c>
+      <c r="AE39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.5005017348532896</v>
+      </c>
+      <c r="AF39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.5452131776905369</v>
+      </c>
+      <c r="AG39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.587249933611155</v>
+      </c>
+      <c r="AH39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.6262688093629731</v>
+      </c>
+      <c r="AI39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.6619810701364632</v>
+      </c>
+      <c r="AJ39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.6940828236174301</v>
+      </c>
+      <c r="AK39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.7261226969808452</v>
+      </c>
+      <c r="AL39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.7537290937634897</v>
+      </c>
+      <c r="AM39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.776493363212412</v>
+      </c>
+      <c r="AN39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.7940175959082327</v>
+      </c>
+      <c r="AO39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.8059200463241432</v>
+      </c>
+      <c r="AP39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.8147227926139333</v>
+      </c>
+      <c r="AQ39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.8172630788952611</v>
+      </c>
+      <c r="AR39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.8132291760832739</v>
+      </c>
+      <c r="AS39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.8023509337462782</v>
+      </c>
+      <c r="AT39" s="73">
+        <f t="shared" si="103"/>
+        <v>2.7805371607201703</v>
+      </c>
+    </row>
+    <row r="40" spans="3:46">
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40">
+        <f>E46+E47</f>
+        <v>61859.382378924005</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ref="F40:AT40" si="104">F46+F47</f>
+        <v>62040.737315400009</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="104"/>
+        <v>71251.68733320001</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="104"/>
+        <v>68856.53778684001</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="104"/>
+        <v>73950.664132289763</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="104"/>
+        <v>74379.692378560794</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="104"/>
+        <v>74876.185184986811</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="104"/>
+        <v>75362.605315013308</v>
+      </c>
+      <c r="M40">
+        <f>M46+M47</f>
+        <v>75764.758806089143</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="104"/>
+        <v>76111.449975596304</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="104"/>
+        <v>76420.114924364432</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="104"/>
+        <v>76720.194063674731</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="104"/>
+        <v>77003.64240261291</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="104"/>
+        <v>77297.205506841128</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="104"/>
+        <v>77589.131049226096</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="104"/>
+        <v>77878.236359679591</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="104"/>
+        <v>78159.223968975843</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="104"/>
+        <v>78451.168905660481</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="104"/>
+        <v>78732.780574274802</v>
+      </c>
+      <c r="X40">
+        <f t="shared" si="104"/>
+        <v>79007.20705105293</v>
+      </c>
+      <c r="Y40">
+        <f t="shared" si="104"/>
+        <v>79273.763128579594</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="104"/>
+        <v>79531.584323124669</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" si="104"/>
+        <v>79787.504311529177</v>
+      </c>
+      <c r="AB40">
+        <f t="shared" si="104"/>
+        <v>80032.896874308077</v>
+      </c>
+      <c r="AC40">
+        <f t="shared" si="104"/>
+        <v>80266.728749249363</v>
+      </c>
+      <c r="AD40">
+        <f t="shared" si="104"/>
+        <v>80488.059821008399</v>
+      </c>
+      <c r="AE40">
+        <f t="shared" si="104"/>
+        <v>80695.826332643497</v>
+      </c>
+      <c r="AF40">
+        <f t="shared" si="104"/>
+        <v>80901.957924783346</v>
+      </c>
+      <c r="AG40">
+        <f t="shared" si="104"/>
+        <v>81092.840384261945</v>
+      </c>
+      <c r="AH40">
+        <f t="shared" si="104"/>
+        <v>81267.551621759427</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" si="104"/>
+        <v>81425.420783927708</v>
+      </c>
+      <c r="AJ40">
+        <f t="shared" si="104"/>
+        <v>81565.69755611998</v>
+      </c>
+      <c r="AK40">
+        <f t="shared" si="104"/>
+        <v>81704.273984091618</v>
+      </c>
+      <c r="AL40">
+        <f t="shared" si="104"/>
+        <v>81822.472238386777</v>
+      </c>
+      <c r="AM40">
+        <f t="shared" si="104"/>
+        <v>81919.101144218512</v>
+      </c>
+      <c r="AN40">
+        <f t="shared" si="104"/>
+        <v>81992.964580826534</v>
+      </c>
+      <c r="AO40">
+        <f t="shared" si="104"/>
+        <v>82042.862885833936</v>
+      </c>
+      <c r="AP40">
+        <f t="shared" si="104"/>
+        <v>82079.632211043747</v>
+      </c>
+      <c r="AQ40">
+        <f t="shared" si="104"/>
+        <v>82090.214616439785</v>
+      </c>
+      <c r="AR40">
+        <f t="shared" si="104"/>
+        <v>82073.423043590316</v>
+      </c>
+      <c r="AS40">
+        <f t="shared" si="104"/>
+        <v>82028.085485654839</v>
+      </c>
+      <c r="AT40">
+        <f t="shared" si="104"/>
+        <v>81936.86911152293</v>
+      </c>
+    </row>
+    <row r="41" spans="3:46">
+      <c r="D41" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="73">
+        <f>E40/$E40</f>
+        <v>1</v>
+      </c>
+      <c r="F41" s="73">
+        <f t="shared" ref="F41" si="105">F40/$E40</f>
+        <v>1.0029317288582855</v>
+      </c>
+      <c r="G41" s="73">
+        <f t="shared" ref="G41" si="106">G40/$E40</f>
+        <v>1.1518331511417748</v>
+      </c>
+      <c r="H41" s="73">
+        <f t="shared" ref="H41" si="107">H40/$E40</f>
+        <v>1.1131138905502553</v>
+      </c>
+      <c r="I41" s="73">
+        <f t="shared" ref="I41" si="108">I40/$E40</f>
+        <v>1.195463990883384</v>
+      </c>
+      <c r="J41" s="73">
+        <f t="shared" ref="J41" si="109">J40/$E40</f>
+        <v>1.2023995312941009</v>
+      </c>
+      <c r="K41" s="73">
+        <f t="shared" ref="K41" si="110">K40/$E40</f>
+        <v>1.2104256833074645</v>
+      </c>
+      <c r="L41" s="73">
+        <f t="shared" ref="L41" si="111">L40/$E40</f>
+        <v>1.2182890034914082</v>
+      </c>
+      <c r="M41" s="73">
+        <f t="shared" ref="M41" si="112">M40/$E40</f>
+        <v>1.2247900947666559</v>
+      </c>
+      <c r="N41" s="73">
+        <f t="shared" ref="N41" si="113">N40/$E40</f>
+        <v>1.2303945989853287</v>
+      </c>
+      <c r="O41" s="73">
+        <f t="shared" ref="O41" si="114">O40/$E40</f>
+        <v>1.235384382861239</v>
+      </c>
+      <c r="P41" s="73">
+        <f t="shared" ref="P41" si="115">P40/$E40</f>
+        <v>1.2402353711474159</v>
+      </c>
+      <c r="Q41" s="73">
+        <f t="shared" ref="Q41" si="116">Q40/$E40</f>
+        <v>1.2448175109625517</v>
+      </c>
+      <c r="R41" s="73">
+        <f t="shared" ref="R41" si="117">R40/$E40</f>
+        <v>1.2495631630033364</v>
+      </c>
+      <c r="S41" s="73">
+        <f t="shared" ref="S41" si="118">S40/$E40</f>
+        <v>1.2542823427163952</v>
+      </c>
+      <c r="T41" s="73">
+        <f t="shared" ref="T41" si="119">T40/$E40</f>
+        <v>1.2589559314160457</v>
+      </c>
+      <c r="U41" s="73">
+        <f t="shared" ref="U41" si="120">U40/$E40</f>
+        <v>1.2634982918226698</v>
+      </c>
+      <c r="V41" s="73">
+        <f t="shared" ref="V41" si="121">V40/$E40</f>
+        <v>1.2682177850580907</v>
+      </c>
+      <c r="W41" s="73">
+        <f t="shared" ref="W41" si="122">W40/$E40</f>
+        <v>1.2727702338182365</v>
+      </c>
+      <c r="X41" s="73">
+        <f t="shared" ref="X41" si="123">X40/$E40</f>
+        <v>1.2772065289480052</v>
+      </c>
+      <c r="Y41" s="73">
+        <f t="shared" ref="Y41" si="124">Y40/$E40</f>
+        <v>1.2815155935922957</v>
+      </c>
+      <c r="Z41" s="73">
+        <f t="shared" ref="Z41" si="125">Z40/$E40</f>
+        <v>1.2856834527695145</v>
+      </c>
+      <c r="AA41" s="73">
+        <f t="shared" ref="AA41" si="126">AA40/$E40</f>
+        <v>1.289820577625318</v>
+      </c>
+      <c r="AB41" s="73">
+        <f t="shared" ref="AB41" si="127">AB40/$E40</f>
+        <v>1.2937875193137385</v>
+      </c>
+      <c r="AC41" s="73">
+        <f t="shared" ref="AC41" si="128">AC40/$E40</f>
+        <v>1.2975675744314721</v>
+      </c>
+      <c r="AD41" s="73">
+        <f t="shared" ref="AD41" si="129">AD40/$E40</f>
+        <v>1.3011455453592007</v>
+      </c>
+      <c r="AE41" s="73">
+        <f t="shared" ref="AE41" si="130">AE40/$E40</f>
+        <v>1.304504235725076</v>
+      </c>
+      <c r="AF41" s="73">
+        <f t="shared" ref="AF41" si="131">AF40/$E40</f>
+        <v>1.3078364964786215</v>
+      </c>
+      <c r="AG41" s="73">
+        <f t="shared" ref="AG41" si="132">AG40/$E40</f>
+        <v>1.3109222443819766</v>
+      </c>
+      <c r="AH41" s="73">
+        <f t="shared" ref="AH41" si="133">AH40/$E40</f>
+        <v>1.3137465732190683</v>
+      </c>
+      <c r="AI41" s="73">
+        <f t="shared" ref="AI41" si="134">AI40/$E40</f>
+        <v>1.3162986381782888</v>
+      </c>
+      <c r="AJ41" s="73">
+        <f t="shared" ref="AJ41" si="135">AJ40/$E40</f>
+        <v>1.3185663099007932</v>
+      </c>
+      <c r="AK41" s="73">
+        <f t="shared" ref="AK41" si="136">AK40/$E40</f>
+        <v>1.3208064943747149</v>
+      </c>
+      <c r="AL41" s="73">
+        <f t="shared" ref="AL41" si="137">AL40/$E40</f>
+        <v>1.3227172514781582</v>
+      </c>
+      <c r="AM41" s="73">
+        <f t="shared" ref="AM41" si="138">AM40/$E40</f>
+        <v>1.3242793250410632</v>
+      </c>
+      <c r="AN41" s="73">
+        <f t="shared" ref="AN41" si="139">AN40/$E40</f>
+        <v>1.3254733789382644</v>
+      </c>
+      <c r="AO41" s="73">
+        <f t="shared" ref="AO41" si="140">AO40/$E40</f>
+        <v>1.3262800197918982</v>
+      </c>
+      <c r="AP41" s="73">
+        <f t="shared" ref="AP41" si="141">AP40/$E40</f>
+        <v>1.3268744215430277</v>
+      </c>
+      <c r="AQ41" s="73">
+        <f t="shared" ref="AQ41" si="142">AQ40/$E40</f>
+        <v>1.3270454934966922</v>
+      </c>
+      <c r="AR41" s="73">
+        <f t="shared" ref="AR41" si="143">AR40/$E40</f>
+        <v>1.3267740460265798</v>
+      </c>
+      <c r="AS41" s="73">
+        <f t="shared" ref="AS41" si="144">AS40/$E40</f>
+        <v>1.3260411328258344</v>
+      </c>
+      <c r="AT41" s="73">
+        <f t="shared" ref="AT41" si="145">AT40/$E40</f>
+        <v>1.3245665566075793</v>
+      </c>
+    </row>
+    <row r="43" spans="3:46">
+      <c r="E43">
+        <v>2019</v>
+      </c>
+      <c r="F43">
+        <v>2020</v>
+      </c>
+      <c r="G43">
+        <v>2021</v>
+      </c>
+      <c r="H43">
+        <v>2022</v>
+      </c>
+      <c r="I43">
+        <v>2023</v>
+      </c>
+      <c r="J43">
+        <v>2024</v>
+      </c>
+      <c r="K43">
+        <v>2025</v>
+      </c>
+      <c r="L43">
+        <v>2026</v>
+      </c>
+      <c r="M43">
+        <v>2027</v>
+      </c>
+      <c r="N43">
+        <v>2028</v>
+      </c>
+      <c r="O43">
+        <v>2029</v>
+      </c>
+      <c r="P43">
+        <v>2030</v>
+      </c>
+      <c r="Q43">
+        <v>2031</v>
+      </c>
+      <c r="R43">
+        <v>2032</v>
+      </c>
+      <c r="S43">
+        <v>2033</v>
+      </c>
+      <c r="T43">
+        <v>2034</v>
+      </c>
+      <c r="U43">
+        <v>2035</v>
+      </c>
+      <c r="V43">
+        <v>2036</v>
+      </c>
+      <c r="W43">
+        <v>2037</v>
+      </c>
+      <c r="X43">
+        <v>2038</v>
+      </c>
+      <c r="Y43">
+        <v>2039</v>
+      </c>
+      <c r="Z43">
+        <v>2040</v>
+      </c>
+      <c r="AA43">
+        <v>2041</v>
+      </c>
+      <c r="AB43">
+        <v>2042</v>
+      </c>
+      <c r="AC43">
+        <v>2043</v>
+      </c>
+      <c r="AD43">
+        <v>2044</v>
+      </c>
+      <c r="AE43">
+        <v>2045</v>
+      </c>
+      <c r="AF43">
+        <v>2046</v>
+      </c>
+      <c r="AG43">
+        <v>2047</v>
+      </c>
+      <c r="AH43">
+        <v>2048</v>
+      </c>
+      <c r="AI43">
+        <v>2049</v>
+      </c>
+      <c r="AJ43">
+        <v>2050</v>
+      </c>
+      <c r="AK43">
+        <v>2051</v>
+      </c>
+      <c r="AL43">
+        <v>2052</v>
+      </c>
+      <c r="AM43">
+        <v>2053</v>
+      </c>
+      <c r="AN43">
+        <v>2054</v>
+      </c>
+      <c r="AO43">
+        <v>2055</v>
+      </c>
+      <c r="AP43">
+        <v>2056</v>
+      </c>
+      <c r="AQ43">
+        <v>2057</v>
+      </c>
+      <c r="AR43">
+        <v>2058</v>
+      </c>
+      <c r="AS43">
+        <v>2059</v>
+      </c>
+      <c r="AT43">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="44" spans="3:46">
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44">
+        <f>2.5*1.2*13334090/10^4*0.91351</f>
+        <v>3654.2473667700001</v>
+      </c>
+      <c r="F44">
+        <f>2.5*1.2*14670670/10^4*0.84025</f>
+        <v>3698.1091402500001</v>
+      </c>
+      <c r="G44">
+        <f>2.5*1.2*15788570/10^4*0.898</f>
+        <v>4253.4407579999997</v>
+      </c>
+      <c r="H44">
+        <v>4723.6055517923769</v>
+      </c>
+      <c r="I44">
+        <v>4997.9999999999991</v>
+      </c>
+      <c r="J44">
+        <v>5200.9729198535242</v>
+      </c>
+      <c r="K44">
+        <v>5443.9924714250628</v>
+      </c>
+      <c r="L44">
+        <v>5691.5541311824545</v>
+      </c>
+      <c r="M44">
+        <v>5904.1549094801676</v>
+      </c>
+      <c r="N44">
+        <v>6093.272235522285</v>
+      </c>
+      <c r="O44">
+        <v>6266.2482718620804</v>
+      </c>
+      <c r="P44">
+        <v>6438.4881687780071</v>
+      </c>
+      <c r="Q44">
+        <v>6605.0004096932153</v>
+      </c>
+      <c r="R44">
+        <v>6781.2633830071491</v>
+      </c>
+      <c r="S44">
+        <v>6960.537237050311</v>
+      </c>
+      <c r="T44">
+        <v>7142.0871237599149</v>
+      </c>
+      <c r="U44">
+        <v>7322.4695587081951</v>
+      </c>
+      <c r="V44">
+        <v>7513.9287956599828</v>
+      </c>
+      <c r="W44">
+        <v>7702.7350351154755</v>
+      </c>
+      <c r="X44">
+        <v>7890.6725238306999</v>
+      </c>
+      <c r="Y44">
+        <v>8077.0244728305443</v>
+      </c>
+      <c r="Z44">
+        <v>8260.9062025529201</v>
+      </c>
+      <c r="AA44">
+        <v>8446.982178065371</v>
+      </c>
+      <c r="AB44">
+        <v>8628.8375494817956</v>
+      </c>
+      <c r="AC44">
+        <v>8805.3134911373309</v>
+      </c>
+      <c r="AD44">
+        <v>8975.274650857591</v>
+      </c>
+      <c r="AE44">
+        <v>9137.4518801914492</v>
+      </c>
+      <c r="AF44">
+        <v>9300.8385524439473</v>
+      </c>
+      <c r="AG44">
+        <v>9454.4512570744191</v>
+      </c>
+      <c r="AH44">
+        <v>9597.035881044827</v>
+      </c>
+      <c r="AI44">
+        <v>9727.5373159377559</v>
+      </c>
+      <c r="AJ44">
+        <v>9844.8450640642805</v>
+      </c>
+      <c r="AK44">
+        <v>9961.9266869341845</v>
+      </c>
+      <c r="AL44">
+        <v>10062.807289683171</v>
+      </c>
+      <c r="AM44">
+        <v>10145.993561373336</v>
+      </c>
+      <c r="AN44">
+        <v>10210.031442556707</v>
+      </c>
+      <c r="AO44">
+        <v>10253.525940647156</v>
+      </c>
+      <c r="AP44">
+        <v>10285.693353096967</v>
+      </c>
+      <c r="AQ44">
+        <v>10294.976187551349</v>
+      </c>
+      <c r="AR44">
+        <v>10280.235308822841</v>
+      </c>
+      <c r="AS44">
+        <v>10240.483520407786</v>
+      </c>
+      <c r="AT44">
+        <v>10160.770597767814</v>
+      </c>
+    </row>
+    <row r="45" spans="3:46">
+      <c r="C45" t="s">
+        <v>119</v>
+      </c>
+      <c r="E45">
+        <f>2.5*1.8/10^4*5714610*0.91351</f>
+        <v>2349.1590214949997</v>
+      </c>
+      <c r="F45">
+        <f>2.5*1.8/10^4*6287430*0.84025</f>
+        <v>2377.355875875</v>
+      </c>
+      <c r="G45">
+        <f>2.5*1.8/10^4*6766530*0.898</f>
+        <v>2734.354773</v>
+      </c>
+      <c r="H45">
+        <v>3036.6035690093854</v>
+      </c>
+      <c r="I45">
+        <v>3213</v>
+      </c>
+      <c r="J45">
+        <v>3343.4825913344089</v>
+      </c>
+      <c r="K45">
+        <v>3499.7094459161126</v>
+      </c>
+      <c r="L45">
+        <v>3658.8562271887213</v>
+      </c>
+      <c r="M45">
+        <v>3795.5281560943931</v>
+      </c>
+      <c r="N45">
+        <v>3917.1035799786123</v>
+      </c>
+      <c r="O45">
+        <v>4028.3024604827656</v>
+      </c>
+      <c r="P45">
+        <v>4139.028108500147</v>
+      </c>
+      <c r="Q45">
+        <v>4246.0716919456381</v>
+      </c>
+      <c r="R45">
+        <v>4359.3836033617399</v>
+      </c>
+      <c r="S45">
+        <v>4474.6310809609158</v>
+      </c>
+      <c r="T45">
+        <v>4591.3417224170889</v>
+      </c>
+      <c r="U45">
+        <v>4707.3018591695545</v>
+      </c>
+      <c r="V45">
+        <v>4830.3827972099889</v>
+      </c>
+      <c r="W45">
+        <v>4951.7582368599478</v>
+      </c>
+      <c r="X45">
+        <v>5072.5751938911635</v>
+      </c>
+      <c r="Y45">
+        <v>5192.3728753910627</v>
+      </c>
+      <c r="Z45">
+        <v>5310.5825587840209</v>
+      </c>
+      <c r="AA45">
+        <v>5430.2028287563089</v>
+      </c>
+      <c r="AB45">
+        <v>5547.1098532382966</v>
+      </c>
+      <c r="AC45">
+        <v>5660.5586728739981</v>
+      </c>
+      <c r="AD45">
+        <v>5769.8194184084514</v>
+      </c>
+      <c r="AE45">
+        <v>5874.0762086945042</v>
+      </c>
+      <c r="AF45">
+        <v>5979.1104979996808</v>
+      </c>
+      <c r="AG45">
+        <v>6077.8615224049863</v>
+      </c>
+      <c r="AH45">
+        <v>6169.523066385962</v>
+      </c>
+      <c r="AI45">
+        <v>6253.4168459599878</v>
+      </c>
+      <c r="AJ45">
+        <v>6328.8289697556083</v>
+      </c>
+      <c r="AK45">
+        <v>6404.0957273148324</v>
+      </c>
+      <c r="AL45">
+        <v>6468.9475433677535</v>
+      </c>
+      <c r="AM45">
+        <v>6522.4244323114317</v>
+      </c>
+      <c r="AN45">
+        <v>6563.5916416435966</v>
+      </c>
+      <c r="AO45">
+        <v>6591.55239041603</v>
+      </c>
+      <c r="AP45">
+        <v>6612.23144127662</v>
+      </c>
+      <c r="AQ45">
+        <v>6618.1989777115814</v>
+      </c>
+      <c r="AR45">
+        <v>6608.722698528969</v>
+      </c>
+      <c r="AS45">
+        <v>6583.1679774050053</v>
+      </c>
+      <c r="AT45">
+        <v>6531.9239557078799</v>
+      </c>
+    </row>
+    <row r="46" spans="3:46">
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46">
+        <f>6*2.92*0.91351/10^4*1162700</f>
+        <v>1860.865910904</v>
+      </c>
+      <c r="F46">
+        <f>6*2.92/10^4*0.84025*1061900</f>
+        <v>1563.2421041999999</v>
+      </c>
+      <c r="G46">
+        <f>6*2.92*0.898/10^4*958800</f>
+        <v>1508.4762048</v>
+      </c>
+      <c r="H46">
+        <f>6*2.92*0.87/10^4*966321</f>
+        <v>1472.90512104</v>
+      </c>
+      <c r="I46">
+        <v>1298.365849516618</v>
+      </c>
+      <c r="J46">
+        <v>1305.8983798863226</v>
+      </c>
+      <c r="K46">
+        <v>1314.6153983466447</v>
+      </c>
+      <c r="L46">
+        <v>1323.1555689151476</v>
+      </c>
+      <c r="M46">
+        <v>1330.216254105786</v>
+      </c>
+      <c r="N46">
+        <v>1336.3031767872624</v>
+      </c>
+      <c r="O46">
+        <v>1341.722465892042</v>
+      </c>
+      <c r="P46">
+        <v>1346.9910123101765</v>
+      </c>
+      <c r="Q46">
+        <v>1351.9675686088622</v>
+      </c>
+      <c r="R46">
+        <v>1357.1217117620079</v>
+      </c>
+      <c r="S46">
+        <v>1362.2471039309842</v>
+      </c>
+      <c r="T46">
+        <v>1367.3229807525261</v>
+      </c>
+      <c r="U46">
+        <v>1372.2563335537254</v>
+      </c>
+      <c r="V46">
+        <v>1377.3820662321032</v>
+      </c>
+      <c r="W46">
+        <v>1382.3263757612256</v>
+      </c>
+      <c r="X46">
+        <v>1387.14453351319</v>
+      </c>
+      <c r="Y46">
+        <v>1391.8245091713204</v>
+      </c>
+      <c r="Z46">
+        <v>1396.3511248306481</v>
+      </c>
+      <c r="AA46">
+        <v>1400.8443606528265</v>
+      </c>
+      <c r="AB46">
+        <v>1405.1527644646915</v>
+      </c>
+      <c r="AC46">
+        <v>1409.2581950854242</v>
+      </c>
+      <c r="AD46">
+        <v>1413.1441467314401</v>
+      </c>
+      <c r="AE46">
+        <v>1416.7919428201626</v>
+      </c>
+      <c r="AF46">
+        <v>1420.4110343169218</v>
+      </c>
+      <c r="AG46">
+        <v>1423.7623938965385</v>
+      </c>
+      <c r="AH46">
+        <v>1426.8298322617668</v>
+      </c>
+      <c r="AI46">
+        <v>1429.6015711130153</v>
+      </c>
+      <c r="AJ46">
+        <v>1432.0644370335842</v>
+      </c>
+      <c r="AK46">
+        <v>1434.4974496878658</v>
+      </c>
+      <c r="AL46">
+        <v>1436.5726788781647</v>
+      </c>
+      <c r="AM46">
+        <v>1438.269210922605</v>
+      </c>
+      <c r="AN46">
+        <v>1439.5660453019184</v>
+      </c>
+      <c r="AO46">
+        <v>1440.4421193159999</v>
+      </c>
+      <c r="AP46">
+        <v>1441.0876853392715</v>
+      </c>
+      <c r="AQ46">
+        <v>1441.2734826398525</v>
+      </c>
+      <c r="AR46">
+        <v>1440.978669807497</v>
+      </c>
+      <c r="AS46">
+        <v>1440.1826696956034</v>
+      </c>
+      <c r="AT46">
+        <v>1438.5811664977721</v>
+      </c>
+    </row>
+    <row r="47" spans="3:46">
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47">
+        <f>6*14.27*0.91351/10^4*7671000</f>
+        <v>59998.516468020003</v>
+      </c>
+      <c r="F47">
+        <f>6*14.27/10^4*0.84025*8406400</f>
+        <v>60477.49521120001</v>
+      </c>
+      <c r="G47">
+        <f>6*14.27*0.898/10^4*9070900</f>
+        <v>69743.211128400013</v>
+      </c>
+      <c r="H47">
+        <f>6*14.27*0.87/10^4*9046070</f>
+        <v>67383.632665800003</v>
+      </c>
+      <c r="I47">
+        <v>72652.298282773147</v>
+      </c>
+      <c r="J47">
+        <v>73073.793998674475</v>
+      </c>
+      <c r="K47">
+        <v>73561.569786640161</v>
+      </c>
+      <c r="L47">
+        <v>74039.449746098166</v>
+      </c>
+      <c r="M47">
+        <v>74434.542551983352</v>
+      </c>
+      <c r="N47">
+        <v>74775.146798809044</v>
+      </c>
+      <c r="O47">
+        <v>75078.392458472386</v>
+      </c>
+      <c r="P47">
+        <v>75373.203051364559</v>
+      </c>
+      <c r="Q47">
+        <v>75651.67483400405</v>
+      </c>
+      <c r="R47">
+        <v>75940.083795079117</v>
+      </c>
+      <c r="S47">
+        <v>76226.883945295107</v>
+      </c>
+      <c r="T47">
+        <v>76510.913378927071</v>
+      </c>
+      <c r="U47">
+        <v>76786.967635422116</v>
+      </c>
+      <c r="V47">
+        <v>77073.786839428372</v>
+      </c>
+      <c r="W47">
+        <v>77350.454198513573</v>
+      </c>
+      <c r="X47">
+        <v>77620.062517539744</v>
+      </c>
+      <c r="Y47">
+        <v>77881.938619408276</v>
+      </c>
+      <c r="Z47">
+        <v>78135.233198294023</v>
+      </c>
+      <c r="AA47">
+        <v>78386.659950876347</v>
+      </c>
+      <c r="AB47">
+        <v>78627.744109843392</v>
+      </c>
+      <c r="AC47">
+        <v>78857.470554163941</v>
+      </c>
+      <c r="AD47">
+        <v>79074.915674276956</v>
+      </c>
+      <c r="AE47">
+        <v>79279.03438982334</v>
+      </c>
+      <c r="AF47">
+        <v>79481.54689046643</v>
+      </c>
+      <c r="AG47">
+        <v>79669.077990365404</v>
+      </c>
+      <c r="AH47">
+        <v>79840.721789497664</v>
+      </c>
+      <c r="AI47">
+        <v>79995.819212814691</v>
+      </c>
+      <c r="AJ47">
+        <v>80133.6331190864</v>
+      </c>
+      <c r="AK47">
+        <v>80269.776534403747</v>
+      </c>
+      <c r="AL47">
+        <v>80385.899559508616</v>
+      </c>
+      <c r="AM47">
+        <v>80480.831933295907</v>
+      </c>
+      <c r="AN47">
+        <v>80553.398535524611</v>
+      </c>
+      <c r="AO47">
+        <v>80602.420766517942</v>
+      </c>
+      <c r="AP47">
+        <v>80638.544525704478</v>
+      </c>
+      <c r="AQ47">
+        <v>80648.941133799934</v>
+      </c>
+      <c r="AR47">
+        <v>80632.444373782811</v>
+      </c>
+      <c r="AS47">
+        <v>80587.902815959242</v>
+      </c>
+      <c r="AT47">
+        <v>80498.287945025164</v>
       </c>
     </row>
   </sheetData>
@@ -13534,991 +19228,1014 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AP7"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:AQ7"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="81">
+    <row r="1" spans="1:43" ht="77.45">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B1">
+        <v>2019</v>
+      </c>
+      <c r="C1">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>2050</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>2051</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>2052</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>2053</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>2054</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>2055</v>
       </c>
-      <c r="AL1">
+      <c r="AM1">
         <v>2056</v>
       </c>
-      <c r="AM1">
+      <c r="AN1">
         <v>2057</v>
       </c>
-      <c r="AN1">
+      <c r="AO1">
         <v>2058</v>
       </c>
-      <c r="AO1">
+      <c r="AP1">
         <v>2059</v>
       </c>
-      <c r="AP1">
+      <c r="AQ1">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <f>passenger!AK21</f>
+        <f>passenger!E36</f>
         <v>1</v>
       </c>
       <c r="C2">
-        <f>passenger!AL21*'raw data'!U22/'raw data'!$T22</f>
-        <v>0.79341313120211276</v>
+        <f>passenger!F36</f>
+        <v>0.93176953330484824</v>
       </c>
       <c r="D2">
-        <f>passenger!AM21*'raw data'!V22/'raw data'!$T22</f>
-        <v>0.53439809369943159</v>
+        <f>passenger!G36</f>
+        <v>0.98544581794857811</v>
       </c>
       <c r="E2">
-        <f>passenger!AN21*'raw data'!W22/'raw data'!$T22</f>
-        <v>1.7768895171187165</v>
+        <f>passenger!H36</f>
+        <v>0.95487307061576332</v>
       </c>
       <c r="F2">
-        <f>passenger!AO21/'raw data'!$T22</f>
-        <v>2.0235490064021762</v>
+        <f>passenger!I36</f>
+        <v>0.92847419815695842</v>
       </c>
       <c r="G2">
-        <f>passenger!AP21/'raw data'!$T22</f>
-        <v>2.0523256721604142</v>
+        <f>passenger!J36</f>
+        <v>0.91612681141496144</v>
       </c>
       <c r="H2">
-        <f>passenger!AQ21/'raw data'!$T22</f>
-        <v>2.0811023379186526</v>
+        <f>passenger!K36</f>
+        <v>0.9639065212252057</v>
       </c>
       <c r="I2">
-        <f>passenger!AR21/'raw data'!$T22</f>
-        <v>2.1098790036768906</v>
+        <f>passenger!L36</f>
+        <v>1.007687069095907</v>
       </c>
       <c r="J2">
-        <f>passenger!AS21/'raw data'!$T22</f>
-        <v>2.1386556694351291</v>
+        <f>passenger!M36</f>
+        <v>1.0411015680975508</v>
       </c>
       <c r="K2">
-        <f>passenger!AT21/'raw data'!$T22</f>
-        <v>2.1674323351933666</v>
+        <f>passenger!N36</f>
+        <v>1.0674045241183117</v>
       </c>
       <c r="L2">
-        <f>passenger!AU21/'raw data'!$T22</f>
-        <v>2.1962090009516055</v>
+        <f>passenger!O36</f>
+        <v>1.0885588949344038</v>
       </c>
       <c r="M2">
-        <f>passenger!AV21/'raw data'!$T22</f>
-        <v>2.1896724466087609</v>
+        <f>passenger!P36</f>
+        <v>1.1069691399758801</v>
       </c>
       <c r="N2">
-        <f>passenger!AW21/'raw data'!$T22</f>
-        <v>2.1831358922659168</v>
+        <f>passenger!Q36</f>
+        <v>1.1222554793931736</v>
       </c>
       <c r="O2">
-        <f>passenger!AX21/'raw data'!$T22</f>
-        <v>2.176599337923073</v>
+        <f>passenger!R36</f>
+        <v>1.1360718178150595</v>
       </c>
       <c r="P2">
-        <f>passenger!AY21/'raw data'!$T22</f>
-        <v>2.1700627835802289</v>
+        <f>passenger!S36</f>
+        <v>1.1477068418857206</v>
       </c>
       <c r="Q2">
-        <f>passenger!AZ21/'raw data'!$T22</f>
-        <v>2.1635262292373847</v>
+        <f>passenger!T36</f>
+        <v>1.1571701293353269</v>
       </c>
       <c r="R2">
-        <f>passenger!BA21/'raw data'!$T22</f>
-        <v>2.1569896748945401</v>
+        <f>passenger!U36</f>
+        <v>1.1641104214519824</v>
       </c>
       <c r="S2">
-        <f>passenger!BB21/'raw data'!$T22</f>
-        <v>2.1504531205516964</v>
+        <f>passenger!V36</f>
+        <v>1.1695724791191184</v>
       </c>
       <c r="T2">
-        <f>passenger!BC21/'raw data'!$T22</f>
-        <v>2.1439165662088517</v>
+        <f>passenger!W36</f>
+        <v>1.1729195343857188</v>
       </c>
       <c r="U2">
-        <f>passenger!BD21/'raw data'!$T22</f>
-        <v>2.137380011866008</v>
+        <f>passenger!X36</f>
+        <v>1.1744435698424076</v>
       </c>
       <c r="V2">
-        <f>passenger!BE21/'raw data'!$T22</f>
-        <v>2.1308434575231634</v>
+        <f>passenger!Y36</f>
+        <v>1.1743052991837069</v>
       </c>
       <c r="W2">
-        <f>passenger!BF21/'raw data'!$T22</f>
-        <v>2.1122243091622086</v>
+        <f>passenger!Z36</f>
+        <v>1.1726448868461425</v>
       </c>
       <c r="X2">
-        <f>passenger!BG21/'raw data'!$T22</f>
-        <v>2.0936051608012538</v>
+        <f>passenger!AA36</f>
+        <v>1.1697033499117306</v>
       </c>
       <c r="Y2">
-        <f>passenger!BH21/'raw data'!$T22</f>
-        <v>2.074986012440299</v>
+        <f>passenger!AB36</f>
+        <v>1.1654578178816104</v>
       </c>
       <c r="Z2">
-        <f>passenger!BI21/'raw data'!$T22</f>
-        <v>2.0563668640793442</v>
+        <f>passenger!AC36</f>
+        <v>1.1600214360864807</v>
       </c>
       <c r="AA2">
-        <f>passenger!BJ21/'raw data'!$T22</f>
-        <v>2.0377477157183885</v>
+        <f>passenger!AD36</f>
+        <v>1.1535097225613236</v>
       </c>
       <c r="AB2">
-        <f>passenger!BK21/'raw data'!$T22</f>
-        <v>2.0191285673574342</v>
+        <f>passenger!AE36</f>
+        <v>1.1460124350708616</v>
       </c>
       <c r="AC2">
-        <f>passenger!BL21/'raw data'!$T22</f>
-        <v>2.0005094189964789</v>
+        <f>passenger!AF36</f>
+        <v>1.1376748785825224</v>
       </c>
       <c r="AD2">
-        <f>passenger!BM21/'raw data'!$T22</f>
-        <v>1.9818902706355241</v>
+        <f>passenger!AG36</f>
+        <v>1.1285095131661682</v>
       </c>
       <c r="AE2">
-        <f>passenger!BN21/'raw data'!$T22</f>
-        <v>1.9632711222745696</v>
+        <f>passenger!AH36</f>
+        <v>1.1185986129913399</v>
       </c>
       <c r="AF2">
-        <f>passenger!BO21/'raw data'!$T22</f>
-        <v>1.9446519739136141</v>
+        <f>passenger!AI36</f>
+        <v>1.108042685107397</v>
       </c>
       <c r="AG2">
-        <f>passenger!BP21/'raw data'!$T22</f>
-        <v>1.9169979707416107</v>
+        <f>passenger!AJ36</f>
+        <v>1.0969208380030395</v>
       </c>
       <c r="AH2">
-        <f>passenger!BQ21/'raw data'!$T22</f>
-        <v>1.8893439675696078</v>
+        <f>passenger!AK36</f>
+        <v>1.0854850327805792</v>
       </c>
       <c r="AI2">
-        <f>passenger!BR21/'raw data'!$T22</f>
-        <v>1.8616899643976044</v>
+        <f>passenger!AL36</f>
+        <v>1.073426035748577</v>
       </c>
       <c r="AJ2">
-        <f>passenger!BS21/'raw data'!$T22</f>
-        <v>1.8340359612256012</v>
+        <f>passenger!AM36</f>
+        <v>1.0607539543804403</v>
       </c>
       <c r="AK2">
-        <f>passenger!BT21/'raw data'!$T22</f>
-        <v>1.8063819580535978</v>
+        <f>passenger!AN36</f>
+        <v>1.0474713860956908</v>
       </c>
       <c r="AL2">
-        <f>passenger!BU21/'raw data'!$T22</f>
-        <v>1.7787279548815946</v>
+        <f>passenger!AO36</f>
+        <v>1.0335746442302569</v>
       </c>
       <c r="AM2">
-        <f>passenger!BV21/'raw data'!$T22</f>
-        <v>1.751073951709591</v>
+        <f>passenger!AP36</f>
+        <v>1.019051278313561</v>
       </c>
       <c r="AN2">
-        <f>passenger!BW21/'raw data'!$T22</f>
-        <v>1.7234199485375878</v>
+        <f>passenger!AQ36</f>
+        <v>1.0038884088115476</v>
       </c>
       <c r="AO2">
-        <f>passenger!BX21/'raw data'!$T22</f>
-        <v>1.6957659453655847</v>
+        <f>passenger!AR36</f>
+        <v>0.98806988795540396</v>
       </c>
       <c r="AP2">
-        <f>passenger!BY21/'raw data'!$T22</f>
-        <v>1.6681119421935813</v>
+        <f>passenger!AS36</f>
+        <v>0.97157615633255356</v>
+      </c>
+      <c r="AQ2">
+        <f>passenger!AT36</f>
+        <v>0.95439536050067719</v>
       </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:43">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <f>passenger!AK22</f>
+        <f>passenger!E38</f>
         <v>1</v>
       </c>
       <c r="C3">
-        <f>passenger!AL22*'raw data'!U22/'raw data'!$T22</f>
-        <v>0.79341313120211276</v>
+        <f>passenger!F38</f>
+        <v>0.72638681616108225</v>
       </c>
       <c r="D3">
-        <f>passenger!AM22*'raw data'!V22/'raw data'!$T22</f>
-        <v>0.53439809369943159</v>
+        <f>passenger!G38</f>
+        <v>0.70959871205371039</v>
       </c>
       <c r="E3">
-        <f>passenger!AN22*'raw data'!W22/'raw data'!$T22</f>
-        <v>1.7768895171187162</v>
+        <f>passenger!H38</f>
+        <v>0.64426415785036162</v>
       </c>
       <c r="F3">
-        <f>passenger!AO22/'raw data'!$T22</f>
-        <v>2.0235490064021762</v>
+        <f>passenger!I38</f>
+        <v>0.76400637311512787</v>
       </c>
       <c r="G3">
-        <f>passenger!AP22/'raw data'!$T22</f>
-        <v>2.0523256721604142</v>
+        <f>passenger!J38</f>
+        <v>0.76112540281291752</v>
       </c>
       <c r="H3">
-        <f>passenger!AQ22/'raw data'!$T22</f>
-        <v>2.0811023379186526</v>
+        <f>passenger!K38</f>
+        <v>0.75782468436877115</v>
       </c>
       <c r="I3">
-        <f>passenger!AR22/'raw data'!$T22</f>
-        <v>2.1098790036768906</v>
+        <f>passenger!L38</f>
+        <v>0.75462803352260688</v>
       </c>
       <c r="J3">
-        <f>passenger!AS22/'raw data'!$T22</f>
-        <v>2.1386556694351291</v>
+        <f>passenger!M38</f>
+        <v>0.75201467523568954</v>
       </c>
       <c r="K3">
-        <f>passenger!AT22/'raw data'!$T22</f>
-        <v>2.1674323351933666</v>
+        <f>passenger!N38</f>
+        <v>0.74978241667076462</v>
       </c>
       <c r="L3">
-        <f>passenger!AU22/'raw data'!$T22</f>
-        <v>2.1962090009516055</v>
+        <f>passenger!O38</f>
+        <v>0.74781065381441392</v>
       </c>
       <c r="M3">
-        <f>passenger!AV22/'raw data'!$T22</f>
-        <v>2.1896724466087605</v>
+        <f>passenger!P38</f>
+        <v>0.74590712379009938</v>
       </c>
       <c r="N3">
-        <f>passenger!AW22/'raw data'!$T22</f>
-        <v>2.1831358922659168</v>
+        <f>passenger!Q38</f>
+        <v>0.74412124742575536</v>
       </c>
       <c r="O3">
-        <f>passenger!AX22/'raw data'!$T22</f>
-        <v>2.176599337923073</v>
+        <f>passenger!R38</f>
+        <v>0.74228341046450175</v>
       </c>
       <c r="P3">
-        <f>passenger!AY22/'raw data'!$T22</f>
-        <v>2.1700627835802289</v>
+        <f>passenger!S38</f>
+        <v>0.74046782072253237</v>
       </c>
       <c r="Q3">
-        <f>passenger!AZ22/'raw data'!$T22</f>
-        <v>2.1635262292373847</v>
+        <f>passenger!T38</f>
+        <v>0.73868146091580356</v>
       </c>
       <c r="R3">
-        <f>passenger!BA22/'raw data'!$T22</f>
-        <v>2.1569896748945401</v>
+        <f>passenger!U38</f>
+        <v>0.73733244555008315</v>
       </c>
       <c r="S3">
-        <f>passenger!BB22/'raw data'!$T22</f>
-        <v>2.1504531205516964</v>
+        <f>passenger!V38</f>
+        <v>0.7359394272620593</v>
       </c>
       <c r="T3">
-        <f>passenger!BC22/'raw data'!$T22</f>
-        <v>2.1439165662088517</v>
+        <f>passenger!W38</f>
+        <v>0.73460424937675406</v>
       </c>
       <c r="U3">
-        <f>passenger!BD22/'raw data'!$T22</f>
-        <v>2.137380011866008</v>
+        <f>passenger!X38</f>
+        <v>0.73331107933473672</v>
       </c>
       <c r="V3">
-        <f>passenger!BE22/'raw data'!$T22</f>
-        <v>2.1308434575231638</v>
+        <f>passenger!Y38</f>
+        <v>0.73206243982074692</v>
       </c>
       <c r="W3">
-        <f>passenger!BF22/'raw data'!$T22</f>
-        <v>2.1122243091622086</v>
+        <f>passenger!Z38</f>
+        <v>0.7308616437230282</v>
       </c>
       <c r="X3">
-        <f>passenger!BG22/'raw data'!$T22</f>
-        <v>2.0936051608012538</v>
+        <f>passenger!AA38</f>
+        <v>0.72967629119409061</v>
       </c>
       <c r="Y3">
-        <f>passenger!BH22/'raw data'!$T22</f>
-        <v>2.0749860124402986</v>
+        <f>passenger!AB38</f>
+        <v>0.72854591390634038</v>
       </c>
       <c r="Z3">
-        <f>passenger!BI22/'raw data'!$T22</f>
-        <v>2.0563668640793442</v>
+        <f>passenger!AC38</f>
+        <v>0.72747441880342134</v>
       </c>
       <c r="AA3">
-        <f>passenger!BJ22/'raw data'!$T22</f>
-        <v>2.0377477157183885</v>
+        <f>passenger!AD38</f>
+        <v>0.72646524123387723</v>
       </c>
       <c r="AB3">
-        <f>passenger!BK22/'raw data'!$T22</f>
-        <v>2.0191285673574342</v>
+        <f>passenger!AE38</f>
+        <v>0.72552235054387193</v>
       </c>
       <c r="AC3">
-        <f>passenger!BL22/'raw data'!$T22</f>
-        <v>2.0005094189964789</v>
+        <f>passenger!AF38</f>
+        <v>0.72459098208099637</v>
       </c>
       <c r="AD3">
-        <f>passenger!BM22/'raw data'!$T22</f>
-        <v>1.9818902706355241</v>
+        <f>passenger!AG38</f>
+        <v>0.72373225650774964</v>
       </c>
       <c r="AE3">
-        <f>passenger!BN22/'raw data'!$T22</f>
-        <v>1.9632711222745691</v>
+        <f>passenger!AH38</f>
+        <v>0.72294943084835472</v>
       </c>
       <c r="AF3">
-        <f>passenger!BO22/'raw data'!$T22</f>
-        <v>1.9446519739136141</v>
+        <f>passenger!AI38</f>
+        <v>0.72224465811758964</v>
       </c>
       <c r="AG3">
-        <f>passenger!BP22/'raw data'!$T22</f>
-        <v>1.9169979707416107</v>
+        <f>passenger!AJ38</f>
+        <v>0.72162048953785374</v>
       </c>
       <c r="AH3">
-        <f>passenger!BQ22/'raw data'!$T22</f>
-        <v>1.8893439675696075</v>
+        <f>passenger!AK38</f>
+        <v>0.72100569154325145</v>
       </c>
       <c r="AI3">
-        <f>passenger!BR22/'raw data'!$T22</f>
-        <v>1.8616899643976041</v>
+        <f>passenger!AL38</f>
+        <v>0.72048281540213144</v>
       </c>
       <c r="AJ3">
-        <f>passenger!BS22/'raw data'!$T22</f>
-        <v>1.834035961225601</v>
+        <f>passenger!AM38</f>
+        <v>0.72005640674696003</v>
       </c>
       <c r="AK3">
-        <f>passenger!BT22/'raw data'!$T22</f>
-        <v>1.8063819580535978</v>
+        <f>passenger!AN38</f>
+        <v>0.71973111278304891</v>
       </c>
       <c r="AL3">
-        <f>passenger!BU22/'raw data'!$T22</f>
-        <v>1.7787279548815946</v>
+        <f>passenger!AO38</f>
+        <v>0.71951169784308</v>
       </c>
       <c r="AM3">
-        <f>passenger!BV22/'raw data'!$T22</f>
-        <v>1.751073951709591</v>
+        <f>passenger!AP38</f>
+        <v>0.71935018149056595</v>
       </c>
       <c r="AN3">
-        <f>passenger!BW22/'raw data'!$T22</f>
-        <v>1.7234199485375878</v>
+        <f>passenger!AQ38</f>
+        <v>0.71930373165674732</v>
       </c>
       <c r="AO3">
-        <f>passenger!BX22/'raw data'!$T22</f>
-        <v>1.6957659453655847</v>
+        <f>passenger!AR38</f>
+        <v>0.71937741951021295</v>
       </c>
       <c r="AP3">
-        <f>passenger!BY22/'raw data'!$T22</f>
-        <v>1.6681119421935815</v>
+        <f>passenger!AS38</f>
+        <v>0.71957644731960901</v>
+      </c>
+      <c r="AQ3">
+        <f>passenger!AT38</f>
+        <v>0.7199772554839079</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:43">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <f>passenger!AK23</f>
+        <f>passenger!E30</f>
         <v>1</v>
       </c>
       <c r="C4">
-        <f>passenger!AL23*'raw data'!U24/'raw data'!$T24</f>
-        <v>1.0289246286914511</v>
+        <f>passenger!F30</f>
+        <v>0.53918310508914769</v>
       </c>
       <c r="D4">
-        <f>passenger!AM23*'raw data'!V24/'raw data'!$T24</f>
-        <v>0.61330297868408601</v>
+        <f>passenger!G30</f>
+        <v>0.5578413197440476</v>
       </c>
       <c r="E4">
-        <f>passenger!AN23*'raw data'!W24/'raw data'!$T24</f>
-        <v>1.6419573565436458</v>
+        <f>passenger!H30</f>
+        <v>0.33436990081416113</v>
       </c>
       <c r="F4">
-        <f>passenger!AO23/'raw data'!$T24</f>
-        <v>1.8139032832747364</v>
+        <f>passenger!I30</f>
+        <v>0.88071215603188302</v>
       </c>
       <c r="G4">
-        <f>passenger!AP23/'raw data'!$T24</f>
-        <v>1.8037211773337143</v>
+        <f>passenger!J30</f>
+        <v>1.1033207179653663</v>
       </c>
       <c r="H4">
-        <f>passenger!AQ23/'raw data'!$T24</f>
-        <v>1.7935390713926918</v>
+        <f>passenger!K30</f>
+        <v>1.2495194484549734</v>
       </c>
       <c r="I4">
-        <f>passenger!AR23/'raw data'!$T24</f>
-        <v>1.7833569654516694</v>
+        <f>passenger!L30</f>
+        <v>1.3240994256313294</v>
       </c>
       <c r="J4">
-        <f>passenger!AS23/'raw data'!$T24</f>
-        <v>1.7731748595106476</v>
+        <f>passenger!M30</f>
+        <v>1.4031308525250177</v>
       </c>
       <c r="K4">
-        <f>passenger!AT23/'raw data'!$T24</f>
-        <v>1.762992753569625</v>
+        <f>passenger!N30</f>
+        <v>1.4868794224941768</v>
       </c>
       <c r="L4">
-        <f>passenger!AU23/'raw data'!$T24</f>
-        <v>1.7528106476286027</v>
+        <f>passenger!O30</f>
+        <v>1.575626687317246</v>
       </c>
       <c r="M4">
-        <f>passenger!AV23/'raw data'!$T24</f>
-        <v>1.8124245037197879</v>
+        <f>passenger!P30</f>
+        <v>1.6696710037333518</v>
       </c>
       <c r="N4">
-        <f>passenger!AW23/'raw data'!$T24</f>
-        <v>1.8720383598109731</v>
+        <f>passenger!Q30</f>
+        <v>1.741146149806418</v>
       </c>
       <c r="O4">
-        <f>passenger!AX23/'raw data'!$T24</f>
-        <v>1.9316522159021585</v>
+        <f>passenger!R30</f>
+        <v>1.8156809983566449</v>
       </c>
       <c r="P4">
-        <f>passenger!AY23/'raw data'!$T24</f>
-        <v>1.9912660719933439</v>
+        <f>passenger!S30</f>
+        <v>1.8934065288889803</v>
       </c>
       <c r="Q4">
-        <f>passenger!AZ23/'raw data'!$T24</f>
-        <v>2.0508799280845289</v>
+        <f>passenger!T30</f>
+        <v>1.9744593278688025</v>
       </c>
       <c r="R4">
-        <f>passenger!BA23/'raw data'!$T24</f>
-        <v>2.1104937841757145</v>
+        <f>passenger!U30</f>
+        <v>2.0589818287442441</v>
       </c>
       <c r="S4">
-        <f>passenger!BB23/'raw data'!$T24</f>
-        <v>2.1701076402668997</v>
+        <f>passenger!V30</f>
+        <v>2.065687093140415</v>
       </c>
       <c r="T4">
-        <f>passenger!BC23/'raw data'!$T24</f>
-        <v>2.2297214963580854</v>
+        <f>passenger!W30</f>
+        <v>2.0724141938490757</v>
       </c>
       <c r="U4">
-        <f>passenger!BD23/'raw data'!$T24</f>
-        <v>2.2893353524492701</v>
+        <f>passenger!X30</f>
+        <v>2.0791632019821926</v>
       </c>
       <c r="V4">
-        <f>passenger!BE23/'raw data'!$T24</f>
-        <v>2.3489492085404557</v>
+        <f>passenger!Y30</f>
+        <v>2.0859341888833169</v>
       </c>
       <c r="W4">
-        <f>passenger!BF23/'raw data'!$T24</f>
-        <v>2.3984371992323577</v>
+        <f>passenger!Z30</f>
+        <v>2.0927272261283352</v>
       </c>
       <c r="X4">
-        <f>passenger!BG23/'raw data'!$T24</f>
-        <v>2.4479251899242596</v>
+        <f>passenger!AA30</f>
+        <v>2.1036838040682193</v>
       </c>
       <c r="Y4">
-        <f>passenger!BH23/'raw data'!$T24</f>
-        <v>2.4974131806161615</v>
+        <f>passenger!AB30</f>
+        <v>2.1146977457192713</v>
       </c>
       <c r="Z4">
-        <f>passenger!BI23/'raw data'!$T24</f>
-        <v>2.5469011713080634</v>
+        <f>passenger!AC30</f>
+        <v>2.125769351412067</v>
       </c>
       <c r="AA4">
-        <f>passenger!BJ23/'raw data'!$T24</f>
-        <v>2.5963891619999653</v>
+        <f>passenger!AD30</f>
+        <v>2.1368989230495776</v>
       </c>
       <c r="AB4">
-        <f>passenger!BK23/'raw data'!$T24</f>
-        <v>2.6458771526918676</v>
+        <f>passenger!AE30</f>
+        <v>2.1480867641154009</v>
       </c>
       <c r="AC4">
-        <f>passenger!BL23/'raw data'!$T24</f>
-        <v>2.6953651433837691</v>
+        <f>passenger!AF30</f>
+        <v>2.1340474751584533</v>
       </c>
       <c r="AD4">
-        <f>passenger!BM23/'raw data'!$T24</f>
-        <v>2.744853134075671</v>
+        <f>passenger!AG30</f>
+        <v>2.1200999430326122</v>
       </c>
       <c r="AE4">
-        <f>passenger!BN23/'raw data'!$T24</f>
-        <v>2.7943411247675729</v>
+        <f>passenger!AH30</f>
+        <v>2.1062435680411209</v>
       </c>
       <c r="AF4">
-        <f>passenger!BO23/'raw data'!$T24</f>
-        <v>2.8438291154594753</v>
+        <f>passenger!AI30</f>
+        <v>2.0924777544066706</v>
       </c>
       <c r="AG4">
-        <f>passenger!BP23/'raw data'!$T24</f>
-        <v>2.8862875620190045</v>
+        <f>passenger!AJ30</f>
+        <v>2.0788019102457862</v>
       </c>
       <c r="AH4">
-        <f>passenger!BQ23/'raw data'!$T24</f>
-        <v>2.9287460085785346</v>
+        <f>passenger!AK30</f>
+        <v>2.0319917609957465</v>
       </c>
       <c r="AI4">
-        <f>passenger!BR23/'raw data'!$T24</f>
-        <v>2.9712044551380639</v>
+        <f>passenger!AL30</f>
+        <v>1.9862356756572381</v>
       </c>
       <c r="AJ4">
-        <f>passenger!BS23/'raw data'!$T24</f>
-        <v>3.0136629016975935</v>
+        <f>passenger!AM30</f>
+        <v>1.9415099189773843</v>
       </c>
       <c r="AK4">
-        <f>passenger!BT23/'raw data'!$T24</f>
-        <v>3.0561213482571232</v>
+        <f>passenger!AN30</f>
+        <v>1.8977912901701703</v>
       </c>
       <c r="AL4">
-        <f>passenger!BU23/'raw data'!$T24</f>
-        <v>3.0985797948166525</v>
+        <f>passenger!AO30</f>
+        <v>1.8550571108813958</v>
       </c>
       <c r="AM4">
-        <f>passenger!BV23/'raw data'!$T24</f>
-        <v>3.1410382413761821</v>
+        <f>passenger!AP30</f>
+        <v>1.7962182767856762</v>
       </c>
       <c r="AN4">
-        <f>passenger!BW23/'raw data'!$T24</f>
-        <v>3.1834966879357114</v>
+        <f>passenger!AQ30</f>
+        <v>1.7392456970372951</v>
       </c>
       <c r="AO4">
-        <f>passenger!BX23/'raw data'!$T24</f>
-        <v>3.2259551344952415</v>
+        <f>passenger!AR30</f>
+        <v>1.6840801776474104</v>
       </c>
       <c r="AP4">
-        <f>passenger!BY23/'raw data'!$T24</f>
-        <v>3.2684135810547712</v>
+        <f>passenger!AS30</f>
+        <v>1.6306644021463503</v>
+      </c>
+      <c r="AQ4">
+        <f>passenger!AT30</f>
+        <v>1.5789428720323273</v>
       </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:43">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <f>passenger!AK24</f>
+        <f>passenger!E32</f>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>passenger!AL24*'raw data'!U21/'raw data'!$T21</f>
-        <v>1.142818911564293</v>
+        <f>passenger!F32</f>
+        <v>0.56207417078046595</v>
       </c>
       <c r="D5">
-        <f>passenger!AM24*'raw data'!V21/'raw data'!$T21</f>
-        <v>0.78079442393503296</v>
+        <f>passenger!G32</f>
+        <v>0.65057865176179397</v>
       </c>
       <c r="E5">
-        <f>passenger!AN24*'raw data'!W21/'raw data'!$T21</f>
-        <v>1.591069484153834</v>
+        <f>passenger!H32</f>
+        <v>0.44724817428909469</v>
       </c>
       <c r="F5">
-        <f>passenger!AO24/'raw data'!$T21</f>
-        <v>1.7240647777369404</v>
+        <f>passenger!I32</f>
+        <v>1.0015503243441719</v>
       </c>
       <c r="G5">
-        <f>passenger!AP24/'raw data'!$T21</f>
-        <v>1.713213935738888</v>
+        <f>passenger!J32</f>
+        <v>1.0742863748249085</v>
       </c>
       <c r="H5">
-        <f>passenger!AQ24/'raw data'!$T21</f>
-        <v>1.7023630937408358</v>
+        <f>passenger!K32</f>
+        <v>1.0609864571130831</v>
       </c>
       <c r="I5">
-        <f>passenger!AR24/'raw data'!$T21</f>
-        <v>1.6915122517427836</v>
+        <f>passenger!L32</f>
+        <v>1.092014418521257</v>
       </c>
       <c r="J5">
-        <f>passenger!AS24/'raw data'!$T21</f>
-        <v>1.6806614097447314</v>
+        <f>passenger!M32</f>
+        <v>1.1239497754788206</v>
       </c>
       <c r="K5">
-        <f>passenger!AT24/'raw data'!$T21</f>
-        <v>1.669810567746679</v>
+        <f>passenger!N32</f>
+        <v>1.156819064266138</v>
       </c>
       <c r="L5">
-        <f>passenger!AU24/'raw data'!$T21</f>
-        <v>1.6589597257486268</v>
+        <f>passenger!O32</f>
+        <v>1.1906495972023974</v>
       </c>
       <c r="M5">
-        <f>passenger!AV24/'raw data'!$T21</f>
-        <v>1.6894445805644256</v>
+        <f>passenger!P32</f>
+        <v>1.2254694853404384</v>
       </c>
       <c r="N5">
-        <f>passenger!AW24/'raw data'!$T21</f>
-        <v>1.7199294353802244</v>
+        <f>passenger!Q32</f>
+        <v>1.2613076618252728</v>
       </c>
       <c r="O5">
-        <f>passenger!AX24/'raw data'!$T21</f>
-        <v>1.7504142901960229</v>
+        <f>passenger!R32</f>
+        <v>1.2981939059357173</v>
       </c>
       <c r="P5">
-        <f>passenger!AY24/'raw data'!$T21</f>
-        <v>1.7808991450118217</v>
+        <f>passenger!S32</f>
+        <v>1.3361588678291063</v>
       </c>
       <c r="Q5">
-        <f>passenger!AZ24/'raw data'!$T21</f>
-        <v>1.8113839998276204</v>
+        <f>passenger!T32</f>
+        <v>1.3752340940096532</v>
       </c>
       <c r="R5">
-        <f>passenger!BA24/'raw data'!$T21</f>
-        <v>1.8418688546434192</v>
+        <f>passenger!U32</f>
+        <v>1.415452053541618</v>
       </c>
       <c r="S5">
-        <f>passenger!BB24/'raw data'!$T21</f>
-        <v>1.872353709459218</v>
+        <f>passenger!V32</f>
+        <v>1.4437610946124506</v>
       </c>
       <c r="T5">
-        <f>passenger!BC24/'raw data'!$T21</f>
-        <v>1.9028385642750163</v>
+        <f>passenger!W32</f>
+        <v>1.4726363165046996</v>
       </c>
       <c r="U5">
-        <f>passenger!BD24/'raw data'!$T21</f>
-        <v>1.9333234190908151</v>
+        <f>passenger!X32</f>
+        <v>1.5020890428347937</v>
       </c>
       <c r="V5">
-        <f>passenger!BE24/'raw data'!$T21</f>
-        <v>1.9638082739066138</v>
+        <f>passenger!Y32</f>
+        <v>1.5321308236914897</v>
       </c>
       <c r="W5">
-        <f>passenger!BF24/'raw data'!$T21</f>
-        <v>1.9870022150547026</v>
+        <f>passenger!Z32</f>
+        <v>1.5627734401653193</v>
       </c>
       <c r="X5">
-        <f>passenger!BG24/'raw data'!$T21</f>
-        <v>2.0101961562027921</v>
+        <f>passenger!AA32</f>
+        <v>1.5940289089686257</v>
       </c>
       <c r="Y5">
-        <f>passenger!BH24/'raw data'!$T21</f>
-        <v>2.0333900973508814</v>
+        <f>passenger!AB32</f>
+        <v>1.6259094871479984</v>
       </c>
       <c r="Z5">
-        <f>passenger!BI24/'raw data'!$T21</f>
-        <v>2.0565840384989702</v>
+        <f>passenger!AC32</f>
+        <v>1.6584276768909583</v>
       </c>
       <c r="AA5">
-        <f>passenger!BJ24/'raw data'!$T21</f>
-        <v>2.079777979647059</v>
+        <f>passenger!AD32</f>
+        <v>1.6915962304287775</v>
       </c>
       <c r="AB5">
-        <f>passenger!BK24/'raw data'!$T21</f>
-        <v>2.1029719207951483</v>
+        <f>passenger!AE32</f>
+        <v>1.7254281550373531</v>
       </c>
       <c r="AC5">
-        <f>passenger!BL24/'raw data'!$T21</f>
-        <v>2.1261658619432375</v>
+        <f>passenger!AF32</f>
+        <v>1.7426824365877267</v>
       </c>
       <c r="AD5">
-        <f>passenger!BM24/'raw data'!$T21</f>
-        <v>2.1493598030913268</v>
+        <f>passenger!AG32</f>
+        <v>1.760109260953604</v>
       </c>
       <c r="AE5">
-        <f>passenger!BN24/'raw data'!$T21</f>
-        <v>2.1725537442394152</v>
+        <f>passenger!AH32</f>
+        <v>1.77771035356314</v>
       </c>
       <c r="AF5">
-        <f>passenger!BO24/'raw data'!$T21</f>
-        <v>2.1957476853875049</v>
+        <f>passenger!AI32</f>
+        <v>1.7954874570987716</v>
       </c>
       <c r="AG5">
-        <f>passenger!BP24/'raw data'!$T21</f>
-        <v>2.2149036698794058</v>
+        <f>passenger!AJ32</f>
+        <v>1.8134423316697592</v>
       </c>
       <c r="AH5">
-        <f>passenger!BQ24/'raw data'!$T21</f>
-        <v>2.2340596543713076</v>
+        <f>passenger!AK32</f>
+        <v>1.8315767549864568</v>
       </c>
       <c r="AI5">
-        <f>passenger!BR24/'raw data'!$T21</f>
-        <v>2.2532156388632094</v>
+        <f>passenger!AL32</f>
+        <v>1.8498925225363214</v>
       </c>
       <c r="AJ5">
-        <f>passenger!BS24/'raw data'!$T21</f>
-        <v>2.2723716233551108</v>
+        <f>passenger!AM32</f>
+        <v>1.8683914477616848</v>
       </c>
       <c r="AK5">
-        <f>passenger!BT24/'raw data'!$T21</f>
-        <v>2.2915276078470121</v>
+        <f>passenger!AN32</f>
+        <v>1.8870753622393015</v>
       </c>
       <c r="AL5">
-        <f>passenger!BU24/'raw data'!$T21</f>
-        <v>2.3106835923389135</v>
+        <f>passenger!AO32</f>
+        <v>1.8870753622393015</v>
       </c>
       <c r="AM5">
-        <f>passenger!BV24/'raw data'!$T21</f>
-        <v>2.3298395768308153</v>
+        <f>passenger!AP32</f>
+        <v>1.8965107390504978</v>
       </c>
       <c r="AN5">
-        <f>passenger!BW24/'raw data'!$T21</f>
-        <v>2.3489955613227163</v>
+        <f>passenger!AQ32</f>
+        <v>1.9059932927457501</v>
       </c>
       <c r="AO5">
-        <f>passenger!BX24/'raw data'!$T21</f>
-        <v>2.3681515458146181</v>
+        <f>passenger!AR32</f>
+        <v>1.9155232592094786</v>
       </c>
       <c r="AP5">
-        <f>passenger!BY24/'raw data'!$T21</f>
-        <v>2.3873075303065199</v>
+        <f>passenger!AS32</f>
+        <v>1.9251008755055259</v>
+      </c>
+      <c r="AQ5">
+        <f>passenger!AT32</f>
+        <v>1.9347263798830534</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:43">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
-        <f>passenger!AK25</f>
+        <f>passenger!E34</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>passenger!AL25*'raw data'!U23/'raw data'!$T23</f>
-        <v>0.97830774234802009</v>
+        <f>passenger!F34</f>
+        <v>0.41147132169576056</v>
       </c>
       <c r="D6">
-        <f>passenger!AM25*'raw data'!V23/'raw data'!$T23</f>
-        <v>0.6505434936352108</v>
+        <f>passenger!G34</f>
+        <v>0.41271820448877805</v>
       </c>
       <c r="E6">
-        <f>passenger!AN25*'raw data'!W23/'raw data'!$T23</f>
-        <v>2.004917911401531</v>
+        <f>passenger!H34</f>
+        <v>0.28179551122194513</v>
       </c>
       <c r="F6">
-        <f>passenger!AO25/'raw data'!$T23</f>
-        <v>2.185622151917967</v>
+        <f>passenger!I34</f>
+        <v>0.67082294264339148</v>
       </c>
       <c r="G6">
-        <f>passenger!AP25/'raw data'!$T23</f>
-        <v>2.1242677626467765</v>
+        <f>passenger!J34</f>
+        <v>0.68204488778054861</v>
       </c>
       <c r="H6">
-        <f>passenger!AQ25/'raw data'!$T23</f>
-        <v>2.0629133733755864</v>
+        <f>passenger!K34</f>
+        <v>0.69792418952618451</v>
       </c>
       <c r="I6">
-        <f>passenger!AR25/'raw data'!$T23</f>
-        <v>2.0015589841043964</v>
+        <f>passenger!L34</f>
+        <v>0.71188267331670829</v>
       </c>
       <c r="J6">
-        <f>passenger!AS25/'raw data'!$T23</f>
-        <v>1.9402045948332063</v>
+        <f>passenger!M34</f>
+        <v>0.72612032678304239</v>
       </c>
       <c r="K6">
-        <f>passenger!AT25/'raw data'!$T23</f>
-        <v>1.878850205562016</v>
+        <f>passenger!N34</f>
+        <v>0.74064273331870334</v>
       </c>
       <c r="L6">
-        <f>passenger!AU25/'raw data'!$T23</f>
-        <v>1.8174958162908259</v>
+        <f>passenger!O34</f>
+        <v>0.75545558798507739</v>
       </c>
       <c r="M6">
-        <f>passenger!AV25/'raw data'!$T23</f>
-        <v>1.8006199266191298</v>
+        <f>passenger!P34</f>
+        <v>0.77056469974477904</v>
       </c>
       <c r="N6">
-        <f>passenger!AW25/'raw data'!$T23</f>
-        <v>1.783744036947434</v>
+        <f>passenger!Q34</f>
+        <v>0.78597599373967464</v>
       </c>
       <c r="O6">
-        <f>passenger!AX25/'raw data'!$T23</f>
-        <v>1.7668681472757382</v>
+        <f>passenger!R34</f>
+        <v>0.80169551361446811</v>
       </c>
       <c r="P6">
-        <f>passenger!AY25/'raw data'!$T23</f>
-        <v>1.7499922576040423</v>
+        <f>passenger!S34</f>
+        <v>0.81772942388675751</v>
       </c>
       <c r="Q6">
-        <f>passenger!AZ25/'raw data'!$T23</f>
-        <v>1.7331163679323465</v>
+        <f>passenger!T34</f>
+        <v>0.83408401236449281</v>
       </c>
       <c r="R6">
-        <f>passenger!BA25/'raw data'!$T23</f>
-        <v>1.7162404782606504</v>
+        <f>passenger!U34</f>
+        <v>0.85076569261178281</v>
       </c>
       <c r="S6">
-        <f>passenger!BB25/'raw data'!$T23</f>
-        <v>1.6993645885889543</v>
+        <f>passenger!V34</f>
+        <v>0.85501952107484169</v>
       </c>
       <c r="T6">
-        <f>passenger!BC25/'raw data'!$T23</f>
-        <v>1.6824886989172585</v>
+        <f>passenger!W34</f>
+        <v>0.85929461868021584</v>
       </c>
       <c r="U6">
-        <f>passenger!BD25/'raw data'!$T23</f>
-        <v>1.6656128092455627</v>
+        <f>passenger!X34</f>
+        <v>0.86359109177361681</v>
       </c>
       <c r="V6">
-        <f>passenger!BE25/'raw data'!$T23</f>
-        <v>1.6487369195738666</v>
+        <f>passenger!Y34</f>
+        <v>0.86790904723248463</v>
       </c>
       <c r="W6">
-        <f>passenger!BF25/'raw data'!$T23</f>
-        <v>1.6283174798240798</v>
+        <f>passenger!Z34</f>
+        <v>0.87224859246864705</v>
       </c>
       <c r="X6">
-        <f>passenger!BG25/'raw data'!$T23</f>
-        <v>1.607898040074293</v>
+        <f>passenger!AA34</f>
+        <v>0.87660983543099025</v>
       </c>
       <c r="Y6">
-        <f>passenger!BH25/'raw data'!$T23</f>
-        <v>1.5874786003245061</v>
+        <f>passenger!AB34</f>
+        <v>0.88099288460814518</v>
       </c>
       <c r="Z6">
-        <f>passenger!BI25/'raw data'!$T23</f>
-        <v>1.5670591605747193</v>
+        <f>passenger!AC34</f>
+        <v>0.88539784903118579</v>
       </c>
       <c r="AA6">
-        <f>passenger!BJ25/'raw data'!$T23</f>
-        <v>1.5466397208249323</v>
+        <f>passenger!AD34</f>
+        <v>0.88982483827634162</v>
       </c>
       <c r="AB6">
-        <f>passenger!BK25/'raw data'!$T23</f>
-        <v>1.5262202810751457</v>
+        <f>passenger!AE34</f>
+        <v>0.89427396246772328</v>
       </c>
       <c r="AC6">
-        <f>passenger!BL25/'raw data'!$T23</f>
-        <v>1.5058008413253587</v>
+        <f>passenger!AF34</f>
+        <v>0.89606251039265872</v>
       </c>
       <c r="AD6">
-        <f>passenger!BM25/'raw data'!$T23</f>
-        <v>1.485381401575572</v>
+        <f>passenger!AG34</f>
+        <v>0.89785463541344412</v>
       </c>
       <c r="AE6">
-        <f>passenger!BN25/'raw data'!$T23</f>
-        <v>1.4649619618257848</v>
+        <f>passenger!AH34</f>
+        <v>0.89965034468427085</v>
       </c>
       <c r="AF6">
-        <f>passenger!BO25/'raw data'!$T23</f>
-        <v>1.444542522075998</v>
+        <f>passenger!AI34</f>
+        <v>0.90144964537363936</v>
       </c>
       <c r="AG6">
-        <f>passenger!BP25/'raw data'!$T23</f>
-        <v>1.4247683062588252</v>
+        <f>passenger!AJ34</f>
+        <v>0.90325254466438676</v>
       </c>
       <c r="AH6">
-        <f>passenger!BQ25/'raw data'!$T23</f>
-        <v>1.4049940904416525</v>
+        <f>passenger!AK34</f>
+        <v>0.90505904975371543</v>
       </c>
       <c r="AI6">
-        <f>passenger!BR25/'raw data'!$T23</f>
-        <v>1.3852198746244795</v>
+        <f>passenger!AL34</f>
+        <v>0.90686916785322291</v>
       </c>
       <c r="AJ6">
-        <f>passenger!BS25/'raw data'!$T23</f>
-        <v>1.3654456588073067</v>
+        <f>passenger!AM34</f>
+        <v>0.90868290618892933</v>
       </c>
       <c r="AK6">
-        <f>passenger!BT25/'raw data'!$T23</f>
-        <v>1.3456714429901342</v>
+        <f>passenger!AN34</f>
+        <v>0.91050027200130723</v>
       </c>
       <c r="AL6">
-        <f>passenger!BU25/'raw data'!$T23</f>
-        <v>1.3258972271729614</v>
+        <f>passenger!AO34</f>
+        <v>0.91050027200130723</v>
       </c>
       <c r="AM6">
-        <f>passenger!BV25/'raw data'!$T23</f>
-        <v>1.3061230113557887</v>
+        <f>passenger!AP34</f>
+        <v>0.91232127254530981</v>
       </c>
       <c r="AN6">
-        <f>passenger!BW25/'raw data'!$T23</f>
-        <v>1.2863487955386157</v>
+        <f>passenger!AQ34</f>
+        <v>0.91414591509040033</v>
       </c>
       <c r="AO6">
-        <f>passenger!BX25/'raw data'!$T23</f>
-        <v>1.2665745797214429</v>
+        <f>passenger!AR34</f>
+        <v>0.91597420692058129</v>
       </c>
       <c r="AP6">
-        <f>passenger!BY25/'raw data'!$T23</f>
-        <v>1.2468003639042702</v>
+        <f>passenger!AS34</f>
+        <v>0.91780615533442234</v>
+      </c>
+      <c r="AQ6">
+        <f>passenger!AT34</f>
+        <v>0.9196417676450912</v>
       </c>
     </row>
-    <row r="7" spans="1:42">
+    <row r="7" spans="1:43">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -14644,6 +20361,10 @@
         <v>1</v>
       </c>
       <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7" cm="1">
+        <f t="array" ref="AQ7">TREND(R7:AP7,$R$1:$AP$1,$AQ$1,TRUE)</f>
         <v>1</v>
       </c>
     </row>
@@ -14654,146 +20375,149 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AP7"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:AQ7"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="81">
+    <row r="1" spans="1:43" ht="77.45">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B1">
+        <v>2019</v>
+      </c>
+      <c r="C1">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>2050</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>2051</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>2052</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>2053</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>2054</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>2055</v>
       </c>
-      <c r="AL1">
+      <c r="AM1">
         <v>2056</v>
       </c>
-      <c r="AM1">
+      <c r="AN1">
         <v>2057</v>
       </c>
-      <c r="AN1">
+      <c r="AO1">
         <v>2058</v>
       </c>
-      <c r="AO1">
+      <c r="AP1">
         <v>2059</v>
       </c>
-      <c r="AP1">
+      <c r="AQ1">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -14802,8 +20526,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <f>freight!AL21</f>
-        <v>1.028797768391698</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <f>freight!AM21</f>
@@ -14961,8 +20684,12 @@
         <f>freight!BY21</f>
         <v>1.6286685551466342</v>
       </c>
+      <c r="AQ2" cm="1">
+        <f t="array" ref="AQ2">TREND(R2:AP2,$R$1:$AP$1,$AQ$1,TRUE)</f>
+        <v>1.6710721043145611</v>
+      </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:43">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -14971,8 +20698,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <f>freight!AL22</f>
-        <v>1.028797768391698</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <f>freight!AM22</f>
@@ -15130,515 +20856,531 @@
         <f>freight!BY22</f>
         <v>1.6286685551466342</v>
       </c>
+      <c r="AQ3" cm="1">
+        <f t="array" ref="AQ3">TREND(R3:AP3,$R$1:$AP$1,$AQ$1,TRUE)</f>
+        <v>1.6710721043145611</v>
+      </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:43">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <f>freight!AK23</f>
+        <f>freight!E32</f>
         <v>1</v>
       </c>
       <c r="C4">
-        <f>freight!AL23</f>
-        <v>1.1502081598667777</v>
+        <f>freight!F32</f>
+        <v>0.91261398176291797</v>
       </c>
       <c r="D4">
-        <f>freight!AM23</f>
-        <v>1.3004163197335554</v>
+        <f>freight!G32</f>
+        <v>1.0568389057750762</v>
       </c>
       <c r="E4">
-        <f>freight!AN23</f>
-        <v>1.4506244796003331</v>
+        <f>freight!H32</f>
+        <v>0.96542553191489366</v>
       </c>
       <c r="F4">
-        <f>freight!AO23</f>
-        <v>1.6008326394671109</v>
+        <f>freight!I32</f>
+        <v>1.0775835866261398</v>
       </c>
       <c r="G4">
-        <f>freight!AP23</f>
-        <v>1.7510407993338883</v>
+        <f>freight!J32</f>
+        <v>1.3445668693009118</v>
       </c>
       <c r="H4">
-        <f>freight!AQ23</f>
-        <v>1.9012489592006661</v>
+        <f>freight!K32</f>
+        <v>1.3984176791404332</v>
       </c>
       <c r="I4">
-        <f>freight!AR23</f>
-        <v>2.051457119067444</v>
+        <f>freight!L32</f>
+        <v>1.4529251443088298</v>
       </c>
       <c r="J4">
-        <f>freight!AS23</f>
-        <v>2.2016652789342213</v>
+        <f>freight!M32</f>
+        <v>1.4994441506473171</v>
       </c>
       <c r="K4">
-        <f>freight!AT23</f>
-        <v>2.351873438800999</v>
+        <f>freight!N32</f>
+        <v>1.5406118957354304</v>
       </c>
       <c r="L4">
-        <f>freight!AU23</f>
-        <v>2.5020815986677771</v>
+        <f>freight!O32</f>
+        <v>1.5780989933025782</v>
       </c>
       <c r="M4">
-        <f>freight!AV23</f>
-        <v>2.6361365528726064</v>
+        <f>freight!P32</f>
+        <v>1.6152793551582547</v>
       </c>
       <c r="N4">
-        <f>freight!AW23</f>
-        <v>2.7701915070774357</v>
+        <f>freight!Q32</f>
+        <v>1.6510859577662245</v>
       </c>
       <c r="O4">
-        <f>freight!AX23</f>
-        <v>2.9042464612822649</v>
+        <f>freight!R32</f>
+        <v>1.6888528402657748</v>
       </c>
       <c r="P4">
-        <f>freight!AY23</f>
-        <v>3.0383014154870942</v>
+        <f>freight!S32</f>
+        <v>1.7271222145467906</v>
       </c>
       <c r="Q4">
-        <f>freight!AZ23</f>
-        <v>3.1723563696919235</v>
+        <f>freight!T32</f>
+        <v>1.7657348550500753</v>
       </c>
       <c r="R4">
-        <f>freight!BA23</f>
-        <v>3.3064113238967532</v>
+        <f>freight!U32</f>
+        <v>1.8039598821254301</v>
       </c>
       <c r="S4">
-        <f>freight!BB23</f>
-        <v>3.4404662781015825</v>
+        <f>freight!V32</f>
+        <v>1.8443894253187751</v>
       </c>
       <c r="T4">
-        <f>freight!BC23</f>
-        <v>3.5745212323064117</v>
+        <f>freight!W32</f>
+        <v>1.8841136199395006</v>
       </c>
       <c r="U4">
-        <f>freight!BD23</f>
-        <v>3.7085761865112405</v>
+        <f>freight!X32</f>
+        <v>1.9235165719601217</v>
       </c>
       <c r="V4">
-        <f>freight!BE23</f>
-        <v>3.8426311407160703</v>
+        <f>freight!Y32</f>
+        <v>1.9624541614497415</v>
       </c>
       <c r="W4">
-        <f>freight!BF23</f>
-        <v>3.945462114904247</v>
+        <f>freight!Z32</f>
+        <v>2.0007489709435924</v>
       </c>
       <c r="X4">
-        <f>freight!BG23</f>
-        <v>4.0482930890924234</v>
+        <f>freight!AA32</f>
+        <v>2.0393775226920829</v>
       </c>
       <c r="Y4">
-        <f>freight!BH23</f>
-        <v>4.1511240632805997</v>
+        <f>freight!AB32</f>
+        <v>2.0770110905861077</v>
       </c>
       <c r="Z4">
-        <f>freight!BI23</f>
-        <v>4.253955037468776</v>
+        <f>freight!AC32</f>
+        <v>2.1134214730578313</v>
       </c>
       <c r="AA4">
-        <f>freight!BJ23</f>
-        <v>4.3567860116569523</v>
+        <f>freight!AD32</f>
+        <v>2.1483873310415347</v>
       </c>
       <c r="AB4">
-        <f>freight!BK23</f>
-        <v>4.4596169858451296</v>
+        <f>freight!AE32</f>
+        <v>2.1816615540060962</v>
       </c>
       <c r="AC4">
-        <f>freight!BL23</f>
-        <v>4.5624479600333059</v>
+        <f>freight!AF32</f>
+        <v>2.2150989241955128</v>
       </c>
       <c r="AD4">
-        <f>freight!BM23</f>
-        <v>4.6652789342214822</v>
+        <f>freight!AG32</f>
+        <v>2.2464571415849068</v>
       </c>
       <c r="AE4">
-        <f>freight!BN23</f>
-        <v>4.7681099084096585</v>
+        <f>freight!AH32</f>
+        <v>2.2754965466913193</v>
       </c>
       <c r="AF4">
-        <f>freight!BO23</f>
-        <v>4.8709408825978358</v>
+        <f>freight!AI32</f>
+        <v>2.3020186253936443</v>
       </c>
       <c r="AG4">
-        <f>freight!BP23</f>
-        <v>5.0416319733555373</v>
+        <f>freight!AJ32</f>
+        <v>2.325813632347574</v>
       </c>
       <c r="AH4">
-        <f>freight!BQ23</f>
-        <v>5.2123230641132396</v>
+        <f>freight!AK32</f>
+        <v>2.3495223448300533</v>
       </c>
       <c r="AI4">
-        <f>freight!BR23</f>
-        <v>5.3830141548709411</v>
+        <f>freight!AL32</f>
+        <v>2.3699160960534305</v>
       </c>
       <c r="AJ4">
-        <f>freight!BS23</f>
-        <v>5.5537052456286427</v>
+        <f>freight!AM32</f>
+        <v>2.3867087247538286</v>
       </c>
       <c r="AK4">
-        <f>freight!BT23</f>
-        <v>5.724396336386345</v>
+        <f>freight!AN32</f>
+        <v>2.3996207689142492</v>
       </c>
       <c r="AL4">
-        <f>freight!BU23</f>
-        <v>5.8950874271440465</v>
+        <f>freight!AO32</f>
+        <v>2.4083827652373375</v>
       </c>
       <c r="AM4">
-        <f>freight!BV23</f>
-        <v>6.0657785179017489</v>
+        <f>freight!AP32</f>
+        <v>2.4148589855453437</v>
       </c>
       <c r="AN4">
-        <f>freight!BW23</f>
-        <v>6.2364696086594504</v>
+        <f>freight!AQ32</f>
+        <v>2.4167270506965299</v>
       </c>
       <c r="AO4">
-        <f>freight!BX23</f>
-        <v>6.4071606994171528</v>
+        <f>freight!AR32</f>
+        <v>2.413760998151631</v>
       </c>
       <c r="AP4">
-        <f>freight!BY23</f>
-        <v>6.5778517901748543</v>
+        <f>freight!AS32</f>
+        <v>2.4057607935759342</v>
+      </c>
+      <c r="AQ4">
+        <f>freight!AT32</f>
+        <v>2.3897093564136922</v>
       </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:43">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <f>freight!AK24</f>
+        <f>freight!E35</f>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>freight!AL24</f>
-        <v>1.0887629668032794</v>
+        <f>freight!F35</f>
+        <v>1.011016499900603</v>
       </c>
       <c r="D5">
-        <f>freight!AM24</f>
-        <v>1.1775259336065591</v>
+        <f>freight!G35</f>
+        <v>1.1012524020939634</v>
       </c>
       <c r="E5">
-        <f>freight!AN24</f>
-        <v>1.2662889004098385</v>
+        <f>freight!H35</f>
+        <v>1.1909648134649791</v>
       </c>
       <c r="F5">
-        <f>freight!AO24</f>
-        <v>1.355051867213118</v>
+        <f>freight!I35</f>
+        <v>1.2080180239878073</v>
       </c>
       <c r="G5">
-        <f>freight!AP24</f>
-        <v>1.4438148340163974</v>
+        <f>freight!J35</f>
+        <v>1.1881883241667219</v>
       </c>
       <c r="H5">
-        <f>freight!AQ24</f>
-        <v>1.5325778008196771</v>
+        <f>freight!K35</f>
+        <v>1.2796368696574116</v>
       </c>
       <c r="I5">
-        <f>freight!AR24</f>
-        <v>1.6213407676229565</v>
+        <f>freight!L35</f>
+        <v>1.3000972101576365</v>
       </c>
       <c r="J5">
-        <f>freight!AS24</f>
-        <v>1.710103734426236</v>
+        <f>freight!M35</f>
+        <v>1.3208846946651276</v>
       </c>
       <c r="K5">
-        <f>freight!AT24</f>
-        <v>1.7988667012295154</v>
+        <f>freight!N35</f>
+        <v>1.3420045539433456</v>
       </c>
       <c r="L5">
-        <f>freight!AU24</f>
-        <v>1.8876296680327951</v>
+        <f>freight!O35</f>
+        <v>1.3634621023913551</v>
       </c>
       <c r="M5">
-        <f>freight!AV24</f>
-        <v>1.9833220053705687</v>
+        <f>freight!P35</f>
+        <v>1.3852627393810881</v>
       </c>
       <c r="N5">
-        <f>freight!AW24</f>
-        <v>2.0790143427083421</v>
+        <f>freight!Q35</f>
+        <v>1.4024001985177346</v>
       </c>
       <c r="O5">
-        <f>freight!AX24</f>
-        <v>2.1747066800461159</v>
+        <f>freight!R35</f>
+        <v>1.4197496697855898</v>
       </c>
       <c r="P5">
-        <f>freight!AY24</f>
-        <v>2.2703990173838897</v>
+        <f>freight!S35</f>
+        <v>1.4373137760439365</v>
       </c>
       <c r="Q5">
-        <f>freight!AZ24</f>
-        <v>2.3660913547216631</v>
+        <f>freight!T35</f>
+        <v>1.4550951726001573</v>
       </c>
       <c r="R5">
-        <f>freight!BA24</f>
-        <v>2.4617836920594369</v>
+        <f>freight!U35</f>
+        <v>1.473096547611159</v>
       </c>
       <c r="S5">
-        <f>freight!BB24</f>
-        <v>2.5574760293972103</v>
+        <f>freight!V35</f>
+        <v>1.4962458636742006</v>
       </c>
       <c r="T5">
-        <f>freight!BC24</f>
-        <v>2.6531683667349841</v>
+        <f>freight!W35</f>
+        <v>1.5197589650132688</v>
       </c>
       <c r="U5">
-        <f>freight!BD24</f>
-        <v>2.7488607040727575</v>
+        <f>freight!X35</f>
+        <v>1.5436415684161378</v>
       </c>
       <c r="V5">
-        <f>freight!BE24</f>
-        <v>2.8445530414105313</v>
+        <f>freight!Y35</f>
+        <v>1.5678994805083644</v>
       </c>
       <c r="W5">
-        <f>freight!BF24</f>
-        <v>2.9500767832693091</v>
+        <f>freight!Z35</f>
+        <v>1.5925385991650653</v>
       </c>
       <c r="X5">
-        <f>freight!BG24</f>
-        <v>3.0556005251280869</v>
+        <f>freight!AA35</f>
+        <v>1.6030348042389713</v>
       </c>
       <c r="Y5">
-        <f>freight!BH24</f>
-        <v>3.1611242669868647</v>
+        <f>freight!AB35</f>
+        <v>1.6136001883714015</v>
       </c>
       <c r="Z5">
-        <f>freight!BI24</f>
-        <v>3.2666480088456424</v>
+        <f>freight!AC35</f>
+        <v>1.6242352075121114</v>
       </c>
       <c r="AA5">
-        <f>freight!BJ24</f>
-        <v>3.3721717507044202</v>
+        <f>freight!AD35</f>
+        <v>1.6349403206159592</v>
       </c>
       <c r="AB5">
-        <f>freight!BK24</f>
-        <v>3.477695492563198</v>
+        <f>freight!AE35</f>
+        <v>1.6457159896627129</v>
       </c>
       <c r="AC5">
-        <f>freight!BL24</f>
-        <v>3.5832192344219758</v>
+        <f>freight!AF35</f>
+        <v>1.6562230699223925</v>
       </c>
       <c r="AD5">
-        <f>freight!BM24</f>
-        <v>3.6887429762807535</v>
+        <f>freight!AG35</f>
+        <v>1.6667972326776406</v>
       </c>
       <c r="AE5">
-        <f>freight!BN24</f>
-        <v>3.7942667181395313</v>
+        <f>freight!AH35</f>
+        <v>1.6774389062169159</v>
       </c>
       <c r="AF5">
-        <f>freight!BO24</f>
-        <v>3.8997904599983091</v>
+        <f>freight!AI35</f>
+        <v>1.6881485215630867</v>
       </c>
       <c r="AG5">
-        <f>freight!BP24</f>
-        <v>3.9718874264856727</v>
+        <f>freight!AJ35</f>
+        <v>1.6989265124908886</v>
       </c>
       <c r="AH5">
-        <f>freight!BQ24</f>
-        <v>4.0439843929730364</v>
+        <f>freight!AK35</f>
+        <v>1.7108190159507748</v>
       </c>
       <c r="AI5">
-        <f>freight!BR24</f>
-        <v>4.1160813594604004</v>
+        <f>freight!AL35</f>
+        <v>1.7227947670599872</v>
       </c>
       <c r="AJ5">
-        <f>freight!BS24</f>
-        <v>4.1881783259477636</v>
+        <f>freight!AM35</f>
+        <v>1.7348543485529475</v>
       </c>
       <c r="AK5">
-        <f>freight!BT24</f>
-        <v>4.2602752924351277</v>
+        <f>freight!AN35</f>
+        <v>1.7469983472432233</v>
       </c>
       <c r="AL5">
-        <f>freight!BU24</f>
-        <v>4.3323722589224909</v>
+        <f>freight!AO35</f>
+        <v>1.759227354052084</v>
       </c>
       <c r="AM5">
-        <f>freight!BV24</f>
-        <v>4.404469225409855</v>
+        <f>freight!AP35</f>
+        <v>1.7711254895080797</v>
       </c>
       <c r="AN5">
-        <f>freight!BW24</f>
-        <v>4.476566191897219</v>
+        <f>freight!AQ35</f>
+        <v>1.7831040953063555</v>
       </c>
       <c r="AO5">
-        <f>freight!BX24</f>
-        <v>4.5486631583845822</v>
+        <f>freight!AR35</f>
+        <v>1.7951637156898317</v>
       </c>
       <c r="AP5">
-        <f>freight!BY24</f>
-        <v>4.6207601248719463</v>
+        <f>freight!AS35</f>
+        <v>1.8073048985822924</v>
+      </c>
+      <c r="AQ5">
+        <f>freight!AT35</f>
+        <v>1.8195281956132794</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:43">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
-        <f>freight!AK25</f>
+        <f>freight!E37</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>freight!AL25</f>
-        <v>1.0303923373147721</v>
+        <f>freight!F37</f>
+        <v>1.0180006348412416</v>
       </c>
       <c r="D6">
-        <f>freight!AM25</f>
-        <v>1.060784674629544</v>
+        <f>freight!G37</f>
+        <v>1.1117176303107836</v>
       </c>
       <c r="E6">
-        <f>freight!AN25</f>
-        <v>1.091177011944316</v>
+        <f>freight!H37</f>
+        <v>1.1639054278926158</v>
       </c>
       <c r="F6">
-        <f>freight!AO25</f>
-        <v>1.1215693492590881</v>
+        <f>freight!I37</f>
+        <v>1.2499783576849457</v>
       </c>
       <c r="G6">
-        <f>freight!AP25</f>
-        <v>1.15196168657386</v>
+        <f>freight!J37</f>
+        <v>1.3603195367582697</v>
       </c>
       <c r="H6">
-        <f>freight!AQ25</f>
-        <v>1.1823540238886321</v>
+        <f>freight!K37</f>
+        <v>1.3952928673681615</v>
       </c>
       <c r="I6">
-        <f>freight!AR25</f>
-        <v>1.212746361203404</v>
+        <f>freight!L37</f>
+        <v>1.4205794550127622</v>
       </c>
       <c r="J6">
-        <f>freight!AS25</f>
-        <v>1.2431386985181763</v>
+        <f>freight!M37</f>
+        <v>1.4463243059579656</v>
       </c>
       <c r="K6">
-        <f>freight!AT25</f>
-        <v>1.2735310358329479</v>
+        <f>freight!N37</f>
+        <v>1.4725357252093996</v>
       </c>
       <c r="L6">
-        <f>freight!AU25</f>
-        <v>1.3039233731477202</v>
+        <f>freight!O37</f>
+        <v>1.4992221682824924</v>
       </c>
       <c r="M6">
-        <f>freight!AV25</f>
-        <v>1.3303797894144855</v>
+        <f>freight!P37</f>
+        <v>1.5263922439301312</v>
       </c>
       <c r="N6">
-        <f>freight!AW25</f>
-        <v>1.3568362056812509</v>
+        <f>freight!Q37</f>
+        <v>1.5475439465072698</v>
       </c>
       <c r="O6">
-        <f>freight!AX25</f>
-        <v>1.3832926219480162</v>
+        <f>freight!R37</f>
+        <v>1.5689887549513248</v>
       </c>
       <c r="P6">
-        <f>freight!AY25</f>
-        <v>1.4097490382147815</v>
+        <f>freight!S37</f>
+        <v>1.5907307309234751</v>
       </c>
       <c r="Q6">
-        <f>freight!AZ25</f>
-        <v>1.4362054544815468</v>
+        <f>freight!T37</f>
+        <v>1.6127739923686295</v>
       </c>
       <c r="R6">
-        <f>freight!BA25</f>
-        <v>1.4626618707483121</v>
+        <f>freight!U37</f>
+        <v>1.6351227142953684</v>
       </c>
       <c r="S6">
-        <f>freight!BB25</f>
-        <v>1.4891182870150774</v>
+        <f>freight!V37</f>
+        <v>1.6557859790084686</v>
       </c>
       <c r="T6">
-        <f>freight!BC25</f>
-        <v>1.5155747032818427</v>
+        <f>freight!W37</f>
+        <v>1.6767103681649338</v>
       </c>
       <c r="U6">
-        <f>freight!BD25</f>
-        <v>1.5420311195486081</v>
+        <f>freight!X37</f>
+        <v>1.6978991816293236</v>
       </c>
       <c r="V6">
-        <f>freight!BE25</f>
-        <v>1.5684875358153736</v>
+        <f>freight!Y37</f>
+        <v>1.7193557609670291</v>
       </c>
       <c r="W6">
-        <f>freight!BF25</f>
-        <v>1.5854952319868656</v>
+        <f>freight!Z37</f>
+        <v>1.7410834899712497</v>
       </c>
       <c r="X6">
-        <f>freight!BG25</f>
-        <v>1.6025029281583576</v>
+        <f>freight!AA37</f>
+        <v>1.7506127508062819</v>
       </c>
       <c r="Y6">
-        <f>freight!BH25</f>
-        <v>1.6195106243298496</v>
+        <f>freight!AB37</f>
+        <v>1.7601941669874448</v>
       </c>
       <c r="Z6">
-        <f>freight!BI25</f>
-        <v>1.6365183205013414</v>
+        <f>freight!AC37</f>
+        <v>1.7698280239702611</v>
       </c>
       <c r="AA6">
-        <f>freight!BJ25</f>
-        <v>1.6535260166728334</v>
+        <f>freight!AD37</f>
+        <v>1.7795146087726021</v>
       </c>
       <c r="AB6">
-        <f>freight!BK25</f>
-        <v>1.6705337128443254</v>
+        <f>freight!AE37</f>
+        <v>1.7892542099832389</v>
       </c>
       <c r="AC6">
-        <f>freight!BL25</f>
-        <v>1.6875414090158174</v>
+        <f>freight!AF37</f>
+        <v>1.7980644584828971</v>
       </c>
       <c r="AD6">
-        <f>freight!BM25</f>
-        <v>1.7045491051873094</v>
+        <f>freight!AG37</f>
+        <v>1.8069180884529983</v>
       </c>
       <c r="AE6">
-        <f>freight!BN25</f>
-        <v>1.7215568013588014</v>
+        <f>freight!AH37</f>
+        <v>1.815815313502952</v>
       </c>
       <c r="AF6">
-        <f>freight!BO25</f>
-        <v>1.7385644975302934</v>
+        <f>freight!AI37</f>
+        <v>1.8247563482939757</v>
       </c>
       <c r="AG6">
-        <f>freight!BP25</f>
-        <v>1.7565170657113129</v>
+        <f>freight!AJ37</f>
+        <v>1.8337414085442729</v>
       </c>
       <c r="AH6">
-        <f>freight!BQ25</f>
-        <v>1.7744696338923323</v>
+        <f>freight!AK37</f>
+        <v>1.8369263895829764</v>
       </c>
       <c r="AI6">
-        <f>freight!BR25</f>
-        <v>1.7924222020733516</v>
+        <f>freight!AL37</f>
+        <v>1.8401169025381048</v>
       </c>
       <c r="AJ6">
-        <f>freight!BS25</f>
-        <v>1.8103747702543709</v>
+        <f>freight!AM37</f>
+        <v>1.8433129570179096</v>
       </c>
       <c r="AK6">
-        <f>freight!BT25</f>
-        <v>1.8283273384353902</v>
+        <f>freight!AN37</f>
+        <v>1.8465145626473309</v>
       </c>
       <c r="AL6">
-        <f>freight!BU25</f>
-        <v>1.8462799066164095</v>
+        <f>freight!AO37</f>
+        <v>1.8497217290680263</v>
       </c>
       <c r="AM6">
-        <f>freight!BV25</f>
-        <v>1.8642324747974288</v>
+        <f>freight!AP37</f>
+        <v>1.8529048947920042</v>
       </c>
       <c r="AN6">
-        <f>freight!BW25</f>
-        <v>1.8821850429784481</v>
+        <f>freight!AQ37</f>
+        <v>1.8560935383907711</v>
       </c>
       <c r="AO6">
-        <f>freight!BX25</f>
-        <v>1.9001376111594674</v>
+        <f>freight!AR37</f>
+        <v>1.8592876692911413</v>
       </c>
       <c r="AP6">
-        <f>freight!BY25</f>
-        <v>1.9180901793404868</v>
+        <f>freight!AS37</f>
+        <v>1.8624872969361514</v>
+      </c>
+      <c r="AQ6">
+        <f>freight!AT37</f>
+        <v>1.8656924307850895</v>
       </c>
     </row>
-    <row r="7" spans="1:42">
+    <row r="7" spans="1:43">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -15766,43 +21508,47 @@
         <v>1</v>
       </c>
       <c r="AG7" cm="1">
-        <f t="array" ref="AG7">TREND($V7:$AF7,$V$1:$AF$1,AG$1)</f>
+        <f t="array" ref="AG7">TREND($V7:$AF7,$W$1:$AG$1,AH$1)</f>
         <v>1</v>
       </c>
       <c r="AH7" cm="1">
-        <f t="array" ref="AH7">TREND($V7:$AF7,$V$1:$AF$1,AH$1)</f>
+        <f t="array" ref="AH7">TREND($V7:$AF7,$W$1:$AG$1,AI$1)</f>
         <v>1</v>
       </c>
       <c r="AI7" cm="1">
-        <f t="array" ref="AI7">TREND($V7:$AF7,$V$1:$AF$1,AI$1)</f>
+        <f t="array" ref="AI7">TREND($V7:$AF7,$W$1:$AG$1,AJ$1)</f>
         <v>1</v>
       </c>
       <c r="AJ7" cm="1">
-        <f t="array" ref="AJ7">TREND($V7:$AF7,$V$1:$AF$1,AJ$1)</f>
+        <f t="array" ref="AJ7">TREND($V7:$AF7,$W$1:$AG$1,AK$1)</f>
         <v>1</v>
       </c>
       <c r="AK7" cm="1">
-        <f t="array" ref="AK7">TREND($V7:$AF7,$V$1:$AF$1,AK$1)</f>
+        <f t="array" ref="AK7">TREND($V7:$AF7,$W$1:$AG$1,AL$1)</f>
         <v>1</v>
       </c>
       <c r="AL7" cm="1">
-        <f t="array" ref="AL7">TREND($V7:$AF7,$V$1:$AF$1,AL$1)</f>
+        <f t="array" ref="AL7">TREND($V7:$AF7,$W$1:$AG$1,AM$1)</f>
         <v>1</v>
       </c>
       <c r="AM7" cm="1">
-        <f t="array" ref="AM7">TREND($V7:$AF7,$V$1:$AF$1,AM$1)</f>
+        <f t="array" ref="AM7">TREND($V7:$AF7,$W$1:$AG$1,AN$1)</f>
         <v>1</v>
       </c>
       <c r="AN7" cm="1">
-        <f t="array" ref="AN7">TREND($V7:$AF7,$V$1:$AF$1,AN$1)</f>
+        <f t="array" ref="AN7">TREND($V7:$AF7,$W$1:$AG$1,AO$1)</f>
         <v>1</v>
       </c>
       <c r="AO7" cm="1">
-        <f t="array" ref="AO7">TREND($V7:$AF7,$V$1:$AF$1,AO$1)</f>
+        <f t="array" ref="AO7">TREND($V7:$AF7,$W$1:$AG$1,AP$1)</f>
         <v>1</v>
       </c>
       <c r="AP7" cm="1">
-        <f t="array" ref="AP7">TREND($V7:$AF7,$V$1:$AF$1,AP$1)</f>
+        <f t="array" ref="AP7">TREND($V7:$AF7,$W$1:$AG$1,AQ$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ7" cm="1">
+        <f t="array" ref="AQ7">TREND(R7:AP7,$R$1:$AP$1,$AQ$1,TRUE)</f>
         <v>1</v>
       </c>
     </row>
@@ -15814,24 +21560,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -16065,10 +21793,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0447F67E-7323-42C4-9E2C-56E0CFB6E612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16092,21 +21850,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0447F67E-7323-42C4-9E2C-56E0CFB6E612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>